--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -32,7 +32,7 @@
     <t>Actualización:</t>
   </si>
   <si>
-    <t>7/3/2026, 3:34:04 p. m.</t>
+    <t>7/3/2026, 3:41:51 p. m.</t>
   </si>
   <si>
     <t>ACCESORIOS</t>
@@ -10238,11 +10238,11 @@
       <c r="E11">
         <v>96</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="7">
         <v>31</v>
       </c>
-      <c r="G11" s="6" t="s">
-        <v>30</v>
+      <c r="G11" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -10261,11 +10261,11 @@
       <c r="E12">
         <v>96</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="7">
         <v>10</v>
       </c>
-      <c r="G12" s="6" t="s">
-        <v>30</v>
+      <c r="G12" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -10399,11 +10399,11 @@
       <c r="E18">
         <v>288</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="7">
         <v>854</v>
       </c>
-      <c r="G18" s="6" t="s">
-        <v>30</v>
+      <c r="G18" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -10514,11 +10514,11 @@
       <c r="E23">
         <v>300</v>
       </c>
-      <c r="F23" s="5">
+      <c r="F23" s="7">
         <v>1775</v>
       </c>
-      <c r="G23" s="6" t="s">
-        <v>30</v>
+      <c r="G23" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -11336,11 +11336,11 @@
       <c r="E4">
         <v>24</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="7">
         <v>15</v>
       </c>
-      <c r="G4" s="6" t="s">
-        <v>30</v>
+      <c r="G4" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -11497,11 +11497,11 @@
       <c r="E11">
         <v>24</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="7">
         <v>180</v>
       </c>
-      <c r="G11" s="6" t="s">
-        <v>30</v>
+      <c r="G11" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -11543,11 +11543,11 @@
       <c r="E13">
         <v>24</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="7">
         <v>168</v>
       </c>
-      <c r="G13" s="6" t="s">
-        <v>30</v>
+      <c r="G13" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -11566,11 +11566,11 @@
       <c r="E14">
         <v>36</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="7">
         <v>182</v>
       </c>
-      <c r="G14" s="6" t="s">
-        <v>30</v>
+      <c r="G14" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -11635,11 +11635,11 @@
       <c r="E17">
         <v>24</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F17" s="7">
         <v>76</v>
       </c>
-      <c r="G17" s="6" t="s">
-        <v>30</v>
+      <c r="G17" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -12026,11 +12026,11 @@
       <c r="E34">
         <v>50</v>
       </c>
-      <c r="F34" s="5">
+      <c r="F34" s="7">
         <v>263</v>
       </c>
-      <c r="G34" s="6" t="s">
-        <v>30</v>
+      <c r="G34" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -12210,11 +12210,11 @@
       <c r="E42">
         <v>48</v>
       </c>
-      <c r="F42" s="5">
+      <c r="F42" s="7">
         <v>39</v>
       </c>
-      <c r="G42" s="6" t="s">
-        <v>30</v>
+      <c r="G42" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -12440,11 +12440,11 @@
       <c r="E52">
         <v>48</v>
       </c>
-      <c r="F52" s="5">
+      <c r="F52" s="7">
         <v>117</v>
       </c>
-      <c r="G52" s="6" t="s">
-        <v>30</v>
+      <c r="G52" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -12486,11 +12486,11 @@
       <c r="E54">
         <v>48</v>
       </c>
-      <c r="F54" s="5">
+      <c r="F54" s="7">
         <v>162</v>
       </c>
-      <c r="G54" s="6" t="s">
-        <v>30</v>
+      <c r="G54" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -12532,11 +12532,11 @@
       <c r="E56">
         <v>36</v>
       </c>
-      <c r="F56" s="5">
+      <c r="F56" s="7">
         <v>196</v>
       </c>
-      <c r="G56" s="6" t="s">
-        <v>30</v>
+      <c r="G56" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -12716,11 +12716,11 @@
       <c r="E64">
         <v>48</v>
       </c>
-      <c r="F64" s="5">
+      <c r="F64" s="7">
         <v>418</v>
       </c>
-      <c r="G64" s="6" t="s">
-        <v>30</v>
+      <c r="G64" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -13084,11 +13084,11 @@
       <c r="E80">
         <v>60</v>
       </c>
-      <c r="F80" s="5">
+      <c r="F80" s="7">
         <v>18</v>
       </c>
-      <c r="G80" s="6" t="s">
-        <v>30</v>
+      <c r="G80" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -13199,11 +13199,11 @@
       <c r="E85">
         <v>60</v>
       </c>
-      <c r="F85" s="5">
+      <c r="F85" s="7">
         <v>154</v>
       </c>
-      <c r="G85" s="6" t="s">
-        <v>30</v>
+      <c r="G85" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -13222,11 +13222,11 @@
       <c r="E86">
         <v>60</v>
       </c>
-      <c r="F86" s="5">
+      <c r="F86" s="7">
         <v>333</v>
       </c>
-      <c r="G86" s="6" t="s">
-        <v>30</v>
+      <c r="G86" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -13636,11 +13636,11 @@
       <c r="E104">
         <v>60</v>
       </c>
-      <c r="F104" s="5">
+      <c r="F104" s="7">
         <v>368</v>
       </c>
-      <c r="G104" s="6" t="s">
-        <v>30</v>
+      <c r="G104" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -14004,11 +14004,11 @@
       <c r="E120">
         <v>36</v>
       </c>
-      <c r="F120" s="5">
+      <c r="F120" s="7">
         <v>261</v>
       </c>
-      <c r="G120" s="6" t="s">
-        <v>30</v>
+      <c r="G120" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -14073,11 +14073,11 @@
       <c r="E123">
         <v>36</v>
       </c>
-      <c r="F123" s="5">
+      <c r="F123" s="7">
         <v>10</v>
       </c>
-      <c r="G123" s="6" t="s">
-        <v>30</v>
+      <c r="G123" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
@@ -14165,11 +14165,11 @@
       <c r="E127">
         <v>120</v>
       </c>
-      <c r="F127" s="5">
+      <c r="F127" s="7">
         <v>155</v>
       </c>
-      <c r="G127" s="6" t="s">
-        <v>30</v>
+      <c r="G127" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
@@ -14188,11 +14188,11 @@
       <c r="E128">
         <v>120</v>
       </c>
-      <c r="F128" s="5">
+      <c r="F128" s="7">
         <v>519</v>
       </c>
-      <c r="G128" s="6" t="s">
-        <v>30</v>
+      <c r="G128" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -14211,11 +14211,11 @@
       <c r="E129">
         <v>120</v>
       </c>
-      <c r="F129" s="5">
+      <c r="F129" s="7">
         <v>1067</v>
       </c>
-      <c r="G129" s="6" t="s">
-        <v>30</v>
+      <c r="G129" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -14234,11 +14234,11 @@
       <c r="E130">
         <v>120</v>
       </c>
-      <c r="F130" s="5">
+      <c r="F130" s="7">
         <v>884</v>
       </c>
-      <c r="G130" s="6" t="s">
-        <v>30</v>
+      <c r="G130" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -14257,11 +14257,11 @@
       <c r="E131">
         <v>120</v>
       </c>
-      <c r="F131" s="5">
+      <c r="F131" s="7">
         <v>55</v>
       </c>
-      <c r="G131" s="6" t="s">
-        <v>30</v>
+      <c r="G131" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
@@ -14280,11 +14280,11 @@
       <c r="E132">
         <v>120</v>
       </c>
-      <c r="F132" s="5">
+      <c r="F132" s="7">
         <v>233</v>
       </c>
-      <c r="G132" s="6" t="s">
-        <v>30</v>
+      <c r="G132" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -14326,11 +14326,11 @@
       <c r="E134">
         <v>120</v>
       </c>
-      <c r="F134" s="5">
+      <c r="F134" s="7">
         <v>1017</v>
       </c>
-      <c r="G134" s="6" t="s">
-        <v>30</v>
+      <c r="G134" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -14418,11 +14418,11 @@
       <c r="E138">
         <v>120</v>
       </c>
-      <c r="F138" s="5">
+      <c r="F138" s="7">
         <v>10</v>
       </c>
-      <c r="G138" s="6" t="s">
-        <v>30</v>
+      <c r="G138" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
@@ -14533,11 +14533,11 @@
       <c r="E143">
         <v>120</v>
       </c>
-      <c r="F143" s="5">
+      <c r="F143" s="7">
         <v>514</v>
       </c>
-      <c r="G143" s="6" t="s">
-        <v>30</v>
+      <c r="G143" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -14648,11 +14648,11 @@
       <c r="E148">
         <v>120</v>
       </c>
-      <c r="F148" s="5">
+      <c r="F148" s="7">
         <v>397</v>
       </c>
-      <c r="G148" s="6" t="s">
-        <v>30</v>
+      <c r="G148" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
@@ -14694,11 +14694,11 @@
       <c r="E150">
         <v>120</v>
       </c>
-      <c r="F150" s="5">
+      <c r="F150" s="7">
         <v>386</v>
       </c>
-      <c r="G150" s="6" t="s">
-        <v>30</v>
+      <c r="G150" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
@@ -14809,11 +14809,11 @@
       <c r="E155">
         <v>120</v>
       </c>
-      <c r="F155" s="5">
+      <c r="F155" s="7">
         <v>908</v>
       </c>
-      <c r="G155" s="6" t="s">
-        <v>30</v>
+      <c r="G155" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
@@ -14832,11 +14832,11 @@
       <c r="E156">
         <v>120</v>
       </c>
-      <c r="F156" s="5">
+      <c r="F156" s="7">
         <v>306</v>
       </c>
-      <c r="G156" s="6" t="s">
-        <v>30</v>
+      <c r="G156" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
@@ -14878,11 +14878,11 @@
       <c r="E158">
         <v>120</v>
       </c>
-      <c r="F158" s="5">
+      <c r="F158" s="7">
         <v>1101</v>
       </c>
-      <c r="G158" s="6" t="s">
-        <v>30</v>
+      <c r="G158" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -15016,11 +15016,11 @@
       <c r="E164">
         <v>120</v>
       </c>
-      <c r="F164" s="5">
+      <c r="F164" s="7">
         <v>264</v>
       </c>
-      <c r="G164" s="6" t="s">
-        <v>30</v>
+      <c r="G164" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
@@ -15085,11 +15085,11 @@
       <c r="E167">
         <v>120</v>
       </c>
-      <c r="F167" s="5">
+      <c r="F167" s="7">
         <v>764</v>
       </c>
-      <c r="G167" s="6" t="s">
-        <v>30</v>
+      <c r="G167" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -15108,11 +15108,11 @@
       <c r="E168">
         <v>120</v>
       </c>
-      <c r="F168" s="5">
+      <c r="F168" s="7">
         <v>157</v>
       </c>
-      <c r="G168" s="6" t="s">
-        <v>30</v>
+      <c r="G168" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
@@ -15131,11 +15131,11 @@
       <c r="E169">
         <v>120</v>
       </c>
-      <c r="F169" s="5">
+      <c r="F169" s="7">
         <v>703</v>
       </c>
-      <c r="G169" s="6" t="s">
-        <v>30</v>
+      <c r="G169" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
@@ -15269,11 +15269,11 @@
       <c r="E175">
         <v>12</v>
       </c>
-      <c r="F175" s="5">
+      <c r="F175" s="7">
         <v>22</v>
       </c>
-      <c r="G175" s="6" t="s">
-        <v>30</v>
+      <c r="G175" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
@@ -15453,11 +15453,11 @@
       <c r="E183">
         <v>12</v>
       </c>
-      <c r="F183" s="5">
+      <c r="F183" s="7">
         <v>53</v>
       </c>
-      <c r="G183" s="6" t="s">
-        <v>30</v>
+      <c r="G183" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
@@ -15476,11 +15476,11 @@
       <c r="E184">
         <v>12</v>
       </c>
-      <c r="F184" s="5">
+      <c r="F184" s="7">
         <v>11</v>
       </c>
-      <c r="G184" s="6" t="s">
-        <v>30</v>
+      <c r="G184" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
@@ -15795,11 +15795,11 @@
       <c r="E6">
         <v>18</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="7">
         <v>115</v>
       </c>
-      <c r="G6" s="6" t="s">
-        <v>30</v>
+      <c r="G6" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -16462,11 +16462,11 @@
       <c r="E35">
         <v>576</v>
       </c>
-      <c r="F35" s="5">
+      <c r="F35" s="7">
         <v>2304</v>
       </c>
-      <c r="G35" s="6" t="s">
-        <v>30</v>
+      <c r="G35" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -16508,11 +16508,11 @@
       <c r="E37">
         <v>576</v>
       </c>
-      <c r="F37" s="5">
+      <c r="F37" s="7">
         <v>1469</v>
       </c>
-      <c r="G37" s="6" t="s">
-        <v>30</v>
+      <c r="G37" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -16531,11 +16531,11 @@
       <c r="E38">
         <v>576</v>
       </c>
-      <c r="F38" s="5">
+      <c r="F38" s="7">
         <v>63</v>
       </c>
-      <c r="G38" s="6" t="s">
-        <v>30</v>
+      <c r="G38" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -16600,11 +16600,11 @@
       <c r="E41">
         <v>576</v>
       </c>
-      <c r="F41" s="5">
+      <c r="F41" s="7">
         <v>2846</v>
       </c>
-      <c r="G41" s="6" t="s">
-        <v>30</v>
+      <c r="G41" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -16623,11 +16623,11 @@
       <c r="E42">
         <v>576</v>
       </c>
-      <c r="F42" s="5">
+      <c r="F42" s="7">
         <v>981</v>
       </c>
-      <c r="G42" s="6" t="s">
-        <v>30</v>
+      <c r="G42" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -16669,11 +16669,11 @@
       <c r="E44">
         <v>576</v>
       </c>
-      <c r="F44" s="5">
+      <c r="F44" s="7">
         <v>125</v>
       </c>
-      <c r="G44" s="6" t="s">
-        <v>30</v>
+      <c r="G44" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -17609,11 +17609,11 @@
       <c r="E7">
         <v>120</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="7">
         <v>1031</v>
       </c>
-      <c r="G7" s="6" t="s">
-        <v>30</v>
+      <c r="G7" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -17632,11 +17632,11 @@
       <c r="E8">
         <v>120</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="7">
         <v>268</v>
       </c>
-      <c r="G8" s="6" t="s">
-        <v>30</v>
+      <c r="G8" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -17655,11 +17655,11 @@
       <c r="E9">
         <v>240</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="7">
         <v>253</v>
       </c>
-      <c r="G9" s="6" t="s">
-        <v>30</v>
+      <c r="G9" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -17678,11 +17678,11 @@
       <c r="E10">
         <v>200</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="7">
         <v>59</v>
       </c>
-      <c r="G10" s="6" t="s">
-        <v>30</v>
+      <c r="G10" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -17724,11 +17724,11 @@
       <c r="E12">
         <v>60</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="7">
         <v>132</v>
       </c>
-      <c r="G12" s="6" t="s">
-        <v>30</v>
+      <c r="G12" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -17747,11 +17747,11 @@
       <c r="E13">
         <v>120</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="7">
         <v>191</v>
       </c>
-      <c r="G13" s="6" t="s">
-        <v>30</v>
+      <c r="G13" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -17770,11 +17770,11 @@
       <c r="E14">
         <v>120</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="7">
         <v>189</v>
       </c>
-      <c r="G14" s="6" t="s">
-        <v>30</v>
+      <c r="G14" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -17793,11 +17793,11 @@
       <c r="E15">
         <v>120</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="7">
         <v>84</v>
       </c>
-      <c r="G15" s="6" t="s">
-        <v>30</v>
+      <c r="G15" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -17816,11 +17816,11 @@
       <c r="E16">
         <v>120</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="7">
         <v>692</v>
       </c>
-      <c r="G16" s="6" t="s">
-        <v>30</v>
+      <c r="G16" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -17839,11 +17839,11 @@
       <c r="E17">
         <v>120</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F17" s="7">
         <v>257</v>
       </c>
-      <c r="G17" s="6" t="s">
-        <v>30</v>
+      <c r="G17" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -17862,11 +17862,11 @@
       <c r="E18">
         <v>120</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="7">
         <v>983</v>
       </c>
-      <c r="G18" s="6" t="s">
-        <v>30</v>
+      <c r="G18" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -17885,11 +17885,11 @@
       <c r="E19">
         <v>120</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F19" s="7">
         <v>195</v>
       </c>
-      <c r="G19" s="6" t="s">
-        <v>30</v>
+      <c r="G19" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -17908,11 +17908,11 @@
       <c r="E20">
         <v>120</v>
       </c>
-      <c r="F20" s="5">
+      <c r="F20" s="7">
         <v>75</v>
       </c>
-      <c r="G20" s="6" t="s">
-        <v>30</v>
+      <c r="G20" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -17931,11 +17931,11 @@
       <c r="E21">
         <v>120</v>
       </c>
-      <c r="F21" s="5">
+      <c r="F21" s="7">
         <v>439</v>
       </c>
-      <c r="G21" s="6" t="s">
-        <v>30</v>
+      <c r="G21" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -18000,11 +18000,11 @@
       <c r="E24">
         <v>120</v>
       </c>
-      <c r="F24" s="5">
+      <c r="F24" s="7">
         <v>113</v>
       </c>
-      <c r="G24" s="6" t="s">
-        <v>30</v>
+      <c r="G24" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -18023,11 +18023,11 @@
       <c r="E25">
         <v>120</v>
       </c>
-      <c r="F25" s="5">
+      <c r="F25" s="7">
         <v>348</v>
       </c>
-      <c r="G25" s="6" t="s">
-        <v>30</v>
+      <c r="G25" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -18046,11 +18046,11 @@
       <c r="E26">
         <v>120</v>
       </c>
-      <c r="F26" s="5">
+      <c r="F26" s="7">
         <v>123</v>
       </c>
-      <c r="G26" s="6" t="s">
-        <v>30</v>
+      <c r="G26" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -18069,11 +18069,11 @@
       <c r="E27">
         <v>120</v>
       </c>
-      <c r="F27" s="5">
+      <c r="F27" s="7">
         <v>160</v>
       </c>
-      <c r="G27" s="6" t="s">
-        <v>30</v>
+      <c r="G27" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -18115,11 +18115,11 @@
       <c r="E29">
         <v>72</v>
       </c>
-      <c r="F29" s="5">
+      <c r="F29" s="7">
         <v>94</v>
       </c>
-      <c r="G29" s="6" t="s">
-        <v>30</v>
+      <c r="G29" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -18138,11 +18138,11 @@
       <c r="E30">
         <v>120</v>
       </c>
-      <c r="F30" s="5">
+      <c r="F30" s="7">
         <v>56</v>
       </c>
-      <c r="G30" s="6" t="s">
-        <v>30</v>
+      <c r="G30" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -18230,11 +18230,11 @@
       <c r="E34">
         <v>120</v>
       </c>
-      <c r="F34" s="5">
+      <c r="F34" s="7">
         <v>907</v>
       </c>
-      <c r="G34" s="6" t="s">
-        <v>30</v>
+      <c r="G34" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -18276,11 +18276,11 @@
       <c r="E36">
         <v>120</v>
       </c>
-      <c r="F36" s="5">
+      <c r="F36" s="7">
         <v>118</v>
       </c>
-      <c r="G36" s="6" t="s">
-        <v>30</v>
+      <c r="G36" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -18299,11 +18299,11 @@
       <c r="E37">
         <v>240</v>
       </c>
-      <c r="F37" s="5">
+      <c r="F37" s="7">
         <v>944</v>
       </c>
-      <c r="G37" s="6" t="s">
-        <v>30</v>
+      <c r="G37" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -18322,11 +18322,11 @@
       <c r="E38">
         <v>120</v>
       </c>
-      <c r="F38" s="5">
+      <c r="F38" s="7">
         <v>123</v>
       </c>
-      <c r="G38" s="6" t="s">
-        <v>30</v>
+      <c r="G38" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -18345,11 +18345,11 @@
       <c r="E39">
         <v>240</v>
       </c>
-      <c r="F39" s="5">
+      <c r="F39" s="7">
         <v>278</v>
       </c>
-      <c r="G39" s="6" t="s">
-        <v>30</v>
+      <c r="G39" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -18368,11 +18368,11 @@
       <c r="E40">
         <v>240</v>
       </c>
-      <c r="F40" s="5">
+      <c r="F40" s="7">
         <v>245</v>
       </c>
-      <c r="G40" s="6" t="s">
-        <v>30</v>
+      <c r="G40" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -18391,11 +18391,11 @@
       <c r="E41">
         <v>240</v>
       </c>
-      <c r="F41" s="5">
+      <c r="F41" s="7">
         <v>107</v>
       </c>
-      <c r="G41" s="6" t="s">
-        <v>30</v>
+      <c r="G41" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -18414,11 +18414,11 @@
       <c r="E42">
         <v>240</v>
       </c>
-      <c r="F42" s="5">
+      <c r="F42" s="7">
         <v>273</v>
       </c>
-      <c r="G42" s="6" t="s">
-        <v>30</v>
+      <c r="G42" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -18460,11 +18460,11 @@
       <c r="E44">
         <v>480</v>
       </c>
-      <c r="F44" s="5">
+      <c r="F44" s="7">
         <v>1090</v>
       </c>
-      <c r="G44" s="6" t="s">
-        <v>30</v>
+      <c r="G44" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -18483,11 +18483,11 @@
       <c r="E45">
         <v>240</v>
       </c>
-      <c r="F45" s="5">
+      <c r="F45" s="7">
         <v>163</v>
       </c>
-      <c r="G45" s="6" t="s">
-        <v>30</v>
+      <c r="G45" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -18506,11 +18506,11 @@
       <c r="E46">
         <v>800</v>
       </c>
-      <c r="F46" s="5">
+      <c r="F46" s="7">
         <v>1475</v>
       </c>
-      <c r="G46" s="6" t="s">
-        <v>30</v>
+      <c r="G46" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -18529,11 +18529,11 @@
       <c r="E47">
         <v>240</v>
       </c>
-      <c r="F47" s="5">
+      <c r="F47" s="7">
         <v>164</v>
       </c>
-      <c r="G47" s="6" t="s">
-        <v>30</v>
+      <c r="G47" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -18552,11 +18552,11 @@
       <c r="E48">
         <v>120</v>
       </c>
-      <c r="F48" s="5">
+      <c r="F48" s="7">
         <v>140</v>
       </c>
-      <c r="G48" s="6" t="s">
-        <v>30</v>
+      <c r="G48" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -18575,11 +18575,11 @@
       <c r="E49">
         <v>120</v>
       </c>
-      <c r="F49" s="5">
+      <c r="F49" s="7">
         <v>261</v>
       </c>
-      <c r="G49" s="6" t="s">
-        <v>30</v>
+      <c r="G49" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -18598,11 +18598,11 @@
       <c r="E50">
         <v>120</v>
       </c>
-      <c r="F50" s="5">
+      <c r="F50" s="7">
         <v>291</v>
       </c>
-      <c r="G50" s="6" t="s">
-        <v>30</v>
+      <c r="G50" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -18621,11 +18621,11 @@
       <c r="E51">
         <v>10</v>
       </c>
-      <c r="F51" s="5">
+      <c r="F51" s="7">
         <v>10</v>
       </c>
-      <c r="G51" s="6" t="s">
-        <v>30</v>
+      <c r="G51" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -18644,11 +18644,11 @@
       <c r="E52">
         <v>60</v>
       </c>
-      <c r="F52" s="5">
+      <c r="F52" s="7">
         <v>82</v>
       </c>
-      <c r="G52" s="6" t="s">
-        <v>30</v>
+      <c r="G52" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -18667,11 +18667,11 @@
       <c r="E53">
         <v>20</v>
       </c>
-      <c r="F53" s="5">
+      <c r="F53" s="7">
         <v>27</v>
       </c>
-      <c r="G53" s="6" t="s">
-        <v>30</v>
+      <c r="G53" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -18690,11 +18690,11 @@
       <c r="E54">
         <v>720</v>
       </c>
-      <c r="F54" s="5">
+      <c r="F54" s="7">
         <v>2462</v>
       </c>
-      <c r="G54" s="6" t="s">
-        <v>30</v>
+      <c r="G54" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -18713,11 +18713,11 @@
       <c r="E55">
         <v>120</v>
       </c>
-      <c r="F55" s="5">
+      <c r="F55" s="7">
         <v>208</v>
       </c>
-      <c r="G55" s="6" t="s">
-        <v>30</v>
+      <c r="G55" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -18759,11 +18759,11 @@
       <c r="E57">
         <v>720</v>
       </c>
-      <c r="F57" s="5">
+      <c r="F57" s="7">
         <v>4873</v>
       </c>
-      <c r="G57" s="6" t="s">
-        <v>30</v>
+      <c r="G57" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -18782,11 +18782,11 @@
       <c r="E58">
         <v>240</v>
       </c>
-      <c r="F58" s="5">
+      <c r="F58" s="7">
         <v>201</v>
       </c>
-      <c r="G58" s="6" t="s">
-        <v>30</v>
+      <c r="G58" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -18851,11 +18851,11 @@
       <c r="E61">
         <v>240</v>
       </c>
-      <c r="F61" s="5">
+      <c r="F61" s="7">
         <v>300</v>
       </c>
-      <c r="G61" s="6" t="s">
-        <v>30</v>
+      <c r="G61" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -18874,11 +18874,11 @@
       <c r="E62">
         <v>240</v>
       </c>
-      <c r="F62" s="5">
+      <c r="F62" s="7">
         <v>198</v>
       </c>
-      <c r="G62" s="6" t="s">
-        <v>30</v>
+      <c r="G62" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -18920,11 +18920,11 @@
       <c r="E64">
         <v>60</v>
       </c>
-      <c r="F64" s="5">
+      <c r="F64" s="7">
         <v>513</v>
       </c>
-      <c r="G64" s="6" t="s">
-        <v>30</v>
+      <c r="G64" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -18943,11 +18943,11 @@
       <c r="E65">
         <v>60</v>
       </c>
-      <c r="F65" s="5">
+      <c r="F65" s="7">
         <v>65</v>
       </c>
-      <c r="G65" s="6" t="s">
-        <v>30</v>
+      <c r="G65" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -18966,11 +18966,11 @@
       <c r="E66">
         <v>120</v>
       </c>
-      <c r="F66" s="5">
+      <c r="F66" s="7">
         <v>69</v>
       </c>
-      <c r="G66" s="6" t="s">
-        <v>30</v>
+      <c r="G66" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -19012,11 +19012,11 @@
       <c r="E68">
         <v>240</v>
       </c>
-      <c r="F68" s="5">
+      <c r="F68" s="7">
         <v>55</v>
       </c>
-      <c r="G68" s="6" t="s">
-        <v>30</v>
+      <c r="G68" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -19058,11 +19058,11 @@
       <c r="E70">
         <v>240</v>
       </c>
-      <c r="F70" s="5">
+      <c r="F70" s="7">
         <v>130</v>
       </c>
-      <c r="G70" s="6" t="s">
-        <v>30</v>
+      <c r="G70" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -19104,11 +19104,11 @@
       <c r="E72">
         <v>480</v>
       </c>
-      <c r="F72" s="5">
+      <c r="F72" s="7">
         <v>412</v>
       </c>
-      <c r="G72" s="6" t="s">
-        <v>30</v>
+      <c r="G72" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -19127,11 +19127,11 @@
       <c r="E73">
         <v>240</v>
       </c>
-      <c r="F73" s="5">
+      <c r="F73" s="7">
         <v>500</v>
       </c>
-      <c r="G73" s="6" t="s">
-        <v>30</v>
+      <c r="G73" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -19150,11 +19150,11 @@
       <c r="E74">
         <v>240</v>
       </c>
-      <c r="F74" s="5">
+      <c r="F74" s="7">
         <v>1529</v>
       </c>
-      <c r="G74" s="6" t="s">
-        <v>30</v>
+      <c r="G74" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -19219,11 +19219,11 @@
       <c r="E77">
         <v>600</v>
       </c>
-      <c r="F77" s="5">
+      <c r="F77" s="7">
         <v>539</v>
       </c>
-      <c r="G77" s="6" t="s">
-        <v>30</v>
+      <c r="G77" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -19242,11 +19242,11 @@
       <c r="E78">
         <v>120</v>
       </c>
-      <c r="F78" s="5">
+      <c r="F78" s="7">
         <v>114</v>
       </c>
-      <c r="G78" s="6" t="s">
-        <v>30</v>
+      <c r="G78" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -19288,11 +19288,11 @@
       <c r="E80">
         <v>60</v>
       </c>
-      <c r="F80" s="5">
+      <c r="F80" s="7">
         <v>12</v>
       </c>
-      <c r="G80" s="6" t="s">
-        <v>30</v>
+      <c r="G80" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -19380,11 +19380,11 @@
       <c r="E84">
         <v>40</v>
       </c>
-      <c r="F84" s="5">
+      <c r="F84" s="7">
         <v>80</v>
       </c>
-      <c r="G84" s="6" t="s">
-        <v>30</v>
+      <c r="G84" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.25">
@@ -19541,11 +19541,11 @@
       <c r="E91">
         <v>10</v>
       </c>
-      <c r="F91" s="5">
+      <c r="F91" s="7">
         <v>68</v>
       </c>
-      <c r="G91" s="6" t="s">
-        <v>30</v>
+      <c r="G91" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -19863,11 +19863,11 @@
       <c r="E105">
         <v>56</v>
       </c>
-      <c r="F105" s="5">
+      <c r="F105" s="7">
         <v>354</v>
       </c>
-      <c r="G105" s="6" t="s">
-        <v>30</v>
+      <c r="G105" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.25">
@@ -19886,11 +19886,11 @@
       <c r="E106">
         <v>120</v>
       </c>
-      <c r="F106" s="5">
+      <c r="F106" s="7">
         <v>15</v>
       </c>
-      <c r="G106" s="6" t="s">
-        <v>30</v>
+      <c r="G106" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -19932,11 +19932,11 @@
       <c r="E108">
         <v>18</v>
       </c>
-      <c r="F108" s="5">
+      <c r="F108" s="7">
         <v>79</v>
       </c>
-      <c r="G108" s="6" t="s">
-        <v>30</v>
+      <c r="G108" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -20070,11 +20070,11 @@
       <c r="E114">
         <v>5</v>
       </c>
-      <c r="F114" s="5">
+      <c r="F114" s="7">
         <v>39</v>
       </c>
-      <c r="G114" s="6" t="s">
-        <v>30</v>
+      <c r="G114" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
@@ -20093,11 +20093,11 @@
       <c r="E115">
         <v>800</v>
       </c>
-      <c r="F115" s="5">
+      <c r="F115" s="7">
         <v>312</v>
       </c>
-      <c r="G115" s="6" t="s">
-        <v>30</v>
+      <c r="G115" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
@@ -20208,11 +20208,11 @@
       <c r="E120">
         <v>10</v>
       </c>
-      <c r="F120" s="5">
+      <c r="F120" s="7">
         <v>36</v>
       </c>
-      <c r="G120" s="6" t="s">
-        <v>30</v>
+      <c r="G120" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -20277,11 +20277,11 @@
       <c r="E123">
         <v>40</v>
       </c>
-      <c r="F123" s="5">
+      <c r="F123" s="7">
         <v>127</v>
       </c>
-      <c r="G123" s="6" t="s">
-        <v>30</v>
+      <c r="G123" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
@@ -20300,11 +20300,11 @@
       <c r="E124">
         <v>4</v>
       </c>
-      <c r="F124" s="5">
+      <c r="F124" s="7">
         <v>37</v>
       </c>
-      <c r="G124" s="6" t="s">
-        <v>30</v>
+      <c r="G124" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
@@ -20346,11 +20346,11 @@
       <c r="E126">
         <v>4</v>
       </c>
-      <c r="F126" s="5">
+      <c r="F126" s="7">
         <v>17</v>
       </c>
-      <c r="G126" s="6" t="s">
-        <v>30</v>
+      <c r="G126" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
@@ -20369,11 +20369,11 @@
       <c r="E127">
         <v>4</v>
       </c>
-      <c r="F127" s="5">
+      <c r="F127" s="7">
         <v>24</v>
       </c>
-      <c r="G127" s="6" t="s">
-        <v>30</v>
+      <c r="G127" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
@@ -20392,11 +20392,11 @@
       <c r="E128">
         <v>4</v>
       </c>
-      <c r="F128" s="5">
+      <c r="F128" s="7">
         <v>18</v>
       </c>
-      <c r="G128" s="6" t="s">
-        <v>30</v>
+      <c r="G128" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -20461,11 +20461,11 @@
       <c r="E131">
         <v>60</v>
       </c>
-      <c r="F131" s="5">
+      <c r="F131" s="7">
         <v>357</v>
       </c>
-      <c r="G131" s="6" t="s">
-        <v>30</v>
+      <c r="G131" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
@@ -20484,11 +20484,11 @@
       <c r="E132">
         <v>60</v>
       </c>
-      <c r="F132" s="5">
+      <c r="F132" s="7">
         <v>58</v>
       </c>
-      <c r="G132" s="6" t="s">
-        <v>30</v>
+      <c r="G132" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -20507,11 +20507,11 @@
       <c r="E133">
         <v>60</v>
       </c>
-      <c r="F133" s="5">
+      <c r="F133" s="7">
         <v>138</v>
       </c>
-      <c r="G133" s="6" t="s">
-        <v>30</v>
+      <c r="G133" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -20530,11 +20530,11 @@
       <c r="E134">
         <v>60</v>
       </c>
-      <c r="F134" s="5">
+      <c r="F134" s="7">
         <v>480</v>
       </c>
-      <c r="G134" s="6" t="s">
-        <v>30</v>
+      <c r="G134" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -20553,11 +20553,11 @@
       <c r="E135">
         <v>60</v>
       </c>
-      <c r="F135" s="5">
+      <c r="F135" s="7">
         <v>521</v>
       </c>
-      <c r="G135" s="6" t="s">
-        <v>30</v>
+      <c r="G135" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -20576,11 +20576,11 @@
       <c r="E136">
         <v>60</v>
       </c>
-      <c r="F136" s="5">
+      <c r="F136" s="7">
         <v>480</v>
       </c>
-      <c r="G136" s="6" t="s">
-        <v>30</v>
+      <c r="G136" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -20645,11 +20645,11 @@
       <c r="E139">
         <v>63</v>
       </c>
-      <c r="F139" s="5">
+      <c r="F139" s="7">
         <v>566</v>
       </c>
-      <c r="G139" s="6" t="s">
-        <v>30</v>
+      <c r="G139" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -20691,11 +20691,11 @@
       <c r="E141">
         <v>40</v>
       </c>
-      <c r="F141" s="5">
+      <c r="F141" s="7">
         <v>108</v>
       </c>
-      <c r="G141" s="6" t="s">
-        <v>30</v>
+      <c r="G141" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -20714,11 +20714,11 @@
       <c r="E142">
         <v>60</v>
       </c>
-      <c r="F142" s="5">
+      <c r="F142" s="7">
         <v>122</v>
       </c>
-      <c r="G142" s="6" t="s">
-        <v>30</v>
+      <c r="G142" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
@@ -20737,11 +20737,11 @@
       <c r="E143">
         <v>6</v>
       </c>
-      <c r="F143" s="5">
+      <c r="F143" s="7">
         <v>15</v>
       </c>
-      <c r="G143" s="6" t="s">
-        <v>30</v>
+      <c r="G143" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -20783,11 +20783,11 @@
       <c r="E145">
         <v>8</v>
       </c>
-      <c r="F145" s="5">
+      <c r="F145" s="7">
         <v>10</v>
       </c>
-      <c r="G145" s="6" t="s">
-        <v>30</v>
+      <c r="G145" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
@@ -20806,11 +20806,11 @@
       <c r="E146">
         <v>30</v>
       </c>
-      <c r="F146" s="5">
+      <c r="F146" s="7">
         <v>34</v>
       </c>
-      <c r="G146" s="6" t="s">
-        <v>30</v>
+      <c r="G146" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
@@ -20852,11 +20852,11 @@
       <c r="E148">
         <v>5</v>
       </c>
-      <c r="F148" s="5">
-        <v>30</v>
-      </c>
-      <c r="G148" s="6" t="s">
-        <v>30</v>
+      <c r="F148" s="7">
+        <v>30</v>
+      </c>
+      <c r="G148" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
@@ -20967,11 +20967,11 @@
       <c r="E153">
         <v>240</v>
       </c>
-      <c r="F153" s="5">
+      <c r="F153" s="7">
         <v>640</v>
       </c>
-      <c r="G153" s="6" t="s">
-        <v>30</v>
+      <c r="G153" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
@@ -20990,11 +20990,11 @@
       <c r="E154">
         <v>120</v>
       </c>
-      <c r="F154" s="5">
+      <c r="F154" s="7">
         <v>121</v>
       </c>
-      <c r="G154" s="6" t="s">
-        <v>30</v>
+      <c r="G154" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
@@ -21059,11 +21059,11 @@
       <c r="E157">
         <v>72</v>
       </c>
-      <c r="F157" s="5">
+      <c r="F157" s="7">
         <v>66</v>
       </c>
-      <c r="G157" s="6" t="s">
-        <v>30</v>
+      <c r="G157" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
@@ -21082,11 +21082,11 @@
       <c r="E158">
         <v>60</v>
       </c>
-      <c r="F158" s="5">
-        <v>30</v>
-      </c>
-      <c r="G158" s="6" t="s">
-        <v>30</v>
+      <c r="F158" s="7">
+        <v>30</v>
+      </c>
+      <c r="G158" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -21105,11 +21105,11 @@
       <c r="E159">
         <v>120</v>
       </c>
-      <c r="F159" s="5">
+      <c r="F159" s="7">
         <v>83</v>
       </c>
-      <c r="G159" s="6" t="s">
-        <v>30</v>
+      <c r="G159" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -21128,11 +21128,11 @@
       <c r="E160">
         <v>72</v>
       </c>
-      <c r="F160" s="5">
+      <c r="F160" s="7">
         <v>10</v>
       </c>
-      <c r="G160" s="6" t="s">
-        <v>30</v>
+      <c r="G160" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -21151,11 +21151,11 @@
       <c r="E161">
         <v>20</v>
       </c>
-      <c r="F161" s="5">
+      <c r="F161" s="7">
         <v>51</v>
       </c>
-      <c r="G161" s="6" t="s">
-        <v>30</v>
+      <c r="G161" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -21174,11 +21174,11 @@
       <c r="E162">
         <v>100</v>
       </c>
-      <c r="F162" s="5">
+      <c r="F162" s="7">
         <v>74</v>
       </c>
-      <c r="G162" s="6" t="s">
-        <v>30</v>
+      <c r="G162" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
@@ -21197,11 +21197,11 @@
       <c r="E163">
         <v>5</v>
       </c>
-      <c r="F163" s="5">
+      <c r="F163" s="7">
         <v>11</v>
       </c>
-      <c r="G163" s="6" t="s">
-        <v>30</v>
+      <c r="G163" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -21243,11 +21243,11 @@
       <c r="E165">
         <v>20</v>
       </c>
-      <c r="F165" s="5">
+      <c r="F165" s="7">
         <v>35</v>
       </c>
-      <c r="G165" s="6" t="s">
-        <v>30</v>
+      <c r="G165" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
@@ -21266,11 +21266,11 @@
       <c r="E166">
         <v>20</v>
       </c>
-      <c r="F166" s="5">
+      <c r="F166" s="7">
         <v>62</v>
       </c>
-      <c r="G166" s="6" t="s">
-        <v>30</v>
+      <c r="G166" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
@@ -21289,11 +21289,11 @@
       <c r="E167">
         <v>24</v>
       </c>
-      <c r="F167" s="5">
+      <c r="F167" s="7">
         <v>28</v>
       </c>
-      <c r="G167" s="6" t="s">
-        <v>30</v>
+      <c r="G167" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -21312,11 +21312,11 @@
       <c r="E168">
         <v>240</v>
       </c>
-      <c r="F168" s="5">
+      <c r="F168" s="7">
         <v>920</v>
       </c>
-      <c r="G168" s="6" t="s">
-        <v>30</v>
+      <c r="G168" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
@@ -21335,11 +21335,11 @@
       <c r="E169">
         <v>240</v>
       </c>
-      <c r="F169" s="5">
+      <c r="F169" s="7">
         <v>102</v>
       </c>
-      <c r="G169" s="6" t="s">
-        <v>30</v>
+      <c r="G169" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
@@ -21358,11 +21358,11 @@
       <c r="E170">
         <v>480</v>
       </c>
-      <c r="F170" s="5">
+      <c r="F170" s="7">
         <v>211</v>
       </c>
-      <c r="G170" s="6" t="s">
-        <v>30</v>
+      <c r="G170" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -21381,11 +21381,11 @@
       <c r="E171">
         <v>120</v>
       </c>
-      <c r="F171" s="5">
+      <c r="F171" s="7">
         <v>753</v>
       </c>
-      <c r="G171" s="6" t="s">
-        <v>30</v>
+      <c r="G171" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
@@ -21404,11 +21404,11 @@
       <c r="E172">
         <v>240</v>
       </c>
-      <c r="F172" s="5">
+      <c r="F172" s="7">
         <v>31</v>
       </c>
-      <c r="G172" s="6" t="s">
-        <v>30</v>
+      <c r="G172" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
@@ -21427,11 +21427,11 @@
       <c r="E173">
         <v>240</v>
       </c>
-      <c r="F173" s="5">
+      <c r="F173" s="7">
         <v>93</v>
       </c>
-      <c r="G173" s="6" t="s">
-        <v>30</v>
+      <c r="G173" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
@@ -21450,11 +21450,11 @@
       <c r="E174">
         <v>480</v>
       </c>
-      <c r="F174" s="5">
+      <c r="F174" s="7">
         <v>378</v>
       </c>
-      <c r="G174" s="6" t="s">
-        <v>30</v>
+      <c r="G174" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
@@ -21473,11 +21473,11 @@
       <c r="E175">
         <v>120</v>
       </c>
-      <c r="F175" s="5">
+      <c r="F175" s="7">
         <v>94</v>
       </c>
-      <c r="G175" s="6" t="s">
-        <v>30</v>
+      <c r="G175" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
@@ -21496,11 +21496,11 @@
       <c r="E176">
         <v>120</v>
       </c>
-      <c r="F176" s="5">
+      <c r="F176" s="7">
         <v>103</v>
       </c>
-      <c r="G176" s="6" t="s">
-        <v>30</v>
+      <c r="G176" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -21519,11 +21519,11 @@
       <c r="E177">
         <v>120</v>
       </c>
-      <c r="F177" s="5">
+      <c r="F177" s="7">
         <v>93</v>
       </c>
-      <c r="G177" s="6" t="s">
-        <v>30</v>
+      <c r="G177" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
@@ -21542,11 +21542,11 @@
       <c r="E178">
         <v>12</v>
       </c>
-      <c r="F178" s="5">
+      <c r="F178" s="7">
         <v>68</v>
       </c>
-      <c r="G178" s="6" t="s">
-        <v>30</v>
+      <c r="G178" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
@@ -21565,11 +21565,11 @@
       <c r="E179">
         <v>12</v>
       </c>
-      <c r="F179" s="5">
+      <c r="F179" s="7">
         <v>77</v>
       </c>
-      <c r="G179" s="6" t="s">
-        <v>30</v>
+      <c r="G179" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
@@ -21703,11 +21703,11 @@
       <c r="E185">
         <v>20</v>
       </c>
-      <c r="F185" s="5">
+      <c r="F185" s="7">
         <v>144</v>
       </c>
-      <c r="G185" s="6" t="s">
-        <v>30</v>
+      <c r="G185" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
@@ -21726,11 +21726,11 @@
       <c r="E186">
         <v>20</v>
       </c>
-      <c r="F186" s="5">
+      <c r="F186" s="7">
         <v>40</v>
       </c>
-      <c r="G186" s="6" t="s">
-        <v>30</v>
+      <c r="G186" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
@@ -21749,11 +21749,11 @@
       <c r="E187">
         <v>56</v>
       </c>
-      <c r="F187" s="5">
+      <c r="F187" s="7">
         <v>20</v>
       </c>
-      <c r="G187" s="6" t="s">
-        <v>30</v>
+      <c r="G187" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
@@ -21772,11 +21772,11 @@
       <c r="E188">
         <v>50</v>
       </c>
-      <c r="F188" s="5">
+      <c r="F188" s="7">
         <v>17</v>
       </c>
-      <c r="G188" s="6" t="s">
-        <v>30</v>
+      <c r="G188" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
@@ -21795,11 +21795,11 @@
       <c r="E189">
         <v>50</v>
       </c>
-      <c r="F189" s="5">
+      <c r="F189" s="7">
         <v>380</v>
       </c>
-      <c r="G189" s="6" t="s">
-        <v>30</v>
+      <c r="G189" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
@@ -21933,11 +21933,11 @@
       <c r="E195">
         <v>60</v>
       </c>
-      <c r="F195" s="5">
+      <c r="F195" s="7">
         <v>454</v>
       </c>
-      <c r="G195" s="6" t="s">
-        <v>30</v>
+      <c r="G195" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
@@ -21956,11 +21956,11 @@
       <c r="E196">
         <v>100</v>
       </c>
-      <c r="F196" s="5">
+      <c r="F196" s="7">
         <v>880</v>
       </c>
-      <c r="G196" s="6" t="s">
-        <v>30</v>
+      <c r="G196" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
@@ -22804,11 +22804,11 @@
       <c r="E35">
         <v>120</v>
       </c>
-      <c r="F35" s="5">
+      <c r="F35" s="7">
         <v>568</v>
       </c>
-      <c r="G35" s="6" t="s">
-        <v>30</v>
+      <c r="G35" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -23287,11 +23287,11 @@
       <c r="E56">
         <v>144</v>
       </c>
-      <c r="F56" s="5">
+      <c r="F56" s="7">
         <v>19</v>
       </c>
-      <c r="G56" s="6" t="s">
-        <v>30</v>
+      <c r="G56" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -23609,11 +23609,11 @@
       <c r="E70">
         <v>12</v>
       </c>
-      <c r="F70" s="5">
+      <c r="F70" s="7">
         <v>22</v>
       </c>
-      <c r="G70" s="6" t="s">
-        <v>30</v>
+      <c r="G70" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -23793,11 +23793,11 @@
       <c r="E78">
         <v>144</v>
       </c>
-      <c r="F78" s="5">
+      <c r="F78" s="7">
         <v>936</v>
       </c>
-      <c r="G78" s="6" t="s">
-        <v>30</v>
+      <c r="G78" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -23816,11 +23816,11 @@
       <c r="E79">
         <v>144</v>
       </c>
-      <c r="F79" s="5">
+      <c r="F79" s="7">
         <v>359</v>
       </c>
-      <c r="G79" s="6" t="s">
-        <v>30</v>
+      <c r="G79" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -23862,11 +23862,11 @@
       <c r="E81">
         <v>144</v>
       </c>
-      <c r="F81" s="5">
+      <c r="F81" s="7">
         <v>319</v>
       </c>
-      <c r="G81" s="6" t="s">
-        <v>30</v>
+      <c r="G81" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -24000,11 +24000,11 @@
       <c r="E87">
         <v>144</v>
       </c>
-      <c r="F87" s="5">
+      <c r="F87" s="7">
         <v>808</v>
       </c>
-      <c r="G87" s="6" t="s">
-        <v>30</v>
+      <c r="G87" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -24549,11 +24549,11 @@
       <c r="E14">
         <v>50</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="7">
         <v>471</v>
       </c>
-      <c r="G14" s="6" t="s">
-        <v>30</v>
+      <c r="G14" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -24572,11 +24572,11 @@
       <c r="E15">
         <v>50</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="7">
         <v>445</v>
       </c>
-      <c r="G15" s="6" t="s">
-        <v>30</v>
+      <c r="G15" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -24756,11 +24756,11 @@
       <c r="E23">
         <v>50</v>
       </c>
-      <c r="F23" s="5">
+      <c r="F23" s="7">
         <v>14</v>
       </c>
-      <c r="G23" s="6" t="s">
-        <v>30</v>
+      <c r="G23" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -25331,11 +25331,11 @@
       <c r="E48">
         <v>100</v>
       </c>
-      <c r="F48" s="5">
+      <c r="F48" s="7">
         <v>42</v>
       </c>
-      <c r="G48" s="6" t="s">
-        <v>30</v>
+      <c r="G48" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -25469,11 +25469,11 @@
       <c r="E54">
         <v>100</v>
       </c>
-      <c r="F54" s="5">
+      <c r="F54" s="7">
         <v>751</v>
       </c>
-      <c r="G54" s="6" t="s">
-        <v>30</v>
+      <c r="G54" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -25607,11 +25607,11 @@
       <c r="E60">
         <v>100</v>
       </c>
-      <c r="F60" s="5">
+      <c r="F60" s="7">
         <v>645</v>
       </c>
-      <c r="G60" s="6" t="s">
-        <v>30</v>
+      <c r="G60" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -25699,11 +25699,11 @@
       <c r="E64">
         <v>100</v>
       </c>
-      <c r="F64" s="5">
+      <c r="F64" s="7">
         <v>253</v>
       </c>
-      <c r="G64" s="6" t="s">
-        <v>30</v>
+      <c r="G64" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -25860,11 +25860,11 @@
       <c r="E71">
         <v>100</v>
       </c>
-      <c r="F71" s="5">
+      <c r="F71" s="7">
         <v>100</v>
       </c>
-      <c r="G71" s="6" t="s">
-        <v>30</v>
+      <c r="G71" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -26182,11 +26182,11 @@
       <c r="E85">
         <v>100</v>
       </c>
-      <c r="F85" s="5">
+      <c r="F85" s="7">
         <v>13</v>
       </c>
-      <c r="G85" s="6" t="s">
-        <v>30</v>
+      <c r="G85" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -26343,11 +26343,11 @@
       <c r="E92">
         <v>100</v>
       </c>
-      <c r="F92" s="5">
+      <c r="F92" s="7">
         <v>940</v>
       </c>
-      <c r="G92" s="6" t="s">
-        <v>30</v>
+      <c r="G92" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -26481,11 +26481,11 @@
       <c r="E98">
         <v>120</v>
       </c>
-      <c r="F98" s="5">
+      <c r="F98" s="7">
         <v>26</v>
       </c>
-      <c r="G98" s="6" t="s">
-        <v>30</v>
+      <c r="G98" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -26573,11 +26573,11 @@
       <c r="E102">
         <v>120</v>
       </c>
-      <c r="F102" s="5">
+      <c r="F102" s="7">
         <v>60</v>
       </c>
-      <c r="G102" s="6" t="s">
-        <v>30</v>
+      <c r="G102" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -26596,11 +26596,11 @@
       <c r="E103">
         <v>120</v>
       </c>
-      <c r="F103" s="5">
+      <c r="F103" s="7">
         <v>335</v>
       </c>
-      <c r="G103" s="6" t="s">
-        <v>30</v>
+      <c r="G103" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -26849,11 +26849,11 @@
       <c r="E114">
         <v>24</v>
       </c>
-      <c r="F114" s="5">
+      <c r="F114" s="7">
         <v>137</v>
       </c>
-      <c r="G114" s="6" t="s">
-        <v>30</v>
+      <c r="G114" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
@@ -27148,11 +27148,11 @@
       <c r="E127">
         <v>24</v>
       </c>
-      <c r="F127" s="5">
+      <c r="F127" s="7">
         <v>57</v>
       </c>
-      <c r="G127" s="6" t="s">
-        <v>30</v>
+      <c r="G127" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
@@ -27424,11 +27424,11 @@
       <c r="E139">
         <v>30</v>
       </c>
-      <c r="F139" s="5">
+      <c r="F139" s="7">
         <v>49</v>
       </c>
-      <c r="G139" s="6" t="s">
-        <v>30</v>
+      <c r="G139" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -27447,11 +27447,11 @@
       <c r="E140">
         <v>30</v>
       </c>
-      <c r="F140" s="5">
+      <c r="F140" s="7">
         <v>297</v>
       </c>
-      <c r="G140" s="6" t="s">
-        <v>30</v>
+      <c r="G140" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
@@ -27470,11 +27470,11 @@
       <c r="E141">
         <v>30</v>
       </c>
-      <c r="F141" s="5">
+      <c r="F141" s="7">
         <v>180</v>
       </c>
-      <c r="G141" s="6" t="s">
-        <v>30</v>
+      <c r="G141" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -27861,11 +27861,11 @@
       <c r="E158">
         <v>24</v>
       </c>
-      <c r="F158" s="5">
+      <c r="F158" s="7">
         <v>17</v>
       </c>
-      <c r="G158" s="6" t="s">
-        <v>30</v>
+      <c r="G158" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -27884,11 +27884,11 @@
       <c r="E159">
         <v>24</v>
       </c>
-      <c r="F159" s="5">
+      <c r="F159" s="7">
         <v>130</v>
       </c>
-      <c r="G159" s="6" t="s">
-        <v>30</v>
+      <c r="G159" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -28275,11 +28275,11 @@
       <c r="E176">
         <v>48</v>
       </c>
-      <c r="F176" s="5">
+      <c r="F176" s="7">
         <v>48</v>
       </c>
-      <c r="G176" s="6" t="s">
-        <v>30</v>
+      <c r="G176" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.25">
@@ -28298,11 +28298,11 @@
       <c r="E177">
         <v>48</v>
       </c>
-      <c r="F177" s="5">
+      <c r="F177" s="7">
         <v>193</v>
       </c>
-      <c r="G177" s="6" t="s">
-        <v>30</v>
+      <c r="G177" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.25">
@@ -28344,11 +28344,11 @@
       <c r="E179">
         <v>36</v>
       </c>
-      <c r="F179" s="5">
+      <c r="F179" s="7">
         <v>218</v>
       </c>
-      <c r="G179" s="6" t="s">
-        <v>30</v>
+      <c r="G179" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
@@ -28482,11 +28482,11 @@
       <c r="E185">
         <v>240</v>
       </c>
-      <c r="F185" s="5">
+      <c r="F185" s="7">
         <v>1086</v>
       </c>
-      <c r="G185" s="6" t="s">
-        <v>30</v>
+      <c r="G185" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
@@ -28804,11 +28804,11 @@
       <c r="E199">
         <v>10</v>
       </c>
-      <c r="F199" s="5">
+      <c r="F199" s="7">
         <v>69</v>
       </c>
-      <c r="G199" s="6" t="s">
-        <v>30</v>
+      <c r="G199" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
@@ -28942,11 +28942,11 @@
       <c r="E205">
         <v>280</v>
       </c>
-      <c r="F205" s="5">
+      <c r="F205" s="7">
         <v>745</v>
       </c>
-      <c r="G205" s="6" t="s">
-        <v>30</v>
+      <c r="G205" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
@@ -29011,11 +29011,11 @@
       <c r="E208">
         <v>720</v>
       </c>
-      <c r="F208" s="5">
+      <c r="F208" s="7">
         <v>5462</v>
       </c>
-      <c r="G208" s="6" t="s">
-        <v>30</v>
+      <c r="G208" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
@@ -29034,11 +29034,11 @@
       <c r="E209">
         <v>720</v>
       </c>
-      <c r="F209" s="5">
+      <c r="F209" s="7">
         <v>6036</v>
       </c>
-      <c r="G209" s="6" t="s">
-        <v>30</v>
+      <c r="G209" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
@@ -29080,11 +29080,11 @@
       <c r="E211">
         <v>720</v>
       </c>
-      <c r="F211" s="5">
+      <c r="F211" s="7">
         <v>848</v>
       </c>
-      <c r="G211" s="6" t="s">
-        <v>30</v>
+      <c r="G211" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.25">
@@ -29103,11 +29103,11 @@
       <c r="E212">
         <v>720</v>
       </c>
-      <c r="F212" s="5">
+      <c r="F212" s="7">
         <v>4603</v>
       </c>
-      <c r="G212" s="6" t="s">
-        <v>30</v>
+      <c r="G212" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
@@ -29126,11 +29126,11 @@
       <c r="E213">
         <v>720</v>
       </c>
-      <c r="F213" s="5">
+      <c r="F213" s="7">
         <v>369</v>
       </c>
-      <c r="G213" s="6" t="s">
-        <v>30</v>
+      <c r="G213" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
@@ -29149,11 +29149,11 @@
       <c r="E214">
         <v>720</v>
       </c>
-      <c r="F214" s="5">
+      <c r="F214" s="7">
         <v>3947</v>
       </c>
-      <c r="G214" s="6" t="s">
-        <v>30</v>
+      <c r="G214" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
@@ -30322,11 +30322,11 @@
       <c r="E265">
         <v>5</v>
       </c>
-      <c r="F265" s="5">
+      <c r="F265" s="7">
         <v>27</v>
       </c>
-      <c r="G265" s="6" t="s">
-        <v>30</v>
+      <c r="G265" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.25">
@@ -30345,11 +30345,11 @@
       <c r="E266">
         <v>5</v>
       </c>
-      <c r="F266" s="5">
+      <c r="F266" s="7">
         <v>26</v>
       </c>
-      <c r="G266" s="6" t="s">
-        <v>30</v>
+      <c r="G266" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -30411,11 +30411,11 @@
       <c r="E2">
         <v>1000</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="7">
         <v>3238</v>
       </c>
-      <c r="G2" s="6" t="s">
-        <v>30</v>
+      <c r="G2" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -30457,11 +30457,11 @@
       <c r="E4">
         <v>1000</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="7">
         <v>4021</v>
       </c>
-      <c r="G4" s="6" t="s">
-        <v>30</v>
+      <c r="G4" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -30503,11 +30503,11 @@
       <c r="E6">
         <v>500</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="7">
         <v>207</v>
       </c>
-      <c r="G6" s="6" t="s">
-        <v>30</v>
+      <c r="G6" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -30687,11 +30687,11 @@
       <c r="E14">
         <v>200</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="7">
         <v>1904</v>
       </c>
-      <c r="G14" s="6" t="s">
-        <v>30</v>
+      <c r="G14" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -30710,11 +30710,11 @@
       <c r="E15">
         <v>120</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="7">
         <v>1063</v>
       </c>
-      <c r="G15" s="6" t="s">
-        <v>30</v>
+      <c r="G15" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -31374,11 +31374,11 @@
       <c r="E26">
         <v>24</v>
       </c>
-      <c r="F26" s="5">
+      <c r="F26" s="7">
         <v>202</v>
       </c>
-      <c r="G26" s="6" t="s">
-        <v>30</v>
+      <c r="G26" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -31397,11 +31397,11 @@
       <c r="E27">
         <v>24</v>
       </c>
-      <c r="F27" s="5">
+      <c r="F27" s="7">
         <v>198</v>
       </c>
-      <c r="G27" s="6" t="s">
-        <v>30</v>
+      <c r="G27" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -31647,11 +31647,11 @@
       <c r="E5">
         <v>288</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="7">
         <v>1038</v>
       </c>
-      <c r="G5" s="6" t="s">
-        <v>30</v>
+      <c r="G5" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -32038,11 +32038,11 @@
       <c r="E22">
         <v>192</v>
       </c>
-      <c r="F22" s="5">
+      <c r="F22" s="7">
         <v>1033</v>
       </c>
-      <c r="G22" s="6" t="s">
-        <v>30</v>
+      <c r="G22" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -32176,11 +32176,11 @@
       <c r="E28">
         <v>192</v>
       </c>
-      <c r="F28" s="5">
+      <c r="F28" s="7">
         <v>122</v>
       </c>
-      <c r="G28" s="6" t="s">
-        <v>30</v>
+      <c r="G28" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -32291,11 +32291,11 @@
       <c r="E33">
         <v>144</v>
       </c>
-      <c r="F33" s="5">
+      <c r="F33" s="7">
         <v>1001</v>
       </c>
-      <c r="G33" s="6" t="s">
-        <v>30</v>
+      <c r="G33" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -32337,11 +32337,11 @@
       <c r="E35">
         <v>144</v>
       </c>
-      <c r="F35" s="5">
+      <c r="F35" s="7">
         <v>258</v>
       </c>
-      <c r="G35" s="6" t="s">
-        <v>30</v>
+      <c r="G35" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -32360,11 +32360,11 @@
       <c r="E36">
         <v>72</v>
       </c>
-      <c r="F36" s="5">
+      <c r="F36" s="7">
         <v>42</v>
       </c>
-      <c r="G36" s="6" t="s">
-        <v>30</v>
+      <c r="G36" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -32383,11 +32383,11 @@
       <c r="E37">
         <v>144</v>
       </c>
-      <c r="F37" s="5">
+      <c r="F37" s="7">
         <v>344</v>
       </c>
-      <c r="G37" s="6" t="s">
-        <v>30</v>
+      <c r="G37" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -32406,11 +32406,11 @@
       <c r="E38">
         <v>72</v>
       </c>
-      <c r="F38" s="5">
+      <c r="F38" s="7">
         <v>235</v>
       </c>
-      <c r="G38" s="6" t="s">
-        <v>30</v>
+      <c r="G38" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -32429,11 +32429,11 @@
       <c r="E39">
         <v>144</v>
       </c>
-      <c r="F39" s="5">
+      <c r="F39" s="7">
         <v>1014</v>
       </c>
-      <c r="G39" s="6" t="s">
-        <v>30</v>
+      <c r="G39" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -32452,11 +32452,11 @@
       <c r="E40">
         <v>72</v>
       </c>
-      <c r="F40" s="5">
+      <c r="F40" s="7">
         <v>120</v>
       </c>
-      <c r="G40" s="6" t="s">
-        <v>30</v>
+      <c r="G40" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -32475,11 +32475,11 @@
       <c r="E41">
         <v>144</v>
       </c>
-      <c r="F41" s="5">
+      <c r="F41" s="7">
         <v>454</v>
       </c>
-      <c r="G41" s="6" t="s">
-        <v>30</v>
+      <c r="G41" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -32498,11 +32498,11 @@
       <c r="E42">
         <v>72</v>
       </c>
-      <c r="F42" s="5">
+      <c r="F42" s="7">
         <v>60</v>
       </c>
-      <c r="G42" s="6" t="s">
-        <v>30</v>
+      <c r="G42" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -32521,11 +32521,11 @@
       <c r="E43">
         <v>144</v>
       </c>
-      <c r="F43" s="5">
+      <c r="F43" s="7">
         <v>400</v>
       </c>
-      <c r="G43" s="6" t="s">
-        <v>30</v>
+      <c r="G43" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -32567,11 +32567,11 @@
       <c r="E45">
         <v>144</v>
       </c>
-      <c r="F45" s="5">
+      <c r="F45" s="7">
         <v>273</v>
       </c>
-      <c r="G45" s="6" t="s">
-        <v>30</v>
+      <c r="G45" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -32613,11 +32613,11 @@
       <c r="E47">
         <v>144</v>
       </c>
-      <c r="F47" s="5">
+      <c r="F47" s="7">
         <v>1400</v>
       </c>
-      <c r="G47" s="6" t="s">
-        <v>30</v>
+      <c r="G47" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -33096,11 +33096,11 @@
       <c r="E68">
         <v>200</v>
       </c>
-      <c r="F68" s="5">
+      <c r="F68" s="7">
         <v>44</v>
       </c>
-      <c r="G68" s="6" t="s">
-        <v>30</v>
+      <c r="G68" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -33165,11 +33165,11 @@
       <c r="E71">
         <v>200</v>
       </c>
-      <c r="F71" s="5">
+      <c r="F71" s="7">
         <v>1246</v>
       </c>
-      <c r="G71" s="6" t="s">
-        <v>30</v>
+      <c r="G71" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -33234,11 +33234,11 @@
       <c r="E74">
         <v>200</v>
       </c>
-      <c r="F74" s="5">
+      <c r="F74" s="7">
         <v>932</v>
       </c>
-      <c r="G74" s="6" t="s">
-        <v>30</v>
+      <c r="G74" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -33349,11 +33349,11 @@
       <c r="E79">
         <v>200</v>
       </c>
-      <c r="F79" s="5">
+      <c r="F79" s="7">
         <v>1865</v>
       </c>
-      <c r="G79" s="6" t="s">
-        <v>30</v>
+      <c r="G79" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -33441,11 +33441,11 @@
       <c r="E83">
         <v>1152</v>
       </c>
-      <c r="F83" s="5">
+      <c r="F83" s="7">
         <v>227</v>
       </c>
-      <c r="G83" s="6" t="s">
-        <v>30</v>
+      <c r="G83" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -33487,11 +33487,11 @@
       <c r="E85">
         <v>1152</v>
       </c>
-      <c r="F85" s="5">
+      <c r="F85" s="7">
         <v>3385</v>
       </c>
-      <c r="G85" s="6" t="s">
-        <v>30</v>
+      <c r="G85" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -33533,11 +33533,11 @@
       <c r="E87">
         <v>576</v>
       </c>
-      <c r="F87" s="5">
+      <c r="F87" s="7">
         <v>4143</v>
       </c>
-      <c r="G87" s="6" t="s">
-        <v>30</v>
+      <c r="G87" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -33556,11 +33556,11 @@
       <c r="E88">
         <v>576</v>
       </c>
-      <c r="F88" s="5">
+      <c r="F88" s="7">
         <v>5653</v>
       </c>
-      <c r="G88" s="6" t="s">
-        <v>30</v>
+      <c r="G88" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -33579,11 +33579,11 @@
       <c r="E89">
         <v>576</v>
       </c>
-      <c r="F89" s="5">
+      <c r="F89" s="7">
         <v>207</v>
       </c>
-      <c r="G89" s="6" t="s">
-        <v>30</v>
+      <c r="G89" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -33602,11 +33602,11 @@
       <c r="E90">
         <v>576</v>
       </c>
-      <c r="F90" s="5">
+      <c r="F90" s="7">
         <v>1132</v>
       </c>
-      <c r="G90" s="6" t="s">
-        <v>30</v>
+      <c r="G90" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -33648,11 +33648,11 @@
       <c r="E92">
         <v>576</v>
       </c>
-      <c r="F92" s="5">
+      <c r="F92" s="7">
         <v>5395</v>
       </c>
-      <c r="G92" s="6" t="s">
-        <v>30</v>
+      <c r="G92" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -33786,11 +33786,11 @@
       <c r="E98">
         <v>144</v>
       </c>
-      <c r="F98" s="5">
+      <c r="F98" s="7">
         <v>233</v>
       </c>
-      <c r="G98" s="6" t="s">
-        <v>30</v>
+      <c r="G98" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -34062,11 +34062,11 @@
       <c r="E110">
         <v>192</v>
       </c>
-      <c r="F110" s="5">
+      <c r="F110" s="7">
         <v>1359</v>
       </c>
-      <c r="G110" s="6" t="s">
-        <v>30</v>
+      <c r="G110" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -34223,11 +34223,11 @@
       <c r="E117">
         <v>192</v>
       </c>
-      <c r="F117" s="5">
+      <c r="F117" s="7">
         <v>65</v>
       </c>
-      <c r="G117" s="6" t="s">
-        <v>30</v>
+      <c r="G117" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
@@ -34292,11 +34292,11 @@
       <c r="E120">
         <v>192</v>
       </c>
-      <c r="F120" s="5">
+      <c r="F120" s="7">
         <v>788</v>
       </c>
-      <c r="G120" s="6" t="s">
-        <v>30</v>
+      <c r="G120" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -34315,11 +34315,11 @@
       <c r="E121">
         <v>192</v>
       </c>
-      <c r="F121" s="5">
+      <c r="F121" s="7">
         <v>137</v>
       </c>
-      <c r="G121" s="6" t="s">
-        <v>30</v>
+      <c r="G121" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.25">
@@ -34545,11 +34545,11 @@
       <c r="E131">
         <v>192</v>
       </c>
-      <c r="F131" s="5">
+      <c r="F131" s="7">
         <v>287</v>
       </c>
-      <c r="G131" s="6" t="s">
-        <v>30</v>
+      <c r="G131" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
@@ -34591,11 +34591,11 @@
       <c r="E133">
         <v>192</v>
       </c>
-      <c r="F133" s="5">
+      <c r="F133" s="7">
         <v>185</v>
       </c>
-      <c r="G133" s="6" t="s">
-        <v>30</v>
+      <c r="G133" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -34683,11 +34683,11 @@
       <c r="E137">
         <v>192</v>
       </c>
-      <c r="F137" s="5">
+      <c r="F137" s="7">
         <v>108</v>
       </c>
-      <c r="G137" s="6" t="s">
-        <v>30</v>
+      <c r="G137" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -34706,11 +34706,11 @@
       <c r="E138">
         <v>192</v>
       </c>
-      <c r="F138" s="5">
+      <c r="F138" s="7">
         <v>99</v>
       </c>
-      <c r="G138" s="6" t="s">
-        <v>30</v>
+      <c r="G138" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
@@ -34729,11 +34729,11 @@
       <c r="E139">
         <v>192</v>
       </c>
-      <c r="F139" s="5">
+      <c r="F139" s="7">
         <v>125</v>
       </c>
-      <c r="G139" s="6" t="s">
-        <v>30</v>
+      <c r="G139" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -34752,11 +34752,11 @@
       <c r="E140">
         <v>192</v>
       </c>
-      <c r="F140" s="5">
+      <c r="F140" s="7">
         <v>17</v>
       </c>
-      <c r="G140" s="6" t="s">
-        <v>30</v>
+      <c r="G140" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
@@ -34775,11 +34775,11 @@
       <c r="E141">
         <v>192</v>
       </c>
-      <c r="F141" s="5">
+      <c r="F141" s="7">
         <v>114</v>
       </c>
-      <c r="G141" s="6" t="s">
-        <v>30</v>
+      <c r="G141" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -34798,11 +34798,11 @@
       <c r="E142">
         <v>192</v>
       </c>
-      <c r="F142" s="5">
+      <c r="F142" s="7">
         <v>126</v>
       </c>
-      <c r="G142" s="6" t="s">
-        <v>30</v>
+      <c r="G142" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
@@ -34821,11 +34821,11 @@
       <c r="E143">
         <v>192</v>
       </c>
-      <c r="F143" s="5">
+      <c r="F143" s="7">
         <v>42</v>
       </c>
-      <c r="G143" s="6" t="s">
-        <v>30</v>
+      <c r="G143" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -34844,11 +34844,11 @@
       <c r="E144">
         <v>192</v>
       </c>
-      <c r="F144" s="5">
+      <c r="F144" s="7">
         <v>58</v>
       </c>
-      <c r="G144" s="6" t="s">
-        <v>30</v>
+      <c r="G144" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -32,7 +32,7 @@
     <t>Actualización:</t>
   </si>
   <si>
-    <t>7/3/2026, 3:41:51 p. m.</t>
+    <t>7/3/2026, 9:22:22 p. m.</t>
   </si>
   <si>
     <t>ACCESORIOS</t>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -32,7 +32,7 @@
     <t>Actualización:</t>
   </si>
   <si>
-    <t>7/3/2026, 9:52:17 p. m.</t>
+    <t>7/3/2026, 5:07:04 p. m.</t>
   </si>
   <si>
     <t>ACCESORIOS</t>
@@ -9885,7 +9885,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>893378</v>
+        <v>1770394</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -9917,7 +9917,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>867812</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -9925,7 +9925,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>436973</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -9933,7 +9933,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>4974</v>
+        <v>9093</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -9941,7 +9941,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>264367</v>
+        <v>261169</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -9957,7 +9957,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>478191</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -10173,7 +10173,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="5">
-        <v>13274</v>
+        <v>10076</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>30</v>
@@ -11293,11 +11293,11 @@
       <c r="E2">
         <v>18</v>
       </c>
-      <c r="F2" s="3">
-        <v>0</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>26</v>
+      <c r="F2" s="5">
+        <v>243</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -11316,11 +11316,11 @@
       <c r="E3">
         <v>24</v>
       </c>
-      <c r="F3" s="3">
-        <v>0</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>26</v>
+      <c r="F3" s="5">
+        <v>2050</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -11339,11 +11339,11 @@
       <c r="E4">
         <v>24</v>
       </c>
-      <c r="F4" s="3">
-        <v>0</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>26</v>
+      <c r="F4" s="7">
+        <v>15</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -11362,11 +11362,11 @@
       <c r="E5">
         <v>24</v>
       </c>
-      <c r="F5" s="3">
-        <v>0</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>26</v>
+      <c r="F5" s="5">
+        <v>3800</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -11385,11 +11385,11 @@
       <c r="E6">
         <v>24</v>
       </c>
-      <c r="F6" s="3">
-        <v>0</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>26</v>
+      <c r="F6" s="5">
+        <v>606</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -11431,11 +11431,11 @@
       <c r="E8">
         <v>24</v>
       </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>26</v>
+      <c r="F8" s="5">
+        <v>4742</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -11454,11 +11454,11 @@
       <c r="E9">
         <v>24</v>
       </c>
-      <c r="F9" s="3">
-        <v>0</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>26</v>
+      <c r="F9" s="5">
+        <v>1463</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -11477,11 +11477,11 @@
       <c r="E10">
         <v>24</v>
       </c>
-      <c r="F10" s="3">
-        <v>0</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>26</v>
+      <c r="F10" s="5">
+        <v>1496</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -11500,11 +11500,11 @@
       <c r="E11">
         <v>24</v>
       </c>
-      <c r="F11" s="3">
-        <v>0</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>26</v>
+      <c r="F11" s="7">
+        <v>180</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -11523,11 +11523,11 @@
       <c r="E12">
         <v>24</v>
       </c>
-      <c r="F12" s="3">
-        <v>0</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>26</v>
+      <c r="F12" s="5">
+        <v>1426</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -11546,11 +11546,11 @@
       <c r="E13">
         <v>24</v>
       </c>
-      <c r="F13" s="3">
-        <v>0</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>26</v>
+      <c r="F13" s="7">
+        <v>168</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -11569,11 +11569,11 @@
       <c r="E14">
         <v>36</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>26</v>
+      <c r="F14" s="7">
+        <v>182</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -11592,11 +11592,11 @@
       <c r="E15">
         <v>36</v>
       </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>26</v>
+      <c r="F15" s="7">
+        <v>1</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -11615,11 +11615,11 @@
       <c r="E16">
         <v>36</v>
       </c>
-      <c r="F16" s="3">
-        <v>0</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>26</v>
+      <c r="F16" s="5">
+        <v>1012</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -11638,11 +11638,11 @@
       <c r="E17">
         <v>24</v>
       </c>
-      <c r="F17" s="3">
-        <v>0</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>26</v>
+      <c r="F17" s="7">
+        <v>76</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -11684,11 +11684,11 @@
       <c r="E19">
         <v>36</v>
       </c>
-      <c r="F19" s="3">
-        <v>0</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>26</v>
+      <c r="F19" s="5">
+        <v>3828</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -11707,11 +11707,11 @@
       <c r="E20">
         <v>36</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>26</v>
+      <c r="F20" s="5">
+        <v>3206</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -11730,11 +11730,11 @@
       <c r="E21">
         <v>36</v>
       </c>
-      <c r="F21" s="3">
-        <v>0</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>26</v>
+      <c r="F21" s="5">
+        <v>8229</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -11753,11 +11753,11 @@
       <c r="E22">
         <v>36</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>26</v>
+      <c r="F22" s="5">
+        <v>1330</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -11845,11 +11845,11 @@
       <c r="E26">
         <v>48</v>
       </c>
-      <c r="F26" s="3">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>26</v>
+      <c r="F26" s="7">
+        <v>1</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -11891,11 +11891,11 @@
       <c r="E28">
         <v>36</v>
       </c>
-      <c r="F28" s="3">
-        <v>0</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>26</v>
+      <c r="F28" s="7">
+        <v>1</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -11914,11 +11914,11 @@
       <c r="E29">
         <v>50</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>26</v>
+      <c r="F29" s="5">
+        <v>3043</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -11983,11 +11983,11 @@
       <c r="E32">
         <v>50</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>26</v>
+      <c r="F32" s="5">
+        <v>3505</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -12006,11 +12006,11 @@
       <c r="E33">
         <v>50</v>
       </c>
-      <c r="F33" s="3">
-        <v>0</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>26</v>
+      <c r="F33" s="5">
+        <v>2922</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -12029,11 +12029,11 @@
       <c r="E34">
         <v>50</v>
       </c>
-      <c r="F34" s="3">
-        <v>0</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>26</v>
+      <c r="F34" s="7">
+        <v>263</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -12052,11 +12052,11 @@
       <c r="E35">
         <v>50</v>
       </c>
-      <c r="F35" s="3">
-        <v>0</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>26</v>
+      <c r="F35" s="5">
+        <v>518</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -12075,11 +12075,11 @@
       <c r="E36">
         <v>50</v>
       </c>
-      <c r="F36" s="3">
-        <v>0</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>26</v>
+      <c r="F36" s="5">
+        <v>873</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -12098,11 +12098,11 @@
       <c r="E37">
         <v>48</v>
       </c>
-      <c r="F37" s="3">
-        <v>0</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>26</v>
+      <c r="F37" s="5">
+        <v>7641</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -12121,11 +12121,11 @@
       <c r="E38">
         <v>48</v>
       </c>
-      <c r="F38" s="3">
-        <v>0</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>26</v>
+      <c r="F38" s="5">
+        <v>1483</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -12190,11 +12190,11 @@
       <c r="E41">
         <v>48</v>
       </c>
-      <c r="F41" s="3">
-        <v>0</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>26</v>
+      <c r="F41" s="7">
+        <v>5</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -12213,11 +12213,11 @@
       <c r="E42">
         <v>48</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
-      <c r="G42" s="4" t="s">
-        <v>26</v>
+      <c r="F42" s="7">
+        <v>39</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -12259,11 +12259,11 @@
       <c r="E44">
         <v>48</v>
       </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>26</v>
+      <c r="F44" s="5">
+        <v>6524</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -12328,11 +12328,11 @@
       <c r="E47">
         <v>48</v>
       </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="4" t="s">
-        <v>26</v>
+      <c r="F47" s="5">
+        <v>11965</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -12374,11 +12374,11 @@
       <c r="E49">
         <v>48</v>
       </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
-      <c r="G49" s="4" t="s">
-        <v>26</v>
+      <c r="F49" s="7">
+        <v>6</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -12397,11 +12397,11 @@
       <c r="E50">
         <v>48</v>
       </c>
-      <c r="F50" s="3">
-        <v>0</v>
-      </c>
-      <c r="G50" s="4" t="s">
-        <v>26</v>
+      <c r="F50" s="5">
+        <v>5578</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -12443,11 +12443,11 @@
       <c r="E52">
         <v>48</v>
       </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="4" t="s">
-        <v>26</v>
+      <c r="F52" s="7">
+        <v>117</v>
+      </c>
+      <c r="G52" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -12466,11 +12466,11 @@
       <c r="E53">
         <v>48</v>
       </c>
-      <c r="F53" s="3">
-        <v>0</v>
-      </c>
-      <c r="G53" s="4" t="s">
-        <v>26</v>
+      <c r="F53" s="7">
+        <v>1</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -12489,11 +12489,11 @@
       <c r="E54">
         <v>48</v>
       </c>
-      <c r="F54" s="3">
-        <v>0</v>
-      </c>
-      <c r="G54" s="4" t="s">
-        <v>26</v>
+      <c r="F54" s="7">
+        <v>162</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -12512,11 +12512,11 @@
       <c r="E55">
         <v>36</v>
       </c>
-      <c r="F55" s="3">
-        <v>0</v>
-      </c>
-      <c r="G55" s="4" t="s">
-        <v>26</v>
+      <c r="F55" s="5">
+        <v>1955</v>
+      </c>
+      <c r="G55" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -12535,11 +12535,11 @@
       <c r="E56">
         <v>36</v>
       </c>
-      <c r="F56" s="3">
-        <v>0</v>
-      </c>
-      <c r="G56" s="4" t="s">
-        <v>26</v>
+      <c r="F56" s="7">
+        <v>196</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -12558,11 +12558,11 @@
       <c r="E57">
         <v>36</v>
       </c>
-      <c r="F57" s="3">
-        <v>0</v>
-      </c>
-      <c r="G57" s="4" t="s">
-        <v>26</v>
+      <c r="F57" s="5">
+        <v>2190</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -12627,11 +12627,11 @@
       <c r="E60">
         <v>36</v>
       </c>
-      <c r="F60" s="3">
-        <v>0</v>
-      </c>
-      <c r="G60" s="4" t="s">
-        <v>26</v>
+      <c r="F60" s="5">
+        <v>1377</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -12673,11 +12673,11 @@
       <c r="E62">
         <v>36</v>
       </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="4" t="s">
-        <v>26</v>
+      <c r="F62" s="5">
+        <v>915</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -12696,11 +12696,11 @@
       <c r="E63">
         <v>36</v>
       </c>
-      <c r="F63" s="3">
-        <v>0</v>
-      </c>
-      <c r="G63" s="4" t="s">
-        <v>26</v>
+      <c r="F63" s="5">
+        <v>798</v>
+      </c>
+      <c r="G63" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -12719,11 +12719,11 @@
       <c r="E64">
         <v>48</v>
       </c>
-      <c r="F64" s="3">
-        <v>0</v>
-      </c>
-      <c r="G64" s="4" t="s">
-        <v>26</v>
+      <c r="F64" s="7">
+        <v>418</v>
+      </c>
+      <c r="G64" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -12742,11 +12742,11 @@
       <c r="E65">
         <v>48</v>
       </c>
-      <c r="F65" s="3">
-        <v>0</v>
-      </c>
-      <c r="G65" s="4" t="s">
-        <v>26</v>
+      <c r="F65" s="5">
+        <v>1218</v>
+      </c>
+      <c r="G65" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -12765,11 +12765,11 @@
       <c r="E66">
         <v>60</v>
       </c>
-      <c r="F66" s="3">
-        <v>0</v>
-      </c>
-      <c r="G66" s="4" t="s">
-        <v>26</v>
+      <c r="F66" s="5">
+        <v>5188</v>
+      </c>
+      <c r="G66" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -12788,11 +12788,11 @@
       <c r="E67">
         <v>60</v>
       </c>
-      <c r="F67" s="3">
-        <v>0</v>
-      </c>
-      <c r="G67" s="4" t="s">
-        <v>26</v>
+      <c r="F67" s="5">
+        <v>1226</v>
+      </c>
+      <c r="G67" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -12811,11 +12811,11 @@
       <c r="E68">
         <v>60</v>
       </c>
-      <c r="F68" s="3">
-        <v>0</v>
-      </c>
-      <c r="G68" s="4" t="s">
-        <v>26</v>
+      <c r="F68" s="5">
+        <v>2119</v>
+      </c>
+      <c r="G68" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -12834,11 +12834,11 @@
       <c r="E69">
         <v>60</v>
       </c>
-      <c r="F69" s="3">
-        <v>0</v>
-      </c>
-      <c r="G69" s="4" t="s">
-        <v>26</v>
+      <c r="F69" s="5">
+        <v>1118</v>
+      </c>
+      <c r="G69" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -12857,11 +12857,11 @@
       <c r="E70">
         <v>60</v>
       </c>
-      <c r="F70" s="3">
-        <v>0</v>
-      </c>
-      <c r="G70" s="4" t="s">
-        <v>26</v>
+      <c r="F70" s="5">
+        <v>4180</v>
+      </c>
+      <c r="G70" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -12880,11 +12880,11 @@
       <c r="E71">
         <v>60</v>
       </c>
-      <c r="F71" s="3">
-        <v>0</v>
-      </c>
-      <c r="G71" s="4" t="s">
-        <v>26</v>
+      <c r="F71" s="5">
+        <v>5085</v>
+      </c>
+      <c r="G71" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -12926,11 +12926,11 @@
       <c r="E73">
         <v>60</v>
       </c>
-      <c r="F73" s="3">
-        <v>0</v>
-      </c>
-      <c r="G73" s="4" t="s">
-        <v>26</v>
+      <c r="F73" s="5">
+        <v>3198</v>
+      </c>
+      <c r="G73" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -12949,11 +12949,11 @@
       <c r="E74">
         <v>60</v>
       </c>
-      <c r="F74" s="3">
-        <v>0</v>
-      </c>
-      <c r="G74" s="4" t="s">
-        <v>26</v>
+      <c r="F74" s="5">
+        <v>1302</v>
+      </c>
+      <c r="G74" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
@@ -12972,11 +12972,11 @@
       <c r="E75">
         <v>60</v>
       </c>
-      <c r="F75" s="3">
-        <v>0</v>
-      </c>
-      <c r="G75" s="4" t="s">
-        <v>26</v>
+      <c r="F75" s="5">
+        <v>4399</v>
+      </c>
+      <c r="G75" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -12995,11 +12995,11 @@
       <c r="E76">
         <v>60</v>
       </c>
-      <c r="F76" s="3">
-        <v>0</v>
-      </c>
-      <c r="G76" s="4" t="s">
-        <v>26</v>
+      <c r="F76" s="5">
+        <v>8596</v>
+      </c>
+      <c r="G76" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
@@ -13018,11 +13018,11 @@
       <c r="E77">
         <v>60</v>
       </c>
-      <c r="F77" s="3">
-        <v>0</v>
-      </c>
-      <c r="G77" s="4" t="s">
-        <v>26</v>
+      <c r="F77" s="5">
+        <v>3977</v>
+      </c>
+      <c r="G77" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.25">
@@ -13041,11 +13041,11 @@
       <c r="E78">
         <v>60</v>
       </c>
-      <c r="F78" s="3">
-        <v>0</v>
-      </c>
-      <c r="G78" s="4" t="s">
-        <v>26</v>
+      <c r="F78" s="5">
+        <v>6465</v>
+      </c>
+      <c r="G78" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -13064,11 +13064,11 @@
       <c r="E79">
         <v>60</v>
       </c>
-      <c r="F79" s="3">
-        <v>0</v>
-      </c>
-      <c r="G79" s="4" t="s">
-        <v>26</v>
+      <c r="F79" s="5">
+        <v>5202</v>
+      </c>
+      <c r="G79" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -13087,11 +13087,11 @@
       <c r="E80">
         <v>60</v>
       </c>
-      <c r="F80" s="3">
-        <v>0</v>
-      </c>
-      <c r="G80" s="4" t="s">
-        <v>26</v>
+      <c r="F80" s="7">
+        <v>18</v>
+      </c>
+      <c r="G80" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.25">
@@ -13110,11 +13110,11 @@
       <c r="E81">
         <v>60</v>
       </c>
-      <c r="F81" s="3">
-        <v>0</v>
-      </c>
-      <c r="G81" s="4" t="s">
-        <v>26</v>
+      <c r="F81" s="7">
+        <v>5</v>
+      </c>
+      <c r="G81" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.25">
@@ -13133,11 +13133,11 @@
       <c r="E82">
         <v>60</v>
       </c>
-      <c r="F82" s="3">
-        <v>0</v>
-      </c>
-      <c r="G82" s="4" t="s">
-        <v>26</v>
+      <c r="F82" s="5">
+        <v>1124</v>
+      </c>
+      <c r="G82" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.25">
@@ -13156,11 +13156,11 @@
       <c r="E83">
         <v>60</v>
       </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="4" t="s">
-        <v>26</v>
+      <c r="F83" s="5">
+        <v>1037</v>
+      </c>
+      <c r="G83" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.25">
@@ -13202,11 +13202,11 @@
       <c r="E85">
         <v>60</v>
       </c>
-      <c r="F85" s="3">
-        <v>0</v>
-      </c>
-      <c r="G85" s="4" t="s">
-        <v>26</v>
+      <c r="F85" s="7">
+        <v>154</v>
+      </c>
+      <c r="G85" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
@@ -13225,11 +13225,11 @@
       <c r="E86">
         <v>60</v>
       </c>
-      <c r="F86" s="3">
-        <v>0</v>
-      </c>
-      <c r="G86" s="4" t="s">
-        <v>26</v>
+      <c r="F86" s="7">
+        <v>333</v>
+      </c>
+      <c r="G86" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
@@ -13248,11 +13248,11 @@
       <c r="E87">
         <v>60</v>
       </c>
-      <c r="F87" s="3">
-        <v>0</v>
-      </c>
-      <c r="G87" s="4" t="s">
-        <v>26</v>
+      <c r="F87" s="5">
+        <v>1531</v>
+      </c>
+      <c r="G87" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -13317,11 +13317,11 @@
       <c r="E90">
         <v>60</v>
       </c>
-      <c r="F90" s="3">
-        <v>0</v>
-      </c>
-      <c r="G90" s="4" t="s">
-        <v>26</v>
+      <c r="F90" s="5">
+        <v>734</v>
+      </c>
+      <c r="G90" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -13340,11 +13340,11 @@
       <c r="E91">
         <v>60</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="4" t="s">
-        <v>26</v>
+      <c r="F91" s="5">
+        <v>1518</v>
+      </c>
+      <c r="G91" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -13363,11 +13363,11 @@
       <c r="E92">
         <v>60</v>
       </c>
-      <c r="F92" s="3">
-        <v>0</v>
-      </c>
-      <c r="G92" s="4" t="s">
-        <v>26</v>
+      <c r="F92" s="5">
+        <v>1372</v>
+      </c>
+      <c r="G92" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -13386,11 +13386,11 @@
       <c r="E93">
         <v>60</v>
       </c>
-      <c r="F93" s="3">
-        <v>0</v>
-      </c>
-      <c r="G93" s="4" t="s">
-        <v>26</v>
+      <c r="F93" s="5">
+        <v>1251</v>
+      </c>
+      <c r="G93" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
@@ -13409,11 +13409,11 @@
       <c r="E94">
         <v>60</v>
       </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="4" t="s">
-        <v>26</v>
+      <c r="F94" s="5">
+        <v>1399</v>
+      </c>
+      <c r="G94" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
@@ -13455,11 +13455,11 @@
       <c r="E96">
         <v>60</v>
       </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="4" t="s">
-        <v>26</v>
+      <c r="F96" s="5">
+        <v>2485</v>
+      </c>
+      <c r="G96" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.25">
@@ -13478,11 +13478,11 @@
       <c r="E97">
         <v>60</v>
       </c>
-      <c r="F97" s="3">
-        <v>0</v>
-      </c>
-      <c r="G97" s="4" t="s">
-        <v>26</v>
+      <c r="F97" s="5">
+        <v>5025</v>
+      </c>
+      <c r="G97" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.25">
@@ -13501,11 +13501,11 @@
       <c r="E98">
         <v>60</v>
       </c>
-      <c r="F98" s="3">
-        <v>0</v>
-      </c>
-      <c r="G98" s="4" t="s">
-        <v>26</v>
+      <c r="F98" s="5">
+        <v>3434</v>
+      </c>
+      <c r="G98" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -13524,11 +13524,11 @@
       <c r="E99">
         <v>60</v>
       </c>
-      <c r="F99" s="3">
-        <v>0</v>
-      </c>
-      <c r="G99" s="4" t="s">
-        <v>26</v>
+      <c r="F99" s="5">
+        <v>3915</v>
+      </c>
+      <c r="G99" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -13547,11 +13547,11 @@
       <c r="E100">
         <v>60</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="4" t="s">
-        <v>26</v>
+      <c r="F100" s="5">
+        <v>1544</v>
+      </c>
+      <c r="G100" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -13570,11 +13570,11 @@
       <c r="E101">
         <v>60</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="4" t="s">
-        <v>26</v>
+      <c r="F101" s="5">
+        <v>5802</v>
+      </c>
+      <c r="G101" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.25">
@@ -13593,11 +13593,11 @@
       <c r="E102">
         <v>60</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="4" t="s">
-        <v>26</v>
+      <c r="F102" s="5">
+        <v>3253</v>
+      </c>
+      <c r="G102" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.25">
@@ -13616,11 +13616,11 @@
       <c r="E103">
         <v>60</v>
       </c>
-      <c r="F103" s="3">
-        <v>0</v>
-      </c>
-      <c r="G103" s="4" t="s">
-        <v>26</v>
+      <c r="F103" s="5">
+        <v>1816</v>
+      </c>
+      <c r="G103" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.25">
@@ -13639,11 +13639,11 @@
       <c r="E104">
         <v>60</v>
       </c>
-      <c r="F104" s="3">
-        <v>0</v>
-      </c>
-      <c r="G104" s="4" t="s">
-        <v>26</v>
+      <c r="F104" s="7">
+        <v>368</v>
+      </c>
+      <c r="G104" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.25">
@@ -13685,11 +13685,11 @@
       <c r="E106">
         <v>60</v>
       </c>
-      <c r="F106" s="3">
-        <v>0</v>
-      </c>
-      <c r="G106" s="4" t="s">
-        <v>26</v>
+      <c r="F106" s="5">
+        <v>852</v>
+      </c>
+      <c r="G106" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.25">
@@ -13708,11 +13708,11 @@
       <c r="E107">
         <v>60</v>
       </c>
-      <c r="F107" s="3">
-        <v>0</v>
-      </c>
-      <c r="G107" s="4" t="s">
-        <v>26</v>
+      <c r="F107" s="5">
+        <v>5594</v>
+      </c>
+      <c r="G107" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.25">
@@ -13731,11 +13731,11 @@
       <c r="E108">
         <v>60</v>
       </c>
-      <c r="F108" s="3">
-        <v>0</v>
-      </c>
-      <c r="G108" s="4" t="s">
-        <v>26</v>
+      <c r="F108" s="5">
+        <v>1998</v>
+      </c>
+      <c r="G108" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
@@ -13754,11 +13754,11 @@
       <c r="E109">
         <v>60</v>
       </c>
-      <c r="F109" s="3">
-        <v>0</v>
-      </c>
-      <c r="G109" s="4" t="s">
-        <v>26</v>
+      <c r="F109" s="5">
+        <v>1725</v>
+      </c>
+      <c r="G109" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
@@ -13777,11 +13777,11 @@
       <c r="E110">
         <v>60</v>
       </c>
-      <c r="F110" s="3">
-        <v>0</v>
-      </c>
-      <c r="G110" s="4" t="s">
-        <v>26</v>
+      <c r="F110" s="5">
+        <v>1887</v>
+      </c>
+      <c r="G110" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -13800,11 +13800,11 @@
       <c r="E111">
         <v>60</v>
       </c>
-      <c r="F111" s="3">
-        <v>0</v>
-      </c>
-      <c r="G111" s="4" t="s">
-        <v>26</v>
+      <c r="F111" s="5">
+        <v>6130</v>
+      </c>
+      <c r="G111" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.25">
@@ -13823,11 +13823,11 @@
       <c r="E112">
         <v>60</v>
       </c>
-      <c r="F112" s="3">
-        <v>0</v>
-      </c>
-      <c r="G112" s="4" t="s">
-        <v>26</v>
+      <c r="F112" s="5">
+        <v>7112</v>
+      </c>
+      <c r="G112" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.25">
@@ -13846,11 +13846,11 @@
       <c r="E113">
         <v>60</v>
       </c>
-      <c r="F113" s="3">
-        <v>0</v>
-      </c>
-      <c r="G113" s="4" t="s">
-        <v>26</v>
+      <c r="F113" s="5">
+        <v>6610</v>
+      </c>
+      <c r="G113" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
@@ -13869,11 +13869,11 @@
       <c r="E114">
         <v>60</v>
       </c>
-      <c r="F114" s="3">
-        <v>0</v>
-      </c>
-      <c r="G114" s="4" t="s">
-        <v>26</v>
+      <c r="F114" s="5">
+        <v>11151</v>
+      </c>
+      <c r="G114" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
@@ -13892,11 +13892,11 @@
       <c r="E115">
         <v>1</v>
       </c>
-      <c r="F115" s="3">
-        <v>0</v>
-      </c>
-      <c r="G115" s="4" t="s">
-        <v>26</v>
+      <c r="F115" s="5">
+        <v>239</v>
+      </c>
+      <c r="G115" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.25">
@@ -13915,11 +13915,11 @@
       <c r="E116">
         <v>1</v>
       </c>
-      <c r="F116" s="3">
-        <v>0</v>
-      </c>
-      <c r="G116" s="4" t="s">
-        <v>26</v>
+      <c r="F116" s="5">
+        <v>85</v>
+      </c>
+      <c r="G116" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
@@ -13938,11 +13938,11 @@
       <c r="E117">
         <v>1</v>
       </c>
-      <c r="F117" s="3">
-        <v>0</v>
-      </c>
-      <c r="G117" s="4" t="s">
-        <v>26</v>
+      <c r="F117" s="5">
+        <v>273</v>
+      </c>
+      <c r="G117" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.25">
@@ -13961,11 +13961,11 @@
       <c r="E118">
         <v>1</v>
       </c>
-      <c r="F118" s="3">
-        <v>0</v>
-      </c>
-      <c r="G118" s="4" t="s">
-        <v>26</v>
+      <c r="F118" s="5">
+        <v>272</v>
+      </c>
+      <c r="G118" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.25">
@@ -14007,11 +14007,11 @@
       <c r="E120">
         <v>36</v>
       </c>
-      <c r="F120" s="3">
-        <v>0</v>
-      </c>
-      <c r="G120" s="4" t="s">
-        <v>26</v>
+      <c r="F120" s="7">
+        <v>261</v>
+      </c>
+      <c r="G120" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.25">
@@ -14053,11 +14053,11 @@
       <c r="E122">
         <v>12</v>
       </c>
-      <c r="F122" s="3">
-        <v>0</v>
-      </c>
-      <c r="G122" s="4" t="s">
-        <v>26</v>
+      <c r="F122" s="5">
+        <v>2925</v>
+      </c>
+      <c r="G122" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.25">
@@ -14076,11 +14076,11 @@
       <c r="E123">
         <v>36</v>
       </c>
-      <c r="F123" s="3">
-        <v>0</v>
-      </c>
-      <c r="G123" s="4" t="s">
-        <v>26</v>
+      <c r="F123" s="7">
+        <v>10</v>
+      </c>
+      <c r="G123" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.25">
@@ -14099,11 +14099,11 @@
       <c r="E124">
         <v>12</v>
       </c>
-      <c r="F124" s="3">
-        <v>0</v>
-      </c>
-      <c r="G124" s="4" t="s">
-        <v>26</v>
+      <c r="F124" s="5">
+        <v>2515</v>
+      </c>
+      <c r="G124" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.25">
@@ -14122,11 +14122,11 @@
       <c r="E125">
         <v>36</v>
       </c>
-      <c r="F125" s="3">
-        <v>0</v>
-      </c>
-      <c r="G125" s="4" t="s">
-        <v>26</v>
+      <c r="F125" s="5">
+        <v>969</v>
+      </c>
+      <c r="G125" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.25">
@@ -14145,11 +14145,11 @@
       <c r="E126">
         <v>120</v>
       </c>
-      <c r="F126" s="3">
-        <v>0</v>
-      </c>
-      <c r="G126" s="4" t="s">
-        <v>26</v>
+      <c r="F126" s="5">
+        <v>2200</v>
+      </c>
+      <c r="G126" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.25">
@@ -14168,11 +14168,11 @@
       <c r="E127">
         <v>120</v>
       </c>
-      <c r="F127" s="3">
-        <v>0</v>
-      </c>
-      <c r="G127" s="4" t="s">
-        <v>26</v>
+      <c r="F127" s="7">
+        <v>155</v>
+      </c>
+      <c r="G127" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
@@ -14191,11 +14191,11 @@
       <c r="E128">
         <v>120</v>
       </c>
-      <c r="F128" s="3">
-        <v>0</v>
-      </c>
-      <c r="G128" s="4" t="s">
-        <v>26</v>
+      <c r="F128" s="7">
+        <v>519</v>
+      </c>
+      <c r="G128" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -14214,11 +14214,11 @@
       <c r="E129">
         <v>120</v>
       </c>
-      <c r="F129" s="3">
-        <v>0</v>
-      </c>
-      <c r="G129" s="4" t="s">
-        <v>26</v>
+      <c r="F129" s="7">
+        <v>1067</v>
+      </c>
+      <c r="G129" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -14237,11 +14237,11 @@
       <c r="E130">
         <v>120</v>
       </c>
-      <c r="F130" s="3">
-        <v>0</v>
-      </c>
-      <c r="G130" s="4" t="s">
-        <v>26</v>
+      <c r="F130" s="7">
+        <v>884</v>
+      </c>
+      <c r="G130" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -14260,11 +14260,11 @@
       <c r="E131">
         <v>120</v>
       </c>
-      <c r="F131" s="3">
-        <v>0</v>
-      </c>
-      <c r="G131" s="4" t="s">
-        <v>26</v>
+      <c r="F131" s="7">
+        <v>55</v>
+      </c>
+      <c r="G131" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
@@ -14283,11 +14283,11 @@
       <c r="E132">
         <v>120</v>
       </c>
-      <c r="F132" s="3">
-        <v>0</v>
-      </c>
-      <c r="G132" s="4" t="s">
-        <v>26</v>
+      <c r="F132" s="7">
+        <v>233</v>
+      </c>
+      <c r="G132" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -14306,11 +14306,11 @@
       <c r="E133">
         <v>120</v>
       </c>
-      <c r="F133" s="3">
-        <v>0</v>
-      </c>
-      <c r="G133" s="4" t="s">
-        <v>26</v>
+      <c r="F133" s="5">
+        <v>6592</v>
+      </c>
+      <c r="G133" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -14329,11 +14329,11 @@
       <c r="E134">
         <v>120</v>
       </c>
-      <c r="F134" s="3">
-        <v>0</v>
-      </c>
-      <c r="G134" s="4" t="s">
-        <v>26</v>
+      <c r="F134" s="7">
+        <v>1017</v>
+      </c>
+      <c r="G134" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -14352,11 +14352,11 @@
       <c r="E135">
         <v>120</v>
       </c>
-      <c r="F135" s="3">
-        <v>0</v>
-      </c>
-      <c r="G135" s="4" t="s">
-        <v>26</v>
+      <c r="F135" s="7">
+        <v>2</v>
+      </c>
+      <c r="G135" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -14375,11 +14375,11 @@
       <c r="E136">
         <v>120</v>
       </c>
-      <c r="F136" s="3">
-        <v>0</v>
-      </c>
-      <c r="G136" s="4" t="s">
-        <v>26</v>
+      <c r="F136" s="5">
+        <v>4015</v>
+      </c>
+      <c r="G136" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -14398,11 +14398,11 @@
       <c r="E137">
         <v>120</v>
       </c>
-      <c r="F137" s="3">
-        <v>0</v>
-      </c>
-      <c r="G137" s="4" t="s">
-        <v>26</v>
+      <c r="F137" s="5">
+        <v>1904</v>
+      </c>
+      <c r="G137" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -14421,11 +14421,11 @@
       <c r="E138">
         <v>120</v>
       </c>
-      <c r="F138" s="3">
-        <v>0</v>
-      </c>
-      <c r="G138" s="4" t="s">
-        <v>26</v>
+      <c r="F138" s="7">
+        <v>10</v>
+      </c>
+      <c r="G138" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
@@ -14444,11 +14444,11 @@
       <c r="E139">
         <v>120</v>
       </c>
-      <c r="F139" s="3">
-        <v>0</v>
-      </c>
-      <c r="G139" s="4" t="s">
-        <v>26</v>
+      <c r="F139" s="5">
+        <v>4463</v>
+      </c>
+      <c r="G139" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -14467,11 +14467,11 @@
       <c r="E140">
         <v>120</v>
       </c>
-      <c r="F140" s="3">
-        <v>0</v>
-      </c>
-      <c r="G140" s="4" t="s">
-        <v>26</v>
+      <c r="F140" s="7">
+        <v>3</v>
+      </c>
+      <c r="G140" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
@@ -14490,11 +14490,11 @@
       <c r="E141">
         <v>120</v>
       </c>
-      <c r="F141" s="3">
-        <v>0</v>
-      </c>
-      <c r="G141" s="4" t="s">
-        <v>26</v>
+      <c r="F141" s="5">
+        <v>4217</v>
+      </c>
+      <c r="G141" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -14513,11 +14513,11 @@
       <c r="E142">
         <v>120</v>
       </c>
-      <c r="F142" s="3">
-        <v>0</v>
-      </c>
-      <c r="G142" s="4" t="s">
-        <v>26</v>
+      <c r="F142" s="5">
+        <v>3364</v>
+      </c>
+      <c r="G142" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
@@ -14536,11 +14536,11 @@
       <c r="E143">
         <v>120</v>
       </c>
-      <c r="F143" s="3">
-        <v>0</v>
-      </c>
-      <c r="G143" s="4" t="s">
-        <v>26</v>
+      <c r="F143" s="7">
+        <v>514</v>
+      </c>
+      <c r="G143" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -14582,11 +14582,11 @@
       <c r="E145">
         <v>120</v>
       </c>
-      <c r="F145" s="3">
-        <v>0</v>
-      </c>
-      <c r="G145" s="4" t="s">
-        <v>26</v>
+      <c r="F145" s="7">
+        <v>1</v>
+      </c>
+      <c r="G145" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
@@ -14605,11 +14605,11 @@
       <c r="E146">
         <v>60</v>
       </c>
-      <c r="F146" s="3">
-        <v>0</v>
-      </c>
-      <c r="G146" s="4" t="s">
-        <v>26</v>
+      <c r="F146" s="5">
+        <v>752</v>
+      </c>
+      <c r="G146" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
@@ -14628,11 +14628,11 @@
       <c r="E147">
         <v>120</v>
       </c>
-      <c r="F147" s="3">
-        <v>0</v>
-      </c>
-      <c r="G147" s="4" t="s">
-        <v>26</v>
+      <c r="F147" s="5">
+        <v>1964</v>
+      </c>
+      <c r="G147" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
@@ -14651,11 +14651,11 @@
       <c r="E148">
         <v>120</v>
       </c>
-      <c r="F148" s="3">
-        <v>0</v>
-      </c>
-      <c r="G148" s="4" t="s">
-        <v>26</v>
+      <c r="F148" s="7">
+        <v>397</v>
+      </c>
+      <c r="G148" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
@@ -14674,11 +14674,11 @@
       <c r="E149">
         <v>120</v>
       </c>
-      <c r="F149" s="3">
-        <v>0</v>
-      </c>
-      <c r="G149" s="4" t="s">
-        <v>26</v>
+      <c r="F149" s="7">
+        <v>1</v>
+      </c>
+      <c r="G149" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
@@ -14697,11 +14697,11 @@
       <c r="E150">
         <v>120</v>
       </c>
-      <c r="F150" s="3">
-        <v>0</v>
-      </c>
-      <c r="G150" s="4" t="s">
-        <v>26</v>
+      <c r="F150" s="7">
+        <v>386</v>
+      </c>
+      <c r="G150" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
@@ -14720,11 +14720,11 @@
       <c r="E151">
         <v>120</v>
       </c>
-      <c r="F151" s="3">
-        <v>0</v>
-      </c>
-      <c r="G151" s="4" t="s">
-        <v>26</v>
+      <c r="F151" s="5">
+        <v>2007</v>
+      </c>
+      <c r="G151" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
@@ -14743,11 +14743,11 @@
       <c r="E152">
         <v>120</v>
       </c>
-      <c r="F152" s="3">
-        <v>0</v>
-      </c>
-      <c r="G152" s="4" t="s">
-        <v>26</v>
+      <c r="F152" s="7">
+        <v>2</v>
+      </c>
+      <c r="G152" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
@@ -14789,11 +14789,11 @@
       <c r="E154">
         <v>120</v>
       </c>
-      <c r="F154" s="3">
-        <v>0</v>
-      </c>
-      <c r="G154" s="4" t="s">
-        <v>26</v>
+      <c r="F154" s="5">
+        <v>3277</v>
+      </c>
+      <c r="G154" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
@@ -14812,11 +14812,11 @@
       <c r="E155">
         <v>120</v>
       </c>
-      <c r="F155" s="3">
-        <v>0</v>
-      </c>
-      <c r="G155" s="4" t="s">
-        <v>26</v>
+      <c r="F155" s="7">
+        <v>908</v>
+      </c>
+      <c r="G155" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
@@ -14835,11 +14835,11 @@
       <c r="E156">
         <v>120</v>
       </c>
-      <c r="F156" s="3">
-        <v>0</v>
-      </c>
-      <c r="G156" s="4" t="s">
-        <v>26</v>
+      <c r="F156" s="7">
+        <v>306</v>
+      </c>
+      <c r="G156" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
@@ -14858,11 +14858,11 @@
       <c r="E157">
         <v>120</v>
       </c>
-      <c r="F157" s="3">
-        <v>0</v>
-      </c>
-      <c r="G157" s="4" t="s">
-        <v>26</v>
+      <c r="F157" s="5">
+        <v>3114</v>
+      </c>
+      <c r="G157" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
@@ -14881,11 +14881,11 @@
       <c r="E158">
         <v>120</v>
       </c>
-      <c r="F158" s="3">
-        <v>0</v>
-      </c>
-      <c r="G158" s="4" t="s">
-        <v>26</v>
+      <c r="F158" s="7">
+        <v>1101</v>
+      </c>
+      <c r="G158" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -14904,11 +14904,11 @@
       <c r="E159">
         <v>120</v>
       </c>
-      <c r="F159" s="3">
-        <v>0</v>
-      </c>
-      <c r="G159" s="4" t="s">
-        <v>26</v>
+      <c r="F159" s="5">
+        <v>3978</v>
+      </c>
+      <c r="G159" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -14927,11 +14927,11 @@
       <c r="E160">
         <v>120</v>
       </c>
-      <c r="F160" s="3">
-        <v>0</v>
-      </c>
-      <c r="G160" s="4" t="s">
-        <v>26</v>
+      <c r="F160" s="7">
+        <v>6</v>
+      </c>
+      <c r="G160" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -14950,11 +14950,11 @@
       <c r="E161">
         <v>120</v>
       </c>
-      <c r="F161" s="3">
-        <v>0</v>
-      </c>
-      <c r="G161" s="4" t="s">
-        <v>26</v>
+      <c r="F161" s="5">
+        <v>1926</v>
+      </c>
+      <c r="G161" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -14973,11 +14973,11 @@
       <c r="E162">
         <v>120</v>
       </c>
-      <c r="F162" s="3">
-        <v>0</v>
-      </c>
-      <c r="G162" s="4" t="s">
-        <v>26</v>
+      <c r="F162" s="5">
+        <v>4672</v>
+      </c>
+      <c r="G162" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
@@ -14996,11 +14996,11 @@
       <c r="E163">
         <v>120</v>
       </c>
-      <c r="F163" s="3">
-        <v>0</v>
-      </c>
-      <c r="G163" s="4" t="s">
-        <v>26</v>
+      <c r="F163" s="5">
+        <v>4562</v>
+      </c>
+      <c r="G163" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -15019,11 +15019,11 @@
       <c r="E164">
         <v>120</v>
       </c>
-      <c r="F164" s="3">
-        <v>0</v>
-      </c>
-      <c r="G164" s="4" t="s">
-        <v>26</v>
+      <c r="F164" s="7">
+        <v>264</v>
+      </c>
+      <c r="G164" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
@@ -15042,11 +15042,11 @@
       <c r="E165">
         <v>120</v>
       </c>
-      <c r="F165" s="3">
-        <v>0</v>
-      </c>
-      <c r="G165" s="4" t="s">
-        <v>26</v>
+      <c r="F165" s="5">
+        <v>1260</v>
+      </c>
+      <c r="G165" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
@@ -15065,11 +15065,11 @@
       <c r="E166">
         <v>120</v>
       </c>
-      <c r="F166" s="3">
-        <v>0</v>
-      </c>
-      <c r="G166" s="4" t="s">
-        <v>26</v>
+      <c r="F166" s="5">
+        <v>3735</v>
+      </c>
+      <c r="G166" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
@@ -15088,11 +15088,11 @@
       <c r="E167">
         <v>120</v>
       </c>
-      <c r="F167" s="3">
-        <v>0</v>
-      </c>
-      <c r="G167" s="4" t="s">
-        <v>26</v>
+      <c r="F167" s="7">
+        <v>764</v>
+      </c>
+      <c r="G167" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.25">
@@ -15111,11 +15111,11 @@
       <c r="E168">
         <v>120</v>
       </c>
-      <c r="F168" s="3">
-        <v>0</v>
-      </c>
-      <c r="G168" s="4" t="s">
-        <v>26</v>
+      <c r="F168" s="7">
+        <v>157</v>
+      </c>
+      <c r="G168" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
@@ -15134,11 +15134,11 @@
       <c r="E169">
         <v>120</v>
       </c>
-      <c r="F169" s="3">
-        <v>0</v>
-      </c>
-      <c r="G169" s="4" t="s">
-        <v>26</v>
+      <c r="F169" s="7">
+        <v>703</v>
+      </c>
+      <c r="G169" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
@@ -15180,11 +15180,11 @@
       <c r="E171">
         <v>120</v>
       </c>
-      <c r="F171" s="3">
-        <v>0</v>
-      </c>
-      <c r="G171" s="4" t="s">
-        <v>26</v>
+      <c r="F171" s="5">
+        <v>7702</v>
+      </c>
+      <c r="G171" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
@@ -15203,11 +15203,11 @@
       <c r="E172">
         <v>120</v>
       </c>
-      <c r="F172" s="3">
-        <v>0</v>
-      </c>
-      <c r="G172" s="4" t="s">
-        <v>26</v>
+      <c r="F172" s="5">
+        <v>2089</v>
+      </c>
+      <c r="G172" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
@@ -15226,11 +15226,11 @@
       <c r="E173">
         <v>1</v>
       </c>
-      <c r="F173" s="3">
-        <v>0</v>
-      </c>
-      <c r="G173" s="4" t="s">
-        <v>26</v>
+      <c r="F173" s="5">
+        <v>232</v>
+      </c>
+      <c r="G173" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.25">
@@ -15249,11 +15249,11 @@
       <c r="E174">
         <v>1</v>
       </c>
-      <c r="F174" s="3">
-        <v>0</v>
-      </c>
-      <c r="G174" s="4" t="s">
-        <v>26</v>
+      <c r="F174" s="5">
+        <v>147</v>
+      </c>
+      <c r="G174" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
@@ -15272,11 +15272,11 @@
       <c r="E175">
         <v>12</v>
       </c>
-      <c r="F175" s="3">
-        <v>0</v>
-      </c>
-      <c r="G175" s="4" t="s">
-        <v>26</v>
+      <c r="F175" s="7">
+        <v>22</v>
+      </c>
+      <c r="G175" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
@@ -15341,11 +15341,11 @@
       <c r="E178">
         <v>12</v>
       </c>
-      <c r="F178" s="3">
-        <v>0</v>
-      </c>
-      <c r="G178" s="4" t="s">
-        <v>26</v>
+      <c r="F178" s="5">
+        <v>163</v>
+      </c>
+      <c r="G178" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.25">
@@ -15364,11 +15364,11 @@
       <c r="E179">
         <v>12</v>
       </c>
-      <c r="F179" s="3">
-        <v>0</v>
-      </c>
-      <c r="G179" s="4" t="s">
-        <v>26</v>
+      <c r="F179" s="7">
+        <v>1</v>
+      </c>
+      <c r="G179" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
@@ -15433,11 +15433,11 @@
       <c r="E182">
         <v>12</v>
       </c>
-      <c r="F182" s="3">
-        <v>0</v>
-      </c>
-      <c r="G182" s="4" t="s">
-        <v>26</v>
+      <c r="F182" s="5">
+        <v>211</v>
+      </c>
+      <c r="G182" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.25">
@@ -15456,11 +15456,11 @@
       <c r="E183">
         <v>12</v>
       </c>
-      <c r="F183" s="3">
-        <v>0</v>
-      </c>
-      <c r="G183" s="4" t="s">
-        <v>26</v>
+      <c r="F183" s="7">
+        <v>53</v>
+      </c>
+      <c r="G183" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.25">
@@ -15479,11 +15479,11 @@
       <c r="E184">
         <v>12</v>
       </c>
-      <c r="F184" s="3">
-        <v>0</v>
-      </c>
-      <c r="G184" s="4" t="s">
-        <v>26</v>
+      <c r="F184" s="7">
+        <v>11</v>
+      </c>
+      <c r="G184" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.25">
@@ -15502,11 +15502,11 @@
       <c r="E185">
         <v>400</v>
       </c>
-      <c r="F185" s="3">
-        <v>0</v>
-      </c>
-      <c r="G185" s="4" t="s">
-        <v>26</v>
+      <c r="F185" s="5">
+        <v>76950</v>
+      </c>
+      <c r="G185" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.25">
@@ -15525,11 +15525,11 @@
       <c r="E186">
         <v>400</v>
       </c>
-      <c r="F186" s="3">
-        <v>0</v>
-      </c>
-      <c r="G186" s="4" t="s">
-        <v>26</v>
+      <c r="F186" s="5">
+        <v>72165</v>
+      </c>
+      <c r="G186" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
@@ -15548,11 +15548,11 @@
       <c r="E187">
         <v>120</v>
       </c>
-      <c r="F187" s="3">
-        <v>0</v>
-      </c>
-      <c r="G187" s="4" t="s">
-        <v>26</v>
+      <c r="F187" s="5">
+        <v>3620</v>
+      </c>
+      <c r="G187" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
@@ -15571,11 +15571,11 @@
       <c r="E188">
         <v>120</v>
       </c>
-      <c r="F188" s="3">
-        <v>0</v>
-      </c>
-      <c r="G188" s="4" t="s">
-        <v>26</v>
+      <c r="F188" s="5">
+        <v>1816</v>
+      </c>
+      <c r="G188" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
@@ -15594,11 +15594,11 @@
       <c r="E189">
         <v>120</v>
       </c>
-      <c r="F189" s="3">
-        <v>0</v>
-      </c>
-      <c r="G189" s="4" t="s">
-        <v>26</v>
+      <c r="F189" s="5">
+        <v>8964</v>
+      </c>
+      <c r="G189" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.25">
@@ -15640,11 +15640,11 @@
       <c r="E191">
         <v>120</v>
       </c>
-      <c r="F191" s="3">
-        <v>0</v>
-      </c>
-      <c r="G191" s="4" t="s">
-        <v>26</v>
+      <c r="F191" s="5">
+        <v>8040</v>
+      </c>
+      <c r="G191" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -24276,11 +24276,11 @@
       <c r="E2">
         <v>50</v>
       </c>
-      <c r="F2" s="3">
-        <v>0</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>26</v>
+      <c r="F2" s="7">
+        <v>1</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -24322,11 +24322,11 @@
       <c r="E4">
         <v>50</v>
       </c>
-      <c r="F4" s="3">
-        <v>0</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>26</v>
+      <c r="F4" s="7">
+        <v>2</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -24368,11 +24368,11 @@
       <c r="E6">
         <v>50</v>
       </c>
-      <c r="F6" s="3">
-        <v>0</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>26</v>
+      <c r="F6" s="5">
+        <v>18563</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -24391,11 +24391,11 @@
       <c r="E7">
         <v>50</v>
       </c>
-      <c r="F7" s="3">
-        <v>0</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>26</v>
+      <c r="F7" s="5">
+        <v>7989</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -24414,11 +24414,11 @@
       <c r="E8">
         <v>50</v>
       </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>26</v>
+      <c r="F8" s="7">
+        <v>8</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -24437,11 +24437,11 @@
       <c r="E9">
         <v>50</v>
       </c>
-      <c r="F9" s="3">
-        <v>0</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>26</v>
+      <c r="F9" s="5">
+        <v>3793</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -24460,11 +24460,11 @@
       <c r="E10">
         <v>50</v>
       </c>
-      <c r="F10" s="3">
-        <v>0</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>26</v>
+      <c r="F10" s="5">
+        <v>14254</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -24483,11 +24483,11 @@
       <c r="E11">
         <v>50</v>
       </c>
-      <c r="F11" s="3">
-        <v>0</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>26</v>
+      <c r="F11" s="5">
+        <v>5110</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -24506,11 +24506,11 @@
       <c r="E12">
         <v>50</v>
       </c>
-      <c r="F12" s="3">
-        <v>0</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>26</v>
+      <c r="F12" s="5">
+        <v>3159</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -24529,11 +24529,11 @@
       <c r="E13">
         <v>50</v>
       </c>
-      <c r="F13" s="3">
-        <v>0</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>26</v>
+      <c r="F13" s="5">
+        <v>4475</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -24552,11 +24552,11 @@
       <c r="E14">
         <v>50</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>26</v>
+      <c r="F14" s="7">
+        <v>471</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -24575,11 +24575,11 @@
       <c r="E15">
         <v>50</v>
       </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>26</v>
+      <c r="F15" s="7">
+        <v>445</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -24598,11 +24598,11 @@
       <c r="E16">
         <v>50</v>
       </c>
-      <c r="F16" s="3">
-        <v>0</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>26</v>
+      <c r="F16" s="5">
+        <v>5267</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -24621,11 +24621,11 @@
       <c r="E17">
         <v>50</v>
       </c>
-      <c r="F17" s="3">
-        <v>0</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>26</v>
+      <c r="F17" s="5">
+        <v>8332</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -24644,11 +24644,11 @@
       <c r="E18">
         <v>50</v>
       </c>
-      <c r="F18" s="3">
-        <v>0</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>26</v>
+      <c r="F18" s="5">
+        <v>15919</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -24667,11 +24667,11 @@
       <c r="E19">
         <v>50</v>
       </c>
-      <c r="F19" s="3">
-        <v>0</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>26</v>
+      <c r="F19" s="5">
+        <v>2347</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -24690,11 +24690,11 @@
       <c r="E20">
         <v>50</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>26</v>
+      <c r="F20" s="7">
+        <v>6</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -24713,11 +24713,11 @@
       <c r="E21">
         <v>50</v>
       </c>
-      <c r="F21" s="3">
-        <v>0</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>26</v>
+      <c r="F21" s="5">
+        <v>950</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -24736,11 +24736,11 @@
       <c r="E22">
         <v>50</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>26</v>
+      <c r="F22" s="5">
+        <v>793</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -24759,11 +24759,11 @@
       <c r="E23">
         <v>50</v>
       </c>
-      <c r="F23" s="3">
-        <v>0</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>26</v>
+      <c r="F23" s="7">
+        <v>14</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -24782,11 +24782,11 @@
       <c r="E24">
         <v>50</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>26</v>
+      <c r="F24" s="5">
+        <v>49742</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -24805,11 +24805,11 @@
       <c r="E25">
         <v>50</v>
       </c>
-      <c r="F25" s="3">
-        <v>0</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>26</v>
+      <c r="F25" s="5">
+        <v>23061</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -24828,11 +24828,11 @@
       <c r="E26">
         <v>50</v>
       </c>
-      <c r="F26" s="3">
-        <v>0</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>26</v>
+      <c r="F26" s="5">
+        <v>8903</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -24851,11 +24851,11 @@
       <c r="E27">
         <v>50</v>
       </c>
-      <c r="F27" s="3">
-        <v>0</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>26</v>
+      <c r="F27" s="5">
+        <v>6190</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -24874,11 +24874,11 @@
       <c r="E28">
         <v>50</v>
       </c>
-      <c r="F28" s="3">
-        <v>0</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>26</v>
+      <c r="F28" s="5">
+        <v>23250</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -24897,11 +24897,11 @@
       <c r="E29">
         <v>50</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>26</v>
+      <c r="F29" s="5">
+        <v>8719</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -24920,11 +24920,11 @@
       <c r="E30">
         <v>50</v>
       </c>
-      <c r="F30" s="3">
-        <v>0</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>26</v>
+      <c r="F30" s="5">
+        <v>9626</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -24943,11 +24943,11 @@
       <c r="E31">
         <v>50</v>
       </c>
-      <c r="F31" s="3">
-        <v>0</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>26</v>
+      <c r="F31" s="5">
+        <v>1199</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -24966,11 +24966,11 @@
       <c r="E32">
         <v>50</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>26</v>
+      <c r="F32" s="5">
+        <v>5477</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -24989,11 +24989,11 @@
       <c r="E33">
         <v>50</v>
       </c>
-      <c r="F33" s="3">
-        <v>0</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>26</v>
+      <c r="F33" s="5">
+        <v>23689</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -25012,11 +25012,11 @@
       <c r="E34">
         <v>50</v>
       </c>
-      <c r="F34" s="3">
-        <v>0</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>26</v>
+      <c r="F34" s="5">
+        <v>8524</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -25035,11 +25035,11 @@
       <c r="E35">
         <v>50</v>
       </c>
-      <c r="F35" s="3">
-        <v>0</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>26</v>
+      <c r="F35" s="5">
+        <v>18686</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -25058,11 +25058,11 @@
       <c r="E36">
         <v>50</v>
       </c>
-      <c r="F36" s="3">
-        <v>0</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>26</v>
+      <c r="F36" s="5">
+        <v>24483</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -25104,11 +25104,11 @@
       <c r="E38">
         <v>50</v>
       </c>
-      <c r="F38" s="3">
-        <v>0</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>26</v>
+      <c r="F38" s="5">
+        <v>4621</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -25127,11 +25127,11 @@
       <c r="E39">
         <v>50</v>
       </c>
-      <c r="F39" s="3">
-        <v>0</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>26</v>
+      <c r="F39" s="5">
+        <v>3223</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -25150,11 +25150,11 @@
       <c r="E40">
         <v>50</v>
       </c>
-      <c r="F40" s="3">
-        <v>0</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>26</v>
+      <c r="F40" s="5">
+        <v>7031</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -25173,11 +25173,11 @@
       <c r="E41">
         <v>50</v>
       </c>
-      <c r="F41" s="3">
-        <v>0</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>26</v>
+      <c r="F41" s="5">
+        <v>8844</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -25196,11 +25196,11 @@
       <c r="E42">
         <v>100</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
-      <c r="G42" s="4" t="s">
-        <v>26</v>
+      <c r="F42" s="7">
+        <v>9</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -25242,11 +25242,11 @@
       <c r="E44">
         <v>100</v>
       </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>26</v>
+      <c r="F44" s="5">
+        <v>3439</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -25265,11 +25265,11 @@
       <c r="E45">
         <v>100</v>
       </c>
-      <c r="F45" s="3">
-        <v>0</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>26</v>
+      <c r="F45" s="5">
+        <v>2776</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -25288,11 +25288,11 @@
       <c r="E46">
         <v>100</v>
       </c>
-      <c r="F46" s="3">
-        <v>0</v>
-      </c>
-      <c r="G46" s="4" t="s">
-        <v>26</v>
+      <c r="F46" s="5">
+        <v>4764</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -25311,11 +25311,11 @@
       <c r="E47">
         <v>100</v>
       </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="4" t="s">
-        <v>26</v>
+      <c r="F47" s="5">
+        <v>3213</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -25334,11 +25334,11 @@
       <c r="E48">
         <v>100</v>
       </c>
-      <c r="F48" s="3">
-        <v>0</v>
-      </c>
-      <c r="G48" s="4" t="s">
-        <v>26</v>
+      <c r="F48" s="7">
+        <v>42</v>
+      </c>
+      <c r="G48" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -25357,11 +25357,11 @@
       <c r="E49">
         <v>100</v>
       </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
-      <c r="G49" s="4" t="s">
-        <v>26</v>
+      <c r="F49" s="5">
+        <v>1689</v>
+      </c>
+      <c r="G49" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -25380,11 +25380,11 @@
       <c r="E50">
         <v>100</v>
       </c>
-      <c r="F50" s="3">
-        <v>0</v>
-      </c>
-      <c r="G50" s="4" t="s">
-        <v>26</v>
+      <c r="F50" s="5">
+        <v>2223</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -25403,11 +25403,11 @@
       <c r="E51">
         <v>100</v>
       </c>
-      <c r="F51" s="3">
-        <v>0</v>
-      </c>
-      <c r="G51" s="4" t="s">
-        <v>26</v>
+      <c r="F51" s="5">
+        <v>1492</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -25426,11 +25426,11 @@
       <c r="E52">
         <v>100</v>
       </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="4" t="s">
-        <v>26</v>
+      <c r="F52" s="5">
+        <v>1217</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -25449,11 +25449,11 @@
       <c r="E53">
         <v>100</v>
       </c>
-      <c r="F53" s="3">
-        <v>0</v>
-      </c>
-      <c r="G53" s="4" t="s">
-        <v>26</v>
+      <c r="F53" s="5">
+        <v>1501</v>
+      </c>
+      <c r="G53" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -25472,11 +25472,11 @@
       <c r="E54">
         <v>100</v>
       </c>
-      <c r="F54" s="3">
-        <v>0</v>
-      </c>
-      <c r="G54" s="4" t="s">
-        <v>26</v>
+      <c r="F54" s="7">
+        <v>751</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -25495,11 +25495,11 @@
       <c r="E55">
         <v>100</v>
       </c>
-      <c r="F55" s="3">
-        <v>0</v>
-      </c>
-      <c r="G55" s="4" t="s">
-        <v>26</v>
+      <c r="F55" s="5">
+        <v>3204</v>
+      </c>
+      <c r="G55" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -25518,11 +25518,11 @@
       <c r="E56">
         <v>100</v>
       </c>
-      <c r="F56" s="3">
-        <v>0</v>
-      </c>
-      <c r="G56" s="4" t="s">
-        <v>26</v>
+      <c r="F56" s="5">
+        <v>6582</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -25541,11 +25541,11 @@
       <c r="E57">
         <v>100</v>
       </c>
-      <c r="F57" s="3">
-        <v>0</v>
-      </c>
-      <c r="G57" s="4" t="s">
-        <v>26</v>
+      <c r="F57" s="5">
+        <v>9360</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -25564,11 +25564,11 @@
       <c r="E58">
         <v>100</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="4" t="s">
-        <v>26</v>
+      <c r="F58" s="5">
+        <v>5186</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -25587,11 +25587,11 @@
       <c r="E59">
         <v>100</v>
       </c>
-      <c r="F59" s="3">
-        <v>0</v>
-      </c>
-      <c r="G59" s="4" t="s">
-        <v>26</v>
+      <c r="F59" s="5">
+        <v>17008</v>
+      </c>
+      <c r="G59" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -25610,11 +25610,11 @@
       <c r="E60">
         <v>100</v>
       </c>
-      <c r="F60" s="3">
-        <v>0</v>
-      </c>
-      <c r="G60" s="4" t="s">
-        <v>26</v>
+      <c r="F60" s="7">
+        <v>645</v>
+      </c>
+      <c r="G60" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -25633,11 +25633,11 @@
       <c r="E61">
         <v>100</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
-      <c r="G61" s="4" t="s">
-        <v>26</v>
+      <c r="F61" s="5">
+        <v>3037</v>
+      </c>
+      <c r="G61" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -25656,11 +25656,11 @@
       <c r="E62">
         <v>100</v>
       </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="4" t="s">
-        <v>26</v>
+      <c r="F62" s="5">
+        <v>2618</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -25679,11 +25679,11 @@
       <c r="E63">
         <v>100</v>
       </c>
-      <c r="F63" s="3">
-        <v>0</v>
-      </c>
-      <c r="G63" s="4" t="s">
-        <v>26</v>
+      <c r="F63" s="5">
+        <v>1754</v>
+      </c>
+      <c r="G63" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -25702,11 +25702,11 @@
       <c r="E64">
         <v>100</v>
       </c>
-      <c r="F64" s="3">
-        <v>0</v>
-      </c>
-      <c r="G64" s="4" t="s">
-        <v>26</v>
+      <c r="F64" s="7">
+        <v>253</v>
+      </c>
+      <c r="G64" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -25748,11 +25748,11 @@
       <c r="E66">
         <v>50</v>
       </c>
-      <c r="F66" s="3">
-        <v>0</v>
-      </c>
-      <c r="G66" s="4" t="s">
-        <v>26</v>
+      <c r="F66" s="5">
+        <v>784</v>
+      </c>
+      <c r="G66" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
@@ -25771,11 +25771,11 @@
       <c r="E67">
         <v>100</v>
       </c>
-      <c r="F67" s="3">
-        <v>0</v>
-      </c>
-      <c r="G67" s="4" t="s">
-        <v>26</v>
+      <c r="F67" s="5">
+        <v>9167</v>
+      </c>
+      <c r="G67" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -25794,11 +25794,11 @@
       <c r="E68">
         <v>100</v>
       </c>
-      <c r="F68" s="3">
-        <v>0</v>
-      </c>
-      <c r="G68" s="4" t="s">
-        <v>26</v>
+      <c r="F68" s="5">
+        <v>38116</v>
+      </c>
+      <c r="G68" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
@@ -25817,11 +25817,11 @@
       <c r="E69">
         <v>100</v>
       </c>
-      <c r="F69" s="3">
-        <v>0</v>
-      </c>
-      <c r="G69" s="4" t="s">
-        <v>26</v>
+      <c r="F69" s="5">
+        <v>41458</v>
+      </c>
+      <c r="G69" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
@@ -25840,11 +25840,11 @@
       <c r="E70">
         <v>100</v>
       </c>
-      <c r="F70" s="3">
-        <v>0</v>
-      </c>
-      <c r="G70" s="4" t="s">
-        <v>26</v>
+      <c r="F70" s="5">
+        <v>5567</v>
+      </c>
+      <c r="G70" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
@@ -25863,11 +25863,11 @@
       <c r="E71">
         <v>100</v>
       </c>
-      <c r="F71" s="3">
-        <v>0</v>
-      </c>
-      <c r="G71" s="4" t="s">
-        <v>26</v>
+      <c r="F71" s="7">
+        <v>100</v>
+      </c>
+      <c r="G71" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -25886,11 +25886,11 @@
       <c r="E72">
         <v>100</v>
       </c>
-      <c r="F72" s="3">
-        <v>0</v>
-      </c>
-      <c r="G72" s="4" t="s">
-        <v>26</v>
+      <c r="F72" s="5">
+        <v>30095</v>
+      </c>
+      <c r="G72" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -25955,11 +25955,11 @@
       <c r="E75">
         <v>100</v>
       </c>
-      <c r="F75" s="3">
-        <v>0</v>
-      </c>
-      <c r="G75" s="4" t="s">
-        <v>26</v>
+      <c r="F75" s="5">
+        <v>23876</v>
+      </c>
+      <c r="G75" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -27519,11 +27519,11 @@
       <c r="E143">
         <v>24</v>
       </c>
-      <c r="F143" s="3">
-        <v>0</v>
-      </c>
-      <c r="G143" s="4" t="s">
-        <v>26</v>
+      <c r="F143" s="7">
+        <v>3</v>
+      </c>
+      <c r="G143" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -27565,11 +27565,11 @@
       <c r="E145">
         <v>24</v>
       </c>
-      <c r="F145" s="3">
-        <v>0</v>
-      </c>
-      <c r="G145" s="4" t="s">
-        <v>26</v>
+      <c r="F145" s="5">
+        <v>538</v>
+      </c>
+      <c r="G145" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
@@ -27588,11 +27588,11 @@
       <c r="E146">
         <v>24</v>
       </c>
-      <c r="F146" s="3">
-        <v>0</v>
-      </c>
-      <c r="G146" s="4" t="s">
-        <v>26</v>
+      <c r="F146" s="7">
+        <v>5</v>
+      </c>
+      <c r="G146" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
@@ -27611,11 +27611,11 @@
       <c r="E147">
         <v>24</v>
       </c>
-      <c r="F147" s="3">
-        <v>0</v>
-      </c>
-      <c r="G147" s="4" t="s">
-        <v>26</v>
+      <c r="F147" s="7">
+        <v>4</v>
+      </c>
+      <c r="G147" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
@@ -27634,11 +27634,11 @@
       <c r="E148">
         <v>12</v>
       </c>
-      <c r="F148" s="3">
-        <v>0</v>
-      </c>
-      <c r="G148" s="4" t="s">
-        <v>26</v>
+      <c r="F148" s="5">
+        <v>172</v>
+      </c>
+      <c r="G148" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
@@ -27657,11 +27657,11 @@
       <c r="E149">
         <v>12</v>
       </c>
-      <c r="F149" s="3">
-        <v>0</v>
-      </c>
-      <c r="G149" s="4" t="s">
-        <v>26</v>
+      <c r="F149" s="5">
+        <v>616</v>
+      </c>
+      <c r="G149" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
@@ -27680,11 +27680,11 @@
       <c r="E150">
         <v>12</v>
       </c>
-      <c r="F150" s="3">
-        <v>0</v>
-      </c>
-      <c r="G150" s="4" t="s">
-        <v>26</v>
+      <c r="F150" s="5">
+        <v>557</v>
+      </c>
+      <c r="G150" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
@@ -27703,11 +27703,11 @@
       <c r="E151">
         <v>12</v>
       </c>
-      <c r="F151" s="3">
-        <v>0</v>
-      </c>
-      <c r="G151" s="4" t="s">
-        <v>26</v>
+      <c r="F151" s="5">
+        <v>459</v>
+      </c>
+      <c r="G151" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
@@ -27726,11 +27726,11 @@
       <c r="E152">
         <v>12</v>
       </c>
-      <c r="F152" s="3">
-        <v>0</v>
-      </c>
-      <c r="G152" s="4" t="s">
-        <v>26</v>
+      <c r="F152" s="5">
+        <v>303</v>
+      </c>
+      <c r="G152" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
@@ -27749,11 +27749,11 @@
       <c r="E153">
         <v>12</v>
       </c>
-      <c r="F153" s="3">
-        <v>0</v>
-      </c>
-      <c r="G153" s="4" t="s">
-        <v>26</v>
+      <c r="F153" s="5">
+        <v>159</v>
+      </c>
+      <c r="G153" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
@@ -27772,11 +27772,11 @@
       <c r="E154">
         <v>6</v>
       </c>
-      <c r="F154" s="3">
-        <v>0</v>
-      </c>
-      <c r="G154" s="4" t="s">
-        <v>26</v>
+      <c r="F154" s="5">
+        <v>283</v>
+      </c>
+      <c r="G154" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
@@ -27795,11 +27795,11 @@
       <c r="E155">
         <v>6</v>
       </c>
-      <c r="F155" s="3">
-        <v>0</v>
-      </c>
-      <c r="G155" s="4" t="s">
-        <v>26</v>
+      <c r="F155" s="5">
+        <v>1459</v>
+      </c>
+      <c r="G155" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
@@ -27818,11 +27818,11 @@
       <c r="E156">
         <v>6</v>
       </c>
-      <c r="F156" s="3">
-        <v>0</v>
-      </c>
-      <c r="G156" s="4" t="s">
-        <v>26</v>
+      <c r="F156" s="5">
+        <v>936</v>
+      </c>
+      <c r="G156" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.25">
@@ -27841,11 +27841,11 @@
       <c r="E157">
         <v>6</v>
       </c>
-      <c r="F157" s="3">
-        <v>0</v>
-      </c>
-      <c r="G157" s="4" t="s">
-        <v>26</v>
+      <c r="F157" s="5">
+        <v>263</v>
+      </c>
+      <c r="G157" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.25">
@@ -27864,11 +27864,11 @@
       <c r="E158">
         <v>24</v>
       </c>
-      <c r="F158" s="3">
-        <v>0</v>
-      </c>
-      <c r="G158" s="4" t="s">
-        <v>26</v>
+      <c r="F158" s="7">
+        <v>17</v>
+      </c>
+      <c r="G158" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -27887,11 +27887,11 @@
       <c r="E159">
         <v>24</v>
       </c>
-      <c r="F159" s="3">
-        <v>0</v>
-      </c>
-      <c r="G159" s="4" t="s">
-        <v>26</v>
+      <c r="F159" s="7">
+        <v>130</v>
+      </c>
+      <c r="G159" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -27933,11 +27933,11 @@
       <c r="E161">
         <v>24</v>
       </c>
-      <c r="F161" s="3">
-        <v>0</v>
-      </c>
-      <c r="G161" s="4" t="s">
-        <v>26</v>
+      <c r="F161" s="5">
+        <v>922</v>
+      </c>
+      <c r="G161" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -27956,11 +27956,11 @@
       <c r="E162">
         <v>24</v>
       </c>
-      <c r="F162" s="3">
-        <v>0</v>
-      </c>
-      <c r="G162" s="4" t="s">
-        <v>26</v>
+      <c r="F162" s="5">
+        <v>1843</v>
+      </c>
+      <c r="G162" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
@@ -27979,11 +27979,11 @@
       <c r="E163">
         <v>24</v>
       </c>
-      <c r="F163" s="3">
-        <v>0</v>
-      </c>
-      <c r="G163" s="4" t="s">
-        <v>26</v>
+      <c r="F163" s="5">
+        <v>586</v>
+      </c>
+      <c r="G163" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -28002,11 +28002,11 @@
       <c r="E164">
         <v>24</v>
       </c>
-      <c r="F164" s="3">
-        <v>0</v>
-      </c>
-      <c r="G164" s="4" t="s">
-        <v>26</v>
+      <c r="F164" s="5">
+        <v>996</v>
+      </c>
+      <c r="G164" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
@@ -28025,11 +28025,11 @@
       <c r="E165">
         <v>24</v>
       </c>
-      <c r="F165" s="3">
-        <v>0</v>
-      </c>
-      <c r="G165" s="4" t="s">
-        <v>26</v>
+      <c r="F165" s="5">
+        <v>1246</v>
+      </c>
+      <c r="G165" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
@@ -28048,11 +28048,11 @@
       <c r="E166">
         <v>24</v>
       </c>
-      <c r="F166" s="3">
-        <v>0</v>
-      </c>
-      <c r="G166" s="4" t="s">
-        <v>26</v>
+      <c r="F166" s="7">
+        <v>1</v>
+      </c>
+      <c r="G166" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.25">
@@ -28784,11 +28784,11 @@
       <c r="E198">
         <v>10</v>
       </c>
-      <c r="F198" s="3">
-        <v>0</v>
-      </c>
-      <c r="G198" s="4" t="s">
-        <v>26</v>
+      <c r="F198" s="5">
+        <v>216</v>
+      </c>
+      <c r="G198" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.25">
@@ -28807,11 +28807,11 @@
       <c r="E199">
         <v>10</v>
       </c>
-      <c r="F199" s="3">
-        <v>0</v>
-      </c>
-      <c r="G199" s="4" t="s">
-        <v>26</v>
+      <c r="F199" s="7">
+        <v>69</v>
+      </c>
+      <c r="G199" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
@@ -29198,11 +29198,11 @@
       <c r="E216">
         <v>5</v>
       </c>
-      <c r="F216" s="3">
-        <v>0</v>
-      </c>
-      <c r="G216" s="4" t="s">
-        <v>26</v>
+      <c r="F216" s="5">
+        <v>90</v>
+      </c>
+      <c r="G216" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.25">
@@ -29221,11 +29221,11 @@
       <c r="E217">
         <v>5</v>
       </c>
-      <c r="F217" s="3">
-        <v>0</v>
-      </c>
-      <c r="G217" s="4" t="s">
-        <v>26</v>
+      <c r="F217" s="5">
+        <v>395</v>
+      </c>
+      <c r="G217" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.25">
@@ -29244,11 +29244,11 @@
       <c r="E218">
         <v>5</v>
       </c>
-      <c r="F218" s="3">
-        <v>0</v>
-      </c>
-      <c r="G218" s="4" t="s">
-        <v>26</v>
+      <c r="F218" s="5">
+        <v>129</v>
+      </c>
+      <c r="G218" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.25">
@@ -29267,11 +29267,11 @@
       <c r="E219">
         <v>5</v>
       </c>
-      <c r="F219" s="3">
-        <v>0</v>
-      </c>
-      <c r="G219" s="4" t="s">
-        <v>26</v>
+      <c r="F219" s="7">
+        <v>1</v>
+      </c>
+      <c r="G219" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.25">
@@ -29520,11 +29520,11 @@
       <c r="E230">
         <v>5</v>
       </c>
-      <c r="F230" s="3">
-        <v>0</v>
-      </c>
-      <c r="G230" s="4" t="s">
-        <v>26</v>
+      <c r="F230" s="5">
+        <v>917</v>
+      </c>
+      <c r="G230" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.25">
@@ -29566,11 +29566,11 @@
       <c r="E232">
         <v>5</v>
       </c>
-      <c r="F232" s="3">
-        <v>0</v>
-      </c>
-      <c r="G232" s="4" t="s">
-        <v>26</v>
+      <c r="F232" s="5">
+        <v>262</v>
+      </c>
+      <c r="G232" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.25">
@@ -29589,11 +29589,11 @@
       <c r="E233">
         <v>5</v>
       </c>
-      <c r="F233" s="3">
-        <v>0</v>
-      </c>
-      <c r="G233" s="4" t="s">
-        <v>26</v>
+      <c r="F233" s="5">
+        <v>176</v>
+      </c>
+      <c r="G233" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.25">
@@ -29612,11 +29612,11 @@
       <c r="E234">
         <v>5</v>
       </c>
-      <c r="F234" s="3">
-        <v>0</v>
-      </c>
-      <c r="G234" s="4" t="s">
-        <v>26</v>
+      <c r="F234" s="5">
+        <v>72</v>
+      </c>
+      <c r="G234" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
@@ -29635,11 +29635,11 @@
       <c r="E235">
         <v>5</v>
       </c>
-      <c r="F235" s="3">
-        <v>0</v>
-      </c>
-      <c r="G235" s="4" t="s">
-        <v>26</v>
+      <c r="F235" s="5">
+        <v>361</v>
+      </c>
+      <c r="G235" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.25">
@@ -29658,11 +29658,11 @@
       <c r="E236">
         <v>5</v>
       </c>
-      <c r="F236" s="3">
-        <v>0</v>
-      </c>
-      <c r="G236" s="4" t="s">
-        <v>26</v>
+      <c r="F236" s="5">
+        <v>257</v>
+      </c>
+      <c r="G236" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.25">
@@ -29681,11 +29681,11 @@
       <c r="E237">
         <v>5</v>
       </c>
-      <c r="F237" s="3">
-        <v>0</v>
-      </c>
-      <c r="G237" s="4" t="s">
-        <v>26</v>
+      <c r="F237" s="5">
+        <v>257</v>
+      </c>
+      <c r="G237" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.25">
@@ -29704,11 +29704,11 @@
       <c r="E238">
         <v>5</v>
       </c>
-      <c r="F238" s="3">
-        <v>0</v>
-      </c>
-      <c r="G238" s="4" t="s">
-        <v>26</v>
+      <c r="F238" s="5">
+        <v>231</v>
+      </c>
+      <c r="G238" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.25">
@@ -29727,11 +29727,11 @@
       <c r="E239">
         <v>5</v>
       </c>
-      <c r="F239" s="3">
-        <v>0</v>
-      </c>
-      <c r="G239" s="4" t="s">
-        <v>26</v>
+      <c r="F239" s="5">
+        <v>277</v>
+      </c>
+      <c r="G239" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.25">
@@ -29750,11 +29750,11 @@
       <c r="E240">
         <v>5</v>
       </c>
-      <c r="F240" s="3">
-        <v>0</v>
-      </c>
-      <c r="G240" s="4" t="s">
-        <v>26</v>
+      <c r="F240" s="5">
+        <v>117</v>
+      </c>
+      <c r="G240" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.25">
@@ -29773,11 +29773,11 @@
       <c r="E241">
         <v>5</v>
       </c>
-      <c r="F241" s="3">
-        <v>0</v>
-      </c>
-      <c r="G241" s="4" t="s">
-        <v>26</v>
+      <c r="F241" s="5">
+        <v>1705</v>
+      </c>
+      <c r="G241" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.25">
@@ -29796,11 +29796,11 @@
       <c r="E242">
         <v>5</v>
       </c>
-      <c r="F242" s="3">
-        <v>0</v>
-      </c>
-      <c r="G242" s="4" t="s">
-        <v>26</v>
+      <c r="F242" s="7">
+        <v>1</v>
+      </c>
+      <c r="G242" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.25">
@@ -29819,11 +29819,11 @@
       <c r="E243">
         <v>5</v>
       </c>
-      <c r="F243" s="3">
-        <v>0</v>
-      </c>
-      <c r="G243" s="4" t="s">
-        <v>26</v>
+      <c r="F243" s="5">
+        <v>275</v>
+      </c>
+      <c r="G243" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.25">
@@ -29842,11 +29842,11 @@
       <c r="E244">
         <v>5</v>
       </c>
-      <c r="F244" s="3">
-        <v>0</v>
-      </c>
-      <c r="G244" s="4" t="s">
-        <v>26</v>
+      <c r="F244" s="5">
+        <v>216</v>
+      </c>
+      <c r="G244" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.25">
@@ -29888,11 +29888,11 @@
       <c r="E246">
         <v>5</v>
       </c>
-      <c r="F246" s="3">
-        <v>0</v>
-      </c>
-      <c r="G246" s="4" t="s">
-        <v>26</v>
+      <c r="F246" s="5">
+        <v>236</v>
+      </c>
+      <c r="G246" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.25">
@@ -29911,11 +29911,11 @@
       <c r="E247">
         <v>5</v>
       </c>
-      <c r="F247" s="3">
-        <v>0</v>
-      </c>
-      <c r="G247" s="4" t="s">
-        <v>26</v>
+      <c r="F247" s="5">
+        <v>392</v>
+      </c>
+      <c r="G247" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.25">
@@ -29934,11 +29934,11 @@
       <c r="E248">
         <v>5</v>
       </c>
-      <c r="F248" s="3">
-        <v>0</v>
-      </c>
-      <c r="G248" s="4" t="s">
-        <v>26</v>
+      <c r="F248" s="5">
+        <v>167</v>
+      </c>
+      <c r="G248" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.25">
@@ -29957,11 +29957,11 @@
       <c r="E249">
         <v>5</v>
       </c>
-      <c r="F249" s="3">
-        <v>0</v>
-      </c>
-      <c r="G249" s="4" t="s">
-        <v>26</v>
+      <c r="F249" s="7">
+        <v>1</v>
+      </c>
+      <c r="G249" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.25">
@@ -29980,11 +29980,11 @@
       <c r="E250">
         <v>5</v>
       </c>
-      <c r="F250" s="3">
-        <v>0</v>
-      </c>
-      <c r="G250" s="4" t="s">
-        <v>26</v>
+      <c r="F250" s="5">
+        <v>320</v>
+      </c>
+      <c r="G250" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.25">
@@ -30003,11 +30003,11 @@
       <c r="E251">
         <v>40</v>
       </c>
-      <c r="F251" s="3">
-        <v>0</v>
-      </c>
-      <c r="G251" s="4" t="s">
-        <v>26</v>
+      <c r="F251" s="5">
+        <v>4427</v>
+      </c>
+      <c r="G251" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.25">
@@ -30095,11 +30095,11 @@
       <c r="E255">
         <v>100</v>
       </c>
-      <c r="F255" s="3">
-        <v>0</v>
-      </c>
-      <c r="G255" s="4" t="s">
-        <v>26</v>
+      <c r="F255" s="5">
+        <v>211699</v>
+      </c>
+      <c r="G255" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.25">
@@ -30118,11 +30118,11 @@
       <c r="E256">
         <v>100</v>
       </c>
-      <c r="F256" s="3">
-        <v>0</v>
-      </c>
-      <c r="G256" s="4" t="s">
-        <v>26</v>
+      <c r="F256" s="5">
+        <v>90955</v>
+      </c>
+      <c r="G256" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.25">
@@ -30141,11 +30141,11 @@
       <c r="E257">
         <v>5</v>
       </c>
-      <c r="F257" s="3">
-        <v>0</v>
-      </c>
-      <c r="G257" s="4" t="s">
-        <v>26</v>
+      <c r="F257" s="5">
+        <v>620</v>
+      </c>
+      <c r="G257" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.25">
@@ -30164,11 +30164,11 @@
       <c r="E258">
         <v>5</v>
       </c>
-      <c r="F258" s="3">
-        <v>0</v>
-      </c>
-      <c r="G258" s="4" t="s">
-        <v>26</v>
+      <c r="F258" s="5">
+        <v>355</v>
+      </c>
+      <c r="G258" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.25">
@@ -30187,11 +30187,11 @@
       <c r="E259">
         <v>5</v>
       </c>
-      <c r="F259" s="3">
-        <v>0</v>
-      </c>
-      <c r="G259" s="4" t="s">
-        <v>26</v>
+      <c r="F259" s="5">
+        <v>89</v>
+      </c>
+      <c r="G259" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.25">
@@ -30210,11 +30210,11 @@
       <c r="E260">
         <v>5</v>
       </c>
-      <c r="F260" s="3">
-        <v>0</v>
-      </c>
-      <c r="G260" s="4" t="s">
-        <v>26</v>
+      <c r="F260" s="5">
+        <v>287</v>
+      </c>
+      <c r="G260" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.25">
@@ -30233,11 +30233,11 @@
       <c r="E261">
         <v>5</v>
       </c>
-      <c r="F261" s="3">
-        <v>0</v>
-      </c>
-      <c r="G261" s="4" t="s">
-        <v>26</v>
+      <c r="F261" s="5">
+        <v>72</v>
+      </c>
+      <c r="G261" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.25">
@@ -30256,11 +30256,11 @@
       <c r="E262">
         <v>5</v>
       </c>
-      <c r="F262" s="3">
-        <v>0</v>
-      </c>
-      <c r="G262" s="4" t="s">
-        <v>26</v>
+      <c r="F262" s="5">
+        <v>328</v>
+      </c>
+      <c r="G262" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.25">
@@ -30279,11 +30279,11 @@
       <c r="E263">
         <v>5</v>
       </c>
-      <c r="F263" s="3">
-        <v>0</v>
-      </c>
-      <c r="G263" s="4" t="s">
-        <v>26</v>
+      <c r="F263" s="5">
+        <v>238</v>
+      </c>
+      <c r="G263" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.25">
@@ -30302,11 +30302,11 @@
       <c r="E264">
         <v>5</v>
       </c>
-      <c r="F264" s="3">
-        <v>0</v>
-      </c>
-      <c r="G264" s="4" t="s">
-        <v>26</v>
+      <c r="F264" s="5">
+        <v>163</v>
+      </c>
+      <c r="G264" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.25">
@@ -30325,11 +30325,11 @@
       <c r="E265">
         <v>5</v>
       </c>
-      <c r="F265" s="3">
-        <v>0</v>
-      </c>
-      <c r="G265" s="4" t="s">
-        <v>26</v>
+      <c r="F265" s="7">
+        <v>27</v>
+      </c>
+      <c r="G265" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.25">
@@ -30348,11 +30348,11 @@
       <c r="E266">
         <v>5</v>
       </c>
-      <c r="F266" s="3">
-        <v>0</v>
-      </c>
-      <c r="G266" s="4" t="s">
+      <c r="F266" s="7">
         <v>26</v>
+      </c>
+      <c r="G266" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -34913,11 +34913,11 @@
       <c r="E2">
         <v>25</v>
       </c>
-      <c r="F2" s="3">
-        <v>0</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>26</v>
+      <c r="F2" s="5">
+        <v>75321</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -34936,11 +34936,11 @@
       <c r="E3">
         <v>50</v>
       </c>
-      <c r="F3" s="3">
-        <v>0</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>26</v>
+      <c r="F3" s="5">
+        <v>217243</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -34959,11 +34959,11 @@
       <c r="E4">
         <v>100</v>
       </c>
-      <c r="F4" s="3">
-        <v>0</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>26</v>
+      <c r="F4" s="5">
+        <v>83362</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -35005,11 +35005,11 @@
       <c r="E6">
         <v>25</v>
       </c>
-      <c r="F6" s="3">
-        <v>0</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>26</v>
+      <c r="F6" s="5">
+        <v>3927</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -35028,11 +35028,11 @@
       <c r="E7">
         <v>25</v>
       </c>
-      <c r="F7" s="3">
-        <v>0</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>26</v>
+      <c r="F7" s="5">
+        <v>9975</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -35051,11 +35051,11 @@
       <c r="E8">
         <v>48</v>
       </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>26</v>
+      <c r="F8" s="5">
+        <v>70240</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -35074,11 +35074,11 @@
       <c r="E9">
         <v>48</v>
       </c>
-      <c r="F9" s="3">
-        <v>0</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>26</v>
+      <c r="F9" s="5">
+        <v>83953</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -35097,11 +35097,11 @@
       <c r="E10">
         <v>18</v>
       </c>
-      <c r="F10" s="3">
-        <v>0</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>26</v>
+      <c r="F10" s="5">
+        <v>23800</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -35120,11 +35120,11 @@
       <c r="E11">
         <v>36</v>
       </c>
-      <c r="F11" s="3">
-        <v>0</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>26</v>
+      <c r="F11" s="5">
+        <v>29904</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -35143,11 +35143,11 @@
       <c r="E12">
         <v>25</v>
       </c>
-      <c r="F12" s="3">
-        <v>0</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>26</v>
+      <c r="F12" s="5">
+        <v>25578</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -35166,11 +35166,11 @@
       <c r="E13">
         <v>50</v>
       </c>
-      <c r="F13" s="3">
-        <v>0</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>26</v>
+      <c r="F13" s="5">
+        <v>130113</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -35189,11 +35189,11 @@
       <c r="E14">
         <v>100</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>26</v>
+      <c r="F14" s="5">
+        <v>114396</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -35255,11 +35255,11 @@
       <c r="E2">
         <v>72</v>
       </c>
-      <c r="F2" s="3">
-        <v>0</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>26</v>
+      <c r="F2" s="5">
+        <v>120536</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -35278,11 +35278,11 @@
       <c r="E3">
         <v>72</v>
       </c>
-      <c r="F3" s="3">
-        <v>0</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>26</v>
+      <c r="F3" s="5">
+        <v>216410</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -35301,11 +35301,11 @@
       <c r="E4">
         <v>72</v>
       </c>
-      <c r="F4" s="3">
-        <v>0</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>26</v>
+      <c r="F4" s="5">
+        <v>67049</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -35324,11 +35324,11 @@
       <c r="E5">
         <v>72</v>
       </c>
-      <c r="F5" s="3">
-        <v>0</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>26</v>
+      <c r="F5" s="5">
+        <v>32978</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -35390,11 +35390,11 @@
       <c r="E2">
         <v>12</v>
       </c>
-      <c r="F2" s="3">
-        <v>0</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>26</v>
+      <c r="F2" s="5">
+        <v>3022</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -35413,11 +35413,11 @@
       <c r="E3">
         <v>12</v>
       </c>
-      <c r="F3" s="3">
-        <v>0</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>26</v>
+      <c r="F3" s="5">
+        <v>286</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -35436,11 +35436,11 @@
       <c r="E4">
         <v>12</v>
       </c>
-      <c r="F4" s="3">
-        <v>0</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>26</v>
+      <c r="F4" s="5">
+        <v>157</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -35459,11 +35459,11 @@
       <c r="E5">
         <v>12</v>
       </c>
-      <c r="F5" s="3">
-        <v>0</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>26</v>
+      <c r="F5" s="5">
+        <v>654</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -32,7 +32,7 @@
     <t>Actualización:</t>
   </si>
   <si>
-    <t>7/3/2026, 5:07:04 p. m.</t>
+    <t>7/3/2026, 10:24:36 p. m.</t>
   </si>
   <si>
     <t>ACCESORIOS</t>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -32,7 +32,7 @@
     <t>Actualización:</t>
   </si>
   <si>
-    <t>7/3/2026, 11:01:03 p. m.</t>
+    <t>7/3/2026, 11:23:48 p. m.</t>
   </si>
   <si>
     <t>ACCESORIOS</t>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -32,7 +32,7 @@
     <t>Actualización:</t>
   </si>
   <si>
-    <t>07/03/2026, 19:17:22</t>
+    <t>07/03/2026, 19:46:36</t>
   </si>
   <si>
     <t>TOTAL GENERAL:</t>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -29,7 +29,7 @@
     <t>STOCKPULSE - RESUMEN</t>
   </si>
   <si>
-    <t>Actualización: 08/03/2026, 10:20:29</t>
+    <t>Actualización: 08/03/2026, 11:23:20</t>
   </si>
   <si>
     <t>TOTAL GENERAL</t>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -29,7 +29,7 @@
     <t>STOCKPULSE - RESUMEN</t>
   </si>
   <si>
-    <t>Actualización: 08/03/2026, 11:23:20</t>
+    <t>Actualización: 08/03/2026, 12:19:54</t>
   </si>
   <si>
     <t>TOTAL GENERAL</t>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -29,7 +29,7 @@
     <t>STOCKPULSE - RESUMEN</t>
   </si>
   <si>
-    <t>Actualización: 08/03/2026, 12:19:54</t>
+    <t>Actualización: 08/03/2026, 13:29:05</t>
   </si>
   <si>
     <t>TOTAL GENERAL</t>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -29,7 +29,7 @@
     <t>STOCKPULSE - RESUMEN</t>
   </si>
   <si>
-    <t>Actualización: 08/03/2026, 16:19:58</t>
+    <t>Actualización: 08/03/2026, 17:20:13</t>
   </si>
   <si>
     <t>TOTAL GENERAL</t>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -29,7 +29,7 @@
     <t>STOCKPULSE - RESUMEN</t>
   </si>
   <si>
-    <t>Actualización: 08/03/2026, 17:20:13</t>
+    <t>Actualización: 08/03/2026, 18:20:06</t>
   </si>
   <si>
     <t>TOTAL GENERAL</t>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -29,7 +29,7 @@
     <t>STOCKPULSE - RESUMEN</t>
   </si>
   <si>
-    <t>Actualización: 09/03/2026, 24:03:44</t>
+    <t>Actualización: 09/03/2026, 07:55:17</t>
   </si>
   <si>
     <t>TOTAL GENERAL</t>
@@ -41,7 +41,7 @@
     <t>Unidades:</t>
   </si>
   <si>
-    <t>8,618,880</t>
+    <t>8,617,846</t>
   </si>
   <si>
     <t>Agotados:</t>
@@ -68,7 +68,7 @@
     <t>ACCESORIOS</t>
   </si>
   <si>
-    <t>983,882</t>
+    <t>983,740</t>
   </si>
   <si>
     <t>11.4%</t>
@@ -77,7 +77,7 @@
     <t>ARCHIVO</t>
   </si>
   <si>
-    <t>1,770,394</t>
+    <t>1,770,138</t>
   </si>
   <si>
     <t>20.5%</t>
@@ -86,7 +86,7 @@
     <t>DIBUJO</t>
   </si>
   <si>
-    <t>121,851</t>
+    <t>121,826</t>
   </si>
   <si>
     <t>1.4%</t>
@@ -95,7 +95,7 @@
     <t>DIDACTICOS</t>
   </si>
   <si>
-    <t>27,311</t>
+    <t>27,293</t>
   </si>
   <si>
     <t>0.3%</t>
@@ -104,7 +104,7 @@
     <t>ESCRITURA</t>
   </si>
   <si>
-    <t>1,461,480</t>
+    <t>1,461,386</t>
   </si>
   <si>
     <t>17.0%</t>
@@ -140,7 +140,7 @@
     <t>METALICA</t>
   </si>
   <si>
-    <t>261,169</t>
+    <t>261,148</t>
   </si>
   <si>
     <t>3.0%</t>
@@ -149,7 +149,7 @@
     <t>PEGAMENTOS</t>
   </si>
   <si>
-    <t>634,664</t>
+    <t>634,544</t>
   </si>
   <si>
     <t>7.4%</t>
@@ -158,7 +158,7 @@
     <t>PELOTAS</t>
   </si>
   <si>
-    <t>478,191</t>
+    <t>477,860</t>
   </si>
   <si>
     <t>5.5%</t>
@@ -167,7 +167,7 @@
     <t>PINTURA</t>
   </si>
   <si>
-    <t>1,246,008</t>
+    <t>1,245,981</t>
   </si>
   <si>
     <t>14.5%</t>
@@ -10217,13 +10217,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="6">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="7">
-        <v>245</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10" ht="25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -10679,7 +10679,7 @@
         <v>48</v>
       </c>
       <c r="F9" s="34">
-        <v>2039</v>
+        <v>2036</v>
       </c>
       <c r="G9" s="35" t="s">
         <v>69</v>
@@ -10725,7 +10725,7 @@
         <v>96</v>
       </c>
       <c r="F11" s="36">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G11" s="37" t="s">
         <v>109</v>
@@ -10748,7 +10748,7 @@
         <v>96</v>
       </c>
       <c r="F12" s="36">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G12" s="37" t="s">
         <v>109</v>
@@ -10771,7 +10771,7 @@
         <v>96</v>
       </c>
       <c r="F13" s="34">
-        <v>1737</v>
+        <v>1735</v>
       </c>
       <c r="G13" s="35" t="s">
         <v>69</v>
@@ -10886,7 +10886,7 @@
         <v>288</v>
       </c>
       <c r="F18" s="36">
-        <v>854</v>
+        <v>842</v>
       </c>
       <c r="G18" s="37" t="s">
         <v>109</v>
@@ -11481,7 +11481,7 @@
         <v>192</v>
       </c>
       <c r="F12" s="34">
-        <v>38568</v>
+        <v>38556</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>69</v>
@@ -11504,7 +11504,7 @@
         <v>576</v>
       </c>
       <c r="F13" s="34">
-        <v>92920</v>
+        <v>92896</v>
       </c>
       <c r="G13" s="35" t="s">
         <v>69</v>
@@ -11527,7 +11527,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="34">
-        <v>91858</v>
+        <v>91846</v>
       </c>
       <c r="G14" s="35" t="s">
         <v>69</v>
@@ -11550,7 +11550,7 @@
         <v>24</v>
       </c>
       <c r="F15" s="34">
-        <v>12961</v>
+        <v>12937</v>
       </c>
       <c r="G15" s="35" t="s">
         <v>69</v>
@@ -11573,7 +11573,7 @@
         <v>48</v>
       </c>
       <c r="F16" s="34">
-        <v>16266</v>
+        <v>16218</v>
       </c>
       <c r="G16" s="35" t="s">
         <v>69</v>
@@ -11915,7 +11915,7 @@
         <v>24</v>
       </c>
       <c r="F8" s="34">
-        <v>4742</v>
+        <v>4741</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>69</v>
@@ -11961,7 +11961,7 @@
         <v>24</v>
       </c>
       <c r="F10" s="34">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="G10" s="35" t="s">
         <v>69</v>
@@ -11984,7 +11984,7 @@
         <v>24</v>
       </c>
       <c r="F11" s="34">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G11" s="35" t="s">
         <v>69</v>
@@ -12007,7 +12007,7 @@
         <v>24</v>
       </c>
       <c r="F12" s="34">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>69</v>
@@ -12030,7 +12030,7 @@
         <v>24</v>
       </c>
       <c r="F13" s="34">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G13" s="35" t="s">
         <v>69</v>
@@ -12214,7 +12214,7 @@
         <v>36</v>
       </c>
       <c r="F21" s="34">
-        <v>8229</v>
+        <v>8227</v>
       </c>
       <c r="G21" s="35" t="s">
         <v>69</v>
@@ -12237,7 +12237,7 @@
         <v>36</v>
       </c>
       <c r="F22" s="34">
-        <v>1330</v>
+        <v>1326</v>
       </c>
       <c r="G22" s="35" t="s">
         <v>69</v>
@@ -12513,7 +12513,7 @@
         <v>50</v>
       </c>
       <c r="F34" s="34">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="G34" s="35" t="s">
         <v>69</v>
@@ -12536,7 +12536,7 @@
         <v>50</v>
       </c>
       <c r="F35" s="34">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="G35" s="35" t="s">
         <v>69</v>
@@ -12559,7 +12559,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="34">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="G36" s="35" t="s">
         <v>69</v>
@@ -12697,7 +12697,7 @@
         <v>48</v>
       </c>
       <c r="F42" s="36">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="G42" s="37" t="s">
         <v>109</v>
@@ -12743,7 +12743,7 @@
         <v>48</v>
       </c>
       <c r="F44" s="34">
-        <v>6524</v>
+        <v>6500</v>
       </c>
       <c r="G44" s="35" t="s">
         <v>69</v>
@@ -12812,7 +12812,7 @@
         <v>48</v>
       </c>
       <c r="F47" s="34">
-        <v>11965</v>
+        <v>11943</v>
       </c>
       <c r="G47" s="35" t="s">
         <v>69</v>
@@ -12881,7 +12881,7 @@
         <v>48</v>
       </c>
       <c r="F50" s="34">
-        <v>5578</v>
+        <v>5570</v>
       </c>
       <c r="G50" s="35" t="s">
         <v>69</v>
@@ -12927,7 +12927,7 @@
         <v>48</v>
       </c>
       <c r="F52" s="36">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="G52" s="37" t="s">
         <v>109</v>
@@ -12949,11 +12949,11 @@
       <c r="E53">
         <v>48</v>
       </c>
-      <c r="F53" s="36">
-        <v>1</v>
-      </c>
-      <c r="G53" s="37" t="s">
-        <v>109</v>
+      <c r="F53" s="32">
+        <v>0</v>
+      </c>
+      <c r="G53" s="33" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -13019,7 +13019,7 @@
         <v>36</v>
       </c>
       <c r="F56" s="34">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G56" s="35" t="s">
         <v>69</v>
@@ -13111,7 +13111,7 @@
         <v>36</v>
       </c>
       <c r="F60" s="34">
-        <v>1377</v>
+        <v>1375</v>
       </c>
       <c r="G60" s="35" t="s">
         <v>69</v>
@@ -13180,7 +13180,7 @@
         <v>36</v>
       </c>
       <c r="F63" s="34">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="G63" s="35" t="s">
         <v>69</v>
@@ -13272,7 +13272,7 @@
         <v>60</v>
       </c>
       <c r="F67" s="34">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="G67" s="35" t="s">
         <v>69</v>
@@ -13341,7 +13341,7 @@
         <v>60</v>
       </c>
       <c r="F70" s="34">
-        <v>4180</v>
+        <v>4179</v>
       </c>
       <c r="G70" s="35" t="s">
         <v>69</v>
@@ -13364,7 +13364,7 @@
         <v>60</v>
       </c>
       <c r="F71" s="34">
-        <v>5085</v>
+        <v>5084</v>
       </c>
       <c r="G71" s="35" t="s">
         <v>69</v>
@@ -13410,7 +13410,7 @@
         <v>60</v>
       </c>
       <c r="F73" s="34">
-        <v>3198</v>
+        <v>3194</v>
       </c>
       <c r="G73" s="35" t="s">
         <v>69</v>
@@ -13433,7 +13433,7 @@
         <v>60</v>
       </c>
       <c r="F74" s="34">
-        <v>1302</v>
+        <v>1299</v>
       </c>
       <c r="G74" s="35" t="s">
         <v>69</v>
@@ -13479,7 +13479,7 @@
         <v>60</v>
       </c>
       <c r="F76" s="34">
-        <v>8596</v>
+        <v>8593</v>
       </c>
       <c r="G76" s="35" t="s">
         <v>69</v>
@@ -13525,7 +13525,7 @@
         <v>60</v>
       </c>
       <c r="F78" s="34">
-        <v>6465</v>
+        <v>6449</v>
       </c>
       <c r="G78" s="35" t="s">
         <v>69</v>
@@ -13571,7 +13571,7 @@
         <v>60</v>
       </c>
       <c r="F80" s="36">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G80" s="37" t="s">
         <v>109</v>
@@ -13732,7 +13732,7 @@
         <v>60</v>
       </c>
       <c r="F87" s="34">
-        <v>1531</v>
+        <v>1522</v>
       </c>
       <c r="G87" s="35" t="s">
         <v>69</v>
@@ -13801,7 +13801,7 @@
         <v>60</v>
       </c>
       <c r="F90" s="34">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="G90" s="35" t="s">
         <v>69</v>
@@ -13847,7 +13847,7 @@
         <v>60</v>
       </c>
       <c r="F92" s="34">
-        <v>1372</v>
+        <v>1369</v>
       </c>
       <c r="G92" s="35" t="s">
         <v>69</v>
@@ -13870,7 +13870,7 @@
         <v>60</v>
       </c>
       <c r="F93" s="34">
-        <v>1251</v>
+        <v>1240</v>
       </c>
       <c r="G93" s="35" t="s">
         <v>69</v>
@@ -13893,7 +13893,7 @@
         <v>60</v>
       </c>
       <c r="F94" s="34">
-        <v>1399</v>
+        <v>1390</v>
       </c>
       <c r="G94" s="35" t="s">
         <v>69</v>
@@ -13985,7 +13985,7 @@
         <v>60</v>
       </c>
       <c r="F98" s="34">
-        <v>3434</v>
+        <v>3432</v>
       </c>
       <c r="G98" s="35" t="s">
         <v>69</v>
@@ -14008,7 +14008,7 @@
         <v>60</v>
       </c>
       <c r="F99" s="34">
-        <v>3915</v>
+        <v>3914</v>
       </c>
       <c r="G99" s="35" t="s">
         <v>69</v>
@@ -14031,7 +14031,7 @@
         <v>60</v>
       </c>
       <c r="F100" s="34">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="G100" s="35" t="s">
         <v>69</v>
@@ -14054,7 +14054,7 @@
         <v>60</v>
       </c>
       <c r="F101" s="34">
-        <v>5802</v>
+        <v>5801</v>
       </c>
       <c r="G101" s="35" t="s">
         <v>69</v>
@@ -14077,7 +14077,7 @@
         <v>60</v>
       </c>
       <c r="F102" s="34">
-        <v>3253</v>
+        <v>3252</v>
       </c>
       <c r="G102" s="35" t="s">
         <v>69</v>
@@ -14192,7 +14192,7 @@
         <v>60</v>
       </c>
       <c r="F107" s="34">
-        <v>5594</v>
+        <v>5582</v>
       </c>
       <c r="G107" s="35" t="s">
         <v>69</v>
@@ -14238,7 +14238,7 @@
         <v>60</v>
       </c>
       <c r="F109" s="34">
-        <v>1725</v>
+        <v>1722</v>
       </c>
       <c r="G109" s="35" t="s">
         <v>69</v>
@@ -14261,7 +14261,7 @@
         <v>60</v>
       </c>
       <c r="F110" s="34">
-        <v>1887</v>
+        <v>1884</v>
       </c>
       <c r="G110" s="35" t="s">
         <v>69</v>
@@ -14284,7 +14284,7 @@
         <v>60</v>
       </c>
       <c r="F111" s="34">
-        <v>6130</v>
+        <v>6118</v>
       </c>
       <c r="G111" s="35" t="s">
         <v>69</v>
@@ -14307,7 +14307,7 @@
         <v>60</v>
       </c>
       <c r="F112" s="34">
-        <v>7112</v>
+        <v>7100</v>
       </c>
       <c r="G112" s="35" t="s">
         <v>69</v>
@@ -14353,7 +14353,7 @@
         <v>60</v>
       </c>
       <c r="F114" s="34">
-        <v>11151</v>
+        <v>11130</v>
       </c>
       <c r="G114" s="35" t="s">
         <v>69</v>
@@ -14583,7 +14583,7 @@
         <v>12</v>
       </c>
       <c r="F124" s="34">
-        <v>2515</v>
+        <v>2509</v>
       </c>
       <c r="G124" s="35" t="s">
         <v>69</v>
@@ -14629,7 +14629,7 @@
         <v>120</v>
       </c>
       <c r="F126" s="34">
-        <v>2200</v>
+        <v>2188</v>
       </c>
       <c r="G126" s="35" t="s">
         <v>69</v>
@@ -14698,7 +14698,7 @@
         <v>120</v>
       </c>
       <c r="F129" s="34">
-        <v>1067</v>
+        <v>1061</v>
       </c>
       <c r="G129" s="35" t="s">
         <v>69</v>
@@ -14744,7 +14744,7 @@
         <v>120</v>
       </c>
       <c r="F131" s="36">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="G131" s="37" t="s">
         <v>109</v>
@@ -14767,7 +14767,7 @@
         <v>120</v>
       </c>
       <c r="F132" s="36">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="G132" s="37" t="s">
         <v>109</v>
@@ -14950,11 +14950,11 @@
       <c r="E140">
         <v>120</v>
       </c>
-      <c r="F140" s="36">
-        <v>3</v>
-      </c>
-      <c r="G140" s="37" t="s">
-        <v>109</v>
+      <c r="F140" s="32">
+        <v>0</v>
+      </c>
+      <c r="G140" s="33" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
@@ -14997,7 +14997,7 @@
         <v>120</v>
       </c>
       <c r="F142" s="34">
-        <v>3364</v>
+        <v>3358</v>
       </c>
       <c r="G142" s="35" t="s">
         <v>69</v>
@@ -15020,7 +15020,7 @@
         <v>120</v>
       </c>
       <c r="F143" s="36">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="G143" s="37" t="s">
         <v>109</v>
@@ -15089,7 +15089,7 @@
         <v>60</v>
       </c>
       <c r="F146" s="34">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="G146" s="35" t="s">
         <v>69</v>
@@ -16032,7 +16032,7 @@
         <v>120</v>
       </c>
       <c r="F187" s="34">
-        <v>3620</v>
+        <v>3608</v>
       </c>
       <c r="G187" s="35" t="s">
         <v>69</v>
@@ -16055,7 +16055,7 @@
         <v>120</v>
       </c>
       <c r="F188" s="34">
-        <v>1816</v>
+        <v>1804</v>
       </c>
       <c r="G188" s="35" t="s">
         <v>69</v>
@@ -16305,7 +16305,7 @@
         <v>144</v>
       </c>
       <c r="F7" s="34">
-        <v>104351</v>
+        <v>104339</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>69</v>
@@ -16328,7 +16328,7 @@
         <v>72</v>
       </c>
       <c r="F8" s="34">
-        <v>15582</v>
+        <v>15579</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>69</v>
@@ -16995,7 +16995,7 @@
         <v>576</v>
       </c>
       <c r="F37" s="36">
-        <v>1469</v>
+        <v>1457</v>
       </c>
       <c r="G37" s="37" t="s">
         <v>109</v>
@@ -22601,7 +22601,7 @@
         <v>144</v>
       </c>
       <c r="F5" s="34">
-        <v>24538</v>
+        <v>24526</v>
       </c>
       <c r="G5" s="35" t="s">
         <v>69</v>
@@ -22624,7 +22624,7 @@
         <v>144</v>
       </c>
       <c r="F6" s="34">
-        <v>10280</v>
+        <v>10268</v>
       </c>
       <c r="G6" s="35" t="s">
         <v>69</v>
@@ -22670,7 +22670,7 @@
         <v>144</v>
       </c>
       <c r="F8" s="34">
-        <v>17903</v>
+        <v>17891</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>69</v>
@@ -22762,7 +22762,7 @@
         <v>36</v>
       </c>
       <c r="F12" s="34">
-        <v>3711</v>
+        <v>3709</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>69</v>
@@ -22808,7 +22808,7 @@
         <v>36</v>
       </c>
       <c r="F14" s="34">
-        <v>3130</v>
+        <v>3129</v>
       </c>
       <c r="G14" s="35" t="s">
         <v>69</v>
@@ -22854,7 +22854,7 @@
         <v>24</v>
       </c>
       <c r="F16" s="36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G16" s="37" t="s">
         <v>109</v>
@@ -22969,7 +22969,7 @@
         <v>40</v>
       </c>
       <c r="F21" s="34">
-        <v>35636</v>
+        <v>35635</v>
       </c>
       <c r="G21" s="35" t="s">
         <v>69</v>
@@ -22992,7 +22992,7 @@
         <v>36</v>
       </c>
       <c r="F22" s="34">
-        <v>15899</v>
+        <v>15898</v>
       </c>
       <c r="G22" s="35" t="s">
         <v>69</v>
@@ -23015,7 +23015,7 @@
         <v>60</v>
       </c>
       <c r="F23" s="34">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="G23" s="35" t="s">
         <v>69</v>
@@ -23038,7 +23038,7 @@
         <v>60</v>
       </c>
       <c r="F24" s="34">
-        <v>3515</v>
+        <v>3514</v>
       </c>
       <c r="G24" s="35" t="s">
         <v>69</v>
@@ -23061,7 +23061,7 @@
         <v>36</v>
       </c>
       <c r="F25" s="34">
-        <v>13017</v>
+        <v>13016</v>
       </c>
       <c r="G25" s="35" t="s">
         <v>69</v>
@@ -23130,7 +23130,7 @@
         <v>36</v>
       </c>
       <c r="F28" s="34">
-        <v>3656</v>
+        <v>3655</v>
       </c>
       <c r="G28" s="35" t="s">
         <v>69</v>
@@ -23153,7 +23153,7 @@
         <v>36</v>
       </c>
       <c r="F29" s="34">
-        <v>5347</v>
+        <v>5346</v>
       </c>
       <c r="G29" s="35" t="s">
         <v>69</v>
@@ -23176,7 +23176,7 @@
         <v>48</v>
       </c>
       <c r="F30" s="34">
-        <v>5915</v>
+        <v>5914</v>
       </c>
       <c r="G30" s="35" t="s">
         <v>69</v>
@@ -23199,7 +23199,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="34">
-        <v>157701</v>
+        <v>157665</v>
       </c>
       <c r="G31" s="35" t="s">
         <v>69</v>
@@ -23245,7 +23245,7 @@
         <v>120</v>
       </c>
       <c r="F33" s="34">
-        <v>40364</v>
+        <v>40352</v>
       </c>
       <c r="G33" s="35" t="s">
         <v>69</v>
@@ -23337,7 +23337,7 @@
         <v>120</v>
       </c>
       <c r="F37" s="34">
-        <v>11422</v>
+        <v>11410</v>
       </c>
       <c r="G37" s="35" t="s">
         <v>69</v>
@@ -23360,7 +23360,7 @@
         <v>120</v>
       </c>
       <c r="F38" s="34">
-        <v>101264</v>
+        <v>101258</v>
       </c>
       <c r="G38" s="35" t="s">
         <v>69</v>
@@ -23383,7 +23383,7 @@
         <v>120</v>
       </c>
       <c r="F39" s="34">
-        <v>16352</v>
+        <v>16346</v>
       </c>
       <c r="G39" s="35" t="s">
         <v>69</v>
@@ -23429,7 +23429,7 @@
         <v>144</v>
       </c>
       <c r="F41" s="34">
-        <v>7758</v>
+        <v>7743</v>
       </c>
       <c r="G41" s="35" t="s">
         <v>69</v>
@@ -23567,7 +23567,7 @@
         <v>144</v>
       </c>
       <c r="F47" s="34">
-        <v>4057</v>
+        <v>4054</v>
       </c>
       <c r="G47" s="35" t="s">
         <v>69</v>
@@ -23682,7 +23682,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="34">
-        <v>6599</v>
+        <v>6596</v>
       </c>
       <c r="G52" s="35" t="s">
         <v>69</v>
@@ -24783,7 +24783,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="34">
-        <v>46880</v>
+        <v>46870</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>69</v>
@@ -24829,7 +24829,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="34">
-        <v>15008</v>
+        <v>14958</v>
       </c>
       <c r="G5" s="35" t="s">
         <v>69</v>
@@ -25266,7 +25266,7 @@
         <v>50</v>
       </c>
       <c r="F24" s="34">
-        <v>49742</v>
+        <v>49692</v>
       </c>
       <c r="G24" s="35" t="s">
         <v>69</v>
@@ -26393,7 +26393,7 @@
         <v>100</v>
       </c>
       <c r="F73" s="34">
-        <v>16599</v>
+        <v>16574</v>
       </c>
       <c r="G73" s="35" t="s">
         <v>69</v>
@@ -26416,7 +26416,7 @@
         <v>100</v>
       </c>
       <c r="F74" s="34">
-        <v>47058</v>
+        <v>47033</v>
       </c>
       <c r="G74" s="35" t="s">
         <v>69</v>
@@ -26715,7 +26715,7 @@
         <v>100</v>
       </c>
       <c r="F87" s="34">
-        <v>8930</v>
+        <v>8925</v>
       </c>
       <c r="G87" s="35" t="s">
         <v>69</v>
@@ -26738,7 +26738,7 @@
         <v>100</v>
       </c>
       <c r="F88" s="34">
-        <v>6513</v>
+        <v>6508</v>
       </c>
       <c r="G88" s="35" t="s">
         <v>69</v>
@@ -26761,7 +26761,7 @@
         <v>100</v>
       </c>
       <c r="F89" s="34">
-        <v>12755</v>
+        <v>12750</v>
       </c>
       <c r="G89" s="35" t="s">
         <v>69</v>
@@ -26784,7 +26784,7 @@
         <v>100</v>
       </c>
       <c r="F90" s="34">
-        <v>7711</v>
+        <v>7706</v>
       </c>
       <c r="G90" s="35" t="s">
         <v>69</v>
@@ -26807,7 +26807,7 @@
         <v>100</v>
       </c>
       <c r="F91" s="34">
-        <v>7789</v>
+        <v>7784</v>
       </c>
       <c r="G91" s="35" t="s">
         <v>69</v>
@@ -26830,7 +26830,7 @@
         <v>100</v>
       </c>
       <c r="F92" s="34">
-        <v>940</v>
+        <v>935</v>
       </c>
       <c r="G92" s="35" t="s">
         <v>69</v>
@@ -26853,7 +26853,7 @@
         <v>100</v>
       </c>
       <c r="F93" s="34">
-        <v>11171</v>
+        <v>11166</v>
       </c>
       <c r="G93" s="35" t="s">
         <v>69</v>
@@ -26876,7 +26876,7 @@
         <v>100</v>
       </c>
       <c r="F94" s="34">
-        <v>2807</v>
+        <v>2802</v>
       </c>
       <c r="G94" s="35" t="s">
         <v>69</v>
@@ -26899,7 +26899,7 @@
         <v>100</v>
       </c>
       <c r="F95" s="34">
-        <v>6808</v>
+        <v>6803</v>
       </c>
       <c r="G95" s="35" t="s">
         <v>69</v>
@@ -26922,7 +26922,7 @@
         <v>100</v>
       </c>
       <c r="F96" s="34">
-        <v>15318</v>
+        <v>15313</v>
       </c>
       <c r="G96" s="35" t="s">
         <v>69</v>
@@ -26945,7 +26945,7 @@
         <v>120</v>
       </c>
       <c r="F97" s="34">
-        <v>2489</v>
+        <v>2487</v>
       </c>
       <c r="G97" s="35" t="s">
         <v>69</v>
@@ -26968,7 +26968,7 @@
         <v>120</v>
       </c>
       <c r="F98" s="36">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G98" s="37" t="s">
         <v>109</v>
@@ -26991,7 +26991,7 @@
         <v>120</v>
       </c>
       <c r="F99" s="34">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="G99" s="35" t="s">
         <v>69</v>
@@ -27014,7 +27014,7 @@
         <v>120</v>
       </c>
       <c r="F100" s="34">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="G100" s="35" t="s">
         <v>69</v>
@@ -27037,7 +27037,7 @@
         <v>120</v>
       </c>
       <c r="F101" s="36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G101" s="37" t="s">
         <v>109</v>
@@ -27336,7 +27336,7 @@
         <v>24</v>
       </c>
       <c r="F114" s="34">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="G114" s="35" t="s">
         <v>69</v>
@@ -27381,11 +27381,11 @@
       <c r="E116">
         <v>24</v>
       </c>
-      <c r="F116" s="36">
-        <v>3</v>
-      </c>
-      <c r="G116" s="37" t="s">
-        <v>109</v>
+      <c r="F116" s="32">
+        <v>0</v>
+      </c>
+      <c r="G116" s="33" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
@@ -27428,7 +27428,7 @@
         <v>24</v>
       </c>
       <c r="F118" s="34">
-        <v>2188</v>
+        <v>2182</v>
       </c>
       <c r="G118" s="35" t="s">
         <v>69</v>
@@ -27474,7 +27474,7 @@
         <v>24</v>
       </c>
       <c r="F120" s="34">
-        <v>28796</v>
+        <v>28793</v>
       </c>
       <c r="G120" s="35" t="s">
         <v>69</v>
@@ -27520,7 +27520,7 @@
         <v>24</v>
       </c>
       <c r="F122" s="34">
-        <v>3714</v>
+        <v>3713</v>
       </c>
       <c r="G122" s="35" t="s">
         <v>69</v>
@@ -27543,7 +27543,7 @@
         <v>24</v>
       </c>
       <c r="F123" s="34">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="G123" s="35" t="s">
         <v>69</v>
@@ -27566,7 +27566,7 @@
         <v>24</v>
       </c>
       <c r="F124" s="34">
-        <v>8130</v>
+        <v>8129</v>
       </c>
       <c r="G124" s="35" t="s">
         <v>69</v>
@@ -27635,7 +27635,7 @@
         <v>24</v>
       </c>
       <c r="F127" s="36">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G127" s="37" t="s">
         <v>109</v>
@@ -29590,7 +29590,7 @@
         <v>720</v>
       </c>
       <c r="F212" s="34">
-        <v>4603</v>
+        <v>4601</v>
       </c>
       <c r="G212" s="35" t="s">
         <v>69</v>
@@ -29613,7 +29613,7 @@
         <v>720</v>
       </c>
       <c r="F213" s="36">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="G213" s="37" t="s">
         <v>109</v>
@@ -29636,7 +29636,7 @@
         <v>720</v>
       </c>
       <c r="F214" s="34">
-        <v>3947</v>
+        <v>3945</v>
       </c>
       <c r="G214" s="35" t="s">
         <v>69</v>
@@ -30579,7 +30579,7 @@
         <v>100</v>
       </c>
       <c r="F255" s="34">
-        <v>211699</v>
+        <v>211687</v>
       </c>
       <c r="G255" s="35" t="s">
         <v>69</v>
@@ -31128,7 +31128,7 @@
         <v>500</v>
       </c>
       <c r="F12" s="34">
-        <v>15306</v>
+        <v>15281</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>69</v>
@@ -31309,7 +31309,7 @@
         <v>12</v>
       </c>
       <c r="F2" s="34">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="G2" s="35" t="s">
         <v>69</v>
@@ -31332,7 +31332,7 @@
         <v>12</v>
       </c>
       <c r="F3" s="34">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>69</v>
@@ -31355,7 +31355,7 @@
         <v>12</v>
       </c>
       <c r="F4" s="34">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="G4" s="35" t="s">
         <v>69</v>
@@ -31378,7 +31378,7 @@
         <v>12</v>
       </c>
       <c r="F5" s="34">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="G5" s="35" t="s">
         <v>69</v>
@@ -31401,7 +31401,7 @@
         <v>24</v>
       </c>
       <c r="F6" s="34">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="G6" s="35" t="s">
         <v>69</v>
@@ -31838,7 +31838,7 @@
         <v>24</v>
       </c>
       <c r="F25" s="34">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="G25" s="35" t="s">
         <v>69</v>
@@ -31907,7 +31907,7 @@
         <v>12</v>
       </c>
       <c r="F28" s="34">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="G28" s="35" t="s">
         <v>69</v>
@@ -31930,7 +31930,7 @@
         <v>12</v>
       </c>
       <c r="F29" s="34">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="G29" s="35" t="s">
         <v>69</v>
@@ -32341,7 +32341,7 @@
         <v>96</v>
       </c>
       <c r="F14" s="34">
-        <v>9351</v>
+        <v>9345</v>
       </c>
       <c r="G14" s="35" t="s">
         <v>69</v>
@@ -32364,7 +32364,7 @@
         <v>96</v>
       </c>
       <c r="F15" s="34">
-        <v>7656</v>
+        <v>7647</v>
       </c>
       <c r="G15" s="35" t="s">
         <v>69</v>
@@ -32525,7 +32525,7 @@
         <v>192</v>
       </c>
       <c r="F22" s="34">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="G22" s="35" t="s">
         <v>69</v>
@@ -32547,11 +32547,11 @@
       <c r="E23">
         <v>192</v>
       </c>
-      <c r="F23" s="36">
-        <v>3</v>
-      </c>
-      <c r="G23" s="37" t="s">
-        <v>109</v>
+      <c r="F23" s="32">
+        <v>0</v>
+      </c>
+      <c r="G23" s="33" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -32571,7 +32571,7 @@
         <v>96</v>
       </c>
       <c r="F24" s="34">
-        <v>3521</v>
+        <v>3512</v>
       </c>
       <c r="G24" s="35" t="s">
         <v>69</v>
@@ -32686,7 +32686,7 @@
         <v>192</v>
       </c>
       <c r="F29" s="34">
-        <v>13784</v>
+        <v>13781</v>
       </c>
       <c r="G29" s="35" t="s">
         <v>69</v>
@@ -32732,7 +32732,7 @@
         <v>96</v>
       </c>
       <c r="F31" s="34">
-        <v>11907</v>
+        <v>11901</v>
       </c>
       <c r="G31" s="35" t="s">
         <v>69</v>
@@ -33215,7 +33215,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="34">
-        <v>7073</v>
+        <v>7067</v>
       </c>
       <c r="G52" s="35" t="s">
         <v>69</v>
@@ -33238,7 +33238,7 @@
         <v>96</v>
       </c>
       <c r="F53" s="34">
-        <v>14694</v>
+        <v>14685</v>
       </c>
       <c r="G53" s="35" t="s">
         <v>69</v>
@@ -33767,7 +33767,7 @@
         <v>200</v>
       </c>
       <c r="F76" s="34">
-        <v>61218</v>
+        <v>61188</v>
       </c>
       <c r="G76" s="35" t="s">
         <v>69</v>
@@ -33836,7 +33836,7 @@
         <v>200</v>
       </c>
       <c r="F79" s="34">
-        <v>1865</v>
+        <v>1855</v>
       </c>
       <c r="G79" s="35" t="s">
         <v>69</v>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -29,7 +29,7 @@
     <t>STOCKPULSE - RESUMEN</t>
   </si>
   <si>
-    <t>Actualización: 09/03/2026, 07:55:17</t>
+    <t>Actualización: 09/03/2026, 09:29:49</t>
   </si>
   <si>
     <t>TOTAL GENERAL</t>
@@ -41,7 +41,7 @@
     <t>Unidades:</t>
   </si>
   <si>
-    <t>8,617,846</t>
+    <t>8,618,146</t>
   </si>
   <si>
     <t>Agotados:</t>
@@ -158,7 +158,7 @@
     <t>PELOTAS</t>
   </si>
   <si>
-    <t>477,860</t>
+    <t>478,160</t>
   </si>
   <si>
     <t>5.5%</t>
@@ -12996,7 +12996,7 @@
         <v>36</v>
       </c>
       <c r="F55" s="34">
-        <v>1955</v>
+        <v>2255</v>
       </c>
       <c r="G55" s="35" t="s">
         <v>69</v>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -29,7 +29,7 @@
     <t>STOCKPULSE - RESUMEN</t>
   </si>
   <si>
-    <t>Actualización: 09/03/2026, 09:51:53</t>
+    <t>Actualización: 09/03/2026, 10:58:36</t>
   </si>
   <si>
     <t>TOTAL GENERAL</t>
@@ -41,7 +41,7 @@
     <t>Unidades:</t>
   </si>
   <si>
-    <t>8,618,135</t>
+    <t>8,578,043</t>
   </si>
   <si>
     <t>Agotados:</t>
@@ -68,7 +68,7 @@
     <t>ACCESORIOS</t>
   </si>
   <si>
-    <t>983,739</t>
+    <t>978,767</t>
   </si>
   <si>
     <t>11.4%</t>
@@ -77,7 +77,7 @@
     <t>ARCHIVO</t>
   </si>
   <si>
-    <t>1,770,138</t>
+    <t>1,756,455</t>
   </si>
   <si>
     <t>20.5%</t>
@@ -86,7 +86,7 @@
     <t>DIBUJO</t>
   </si>
   <si>
-    <t>121,824</t>
+    <t>118,449</t>
   </si>
   <si>
     <t>1.4%</t>
@@ -104,7 +104,7 @@
     <t>ESCRITURA</t>
   </si>
   <si>
-    <t>1,461,384</t>
+    <t>1,456,272</t>
   </si>
   <si>
     <t>17.0%</t>
@@ -113,10 +113,10 @@
     <t>FORROS</t>
   </si>
   <si>
-    <t>867,387</t>
-  </si>
-  <si>
-    <t>10.1%</t>
+    <t>858,809</t>
+  </si>
+  <si>
+    <t>10.0%</t>
   </si>
   <si>
     <t>MANUALIDADES</t>
@@ -140,7 +140,7 @@
     <t>METALICA</t>
   </si>
   <si>
-    <t>261,148</t>
+    <t>260,848</t>
   </si>
   <si>
     <t>3.0%</t>
@@ -149,7 +149,7 @@
     <t>PEGAMENTOS</t>
   </si>
   <si>
-    <t>634,542</t>
+    <t>632,170</t>
   </si>
   <si>
     <t>7.4%</t>
@@ -158,16 +158,16 @@
     <t>PELOTAS</t>
   </si>
   <si>
-    <t>478,160</t>
-  </si>
-  <si>
-    <t>5.5%</t>
+    <t>477,986</t>
+  </si>
+  <si>
+    <t>5.6%</t>
   </si>
   <si>
     <t>PINTURA</t>
   </si>
   <si>
-    <t>1,245,977</t>
+    <t>1,245,181</t>
   </si>
   <si>
     <t>14.5%</t>
@@ -176,7 +176,7 @@
     <t>REPRESENTADAS</t>
   </si>
   <si>
-    <t>320,477</t>
+    <t>319,747</t>
   </si>
   <si>
     <t>3.7%</t>
@@ -10217,7 +10217,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="6">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>7</v>
@@ -10886,7 +10886,7 @@
         <v>288</v>
       </c>
       <c r="F18" s="36">
-        <v>842</v>
+        <v>542</v>
       </c>
       <c r="G18" s="37" t="s">
         <v>109</v>
@@ -11527,7 +11527,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="34">
-        <v>91846</v>
+        <v>91774</v>
       </c>
       <c r="G14" s="35" t="s">
         <v>69</v>
@@ -11550,7 +11550,7 @@
         <v>24</v>
       </c>
       <c r="F15" s="34">
-        <v>12937</v>
+        <v>10937</v>
       </c>
       <c r="G15" s="35" t="s">
         <v>69</v>
@@ -11573,7 +11573,7 @@
         <v>48</v>
       </c>
       <c r="F16" s="34">
-        <v>16216</v>
+        <v>15916</v>
       </c>
       <c r="G16" s="35" t="s">
         <v>69</v>
@@ -12075,11 +12075,11 @@
       <c r="E15">
         <v>36</v>
       </c>
-      <c r="F15" s="36">
-        <v>1</v>
-      </c>
-      <c r="G15" s="37" t="s">
-        <v>109</v>
+      <c r="F15" s="32">
+        <v>0</v>
+      </c>
+      <c r="G15" s="33" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -12674,7 +12674,7 @@
         <v>48</v>
       </c>
       <c r="F41" s="36">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G41" s="37" t="s">
         <v>109</v>
@@ -12743,7 +12743,7 @@
         <v>48</v>
       </c>
       <c r="F44" s="34">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="G44" s="35" t="s">
         <v>69</v>
@@ -12812,7 +12812,7 @@
         <v>48</v>
       </c>
       <c r="F47" s="34">
-        <v>11943</v>
+        <v>11847</v>
       </c>
       <c r="G47" s="35" t="s">
         <v>69</v>
@@ -12996,7 +12996,7 @@
         <v>36</v>
       </c>
       <c r="F55" s="34">
-        <v>2255</v>
+        <v>2218</v>
       </c>
       <c r="G55" s="35" t="s">
         <v>69</v>
@@ -13018,11 +13018,11 @@
       <c r="E56">
         <v>36</v>
       </c>
-      <c r="F56" s="34">
-        <v>195</v>
-      </c>
-      <c r="G56" s="35" t="s">
-        <v>69</v>
+      <c r="F56" s="36">
+        <v>159</v>
+      </c>
+      <c r="G56" s="37" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -14169,7 +14169,7 @@
         <v>60</v>
       </c>
       <c r="F106" s="34">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="G106" s="35" t="s">
         <v>69</v>
@@ -14192,7 +14192,7 @@
         <v>60</v>
       </c>
       <c r="F107" s="34">
-        <v>5582</v>
+        <v>5577</v>
       </c>
       <c r="G107" s="35" t="s">
         <v>69</v>
@@ -14215,7 +14215,7 @@
         <v>60</v>
       </c>
       <c r="F108" s="34">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="G108" s="35" t="s">
         <v>69</v>
@@ -14238,7 +14238,7 @@
         <v>60</v>
       </c>
       <c r="F109" s="34">
-        <v>1722</v>
+        <v>1728</v>
       </c>
       <c r="G109" s="35" t="s">
         <v>69</v>
@@ -14261,7 +14261,7 @@
         <v>60</v>
       </c>
       <c r="F110" s="34">
-        <v>1884</v>
+        <v>1889</v>
       </c>
       <c r="G110" s="35" t="s">
         <v>69</v>
@@ -14284,7 +14284,7 @@
         <v>60</v>
       </c>
       <c r="F111" s="34">
-        <v>6118</v>
+        <v>6114</v>
       </c>
       <c r="G111" s="35" t="s">
         <v>69</v>
@@ -14307,7 +14307,7 @@
         <v>60</v>
       </c>
       <c r="F112" s="34">
-        <v>7100</v>
+        <v>7097</v>
       </c>
       <c r="G112" s="35" t="s">
         <v>69</v>
@@ -14330,7 +14330,7 @@
         <v>60</v>
       </c>
       <c r="F113" s="34">
-        <v>6610</v>
+        <v>6609</v>
       </c>
       <c r="G113" s="35" t="s">
         <v>69</v>
@@ -14491,7 +14491,7 @@
         <v>36</v>
       </c>
       <c r="F120" s="34">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G120" s="35" t="s">
         <v>69</v>
@@ -14583,7 +14583,7 @@
         <v>12</v>
       </c>
       <c r="F124" s="34">
-        <v>2509</v>
+        <v>2508</v>
       </c>
       <c r="G124" s="35" t="s">
         <v>69</v>
@@ -16305,7 +16305,7 @@
         <v>144</v>
       </c>
       <c r="F7" s="34">
-        <v>104339</v>
+        <v>104051</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>69</v>
@@ -16328,7 +16328,7 @@
         <v>72</v>
       </c>
       <c r="F8" s="34">
-        <v>15578</v>
+        <v>15506</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>69</v>
@@ -16374,7 +16374,7 @@
         <v>18</v>
       </c>
       <c r="F10" s="34">
-        <v>2060</v>
+        <v>2024</v>
       </c>
       <c r="G10" s="35" t="s">
         <v>69</v>
@@ -17800,7 +17800,7 @@
         <v>144</v>
       </c>
       <c r="F72" s="34">
-        <v>6387</v>
+        <v>6187</v>
       </c>
       <c r="G72" s="35" t="s">
         <v>69</v>
@@ -17823,7 +17823,7 @@
         <v>144</v>
       </c>
       <c r="F73" s="34">
-        <v>4504</v>
+        <v>4404</v>
       </c>
       <c r="G73" s="35" t="s">
         <v>69</v>
@@ -17846,7 +17846,7 @@
         <v>144</v>
       </c>
       <c r="F74" s="34">
-        <v>10923</v>
+        <v>10823</v>
       </c>
       <c r="G74" s="35" t="s">
         <v>69</v>
@@ -17981,7 +17981,7 @@
         <v>30</v>
       </c>
       <c r="F2" s="34">
-        <v>6770</v>
+        <v>6590</v>
       </c>
       <c r="G2" s="35" t="s">
         <v>69</v>
@@ -18004,7 +18004,7 @@
         <v>80</v>
       </c>
       <c r="F3" s="34">
-        <v>27406</v>
+        <v>27106</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>69</v>
@@ -18050,7 +18050,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="34">
-        <v>20889</v>
+        <v>20689</v>
       </c>
       <c r="G5" s="35" t="s">
         <v>69</v>
@@ -19821,7 +19821,7 @@
         <v>40</v>
       </c>
       <c r="F82" s="34">
-        <v>2766</v>
+        <v>2716</v>
       </c>
       <c r="G82" s="35" t="s">
         <v>69</v>
@@ -22578,7 +22578,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="34">
-        <v>11531</v>
+        <v>11431</v>
       </c>
       <c r="G4" s="35" t="s">
         <v>69</v>
@@ -22946,7 +22946,7 @@
         <v>36</v>
       </c>
       <c r="F20" s="34">
-        <v>5426</v>
+        <v>5384</v>
       </c>
       <c r="G20" s="35" t="s">
         <v>69</v>
@@ -23015,7 +23015,7 @@
         <v>60</v>
       </c>
       <c r="F23" s="34">
-        <v>708</v>
+        <v>666</v>
       </c>
       <c r="G23" s="35" t="s">
         <v>69</v>
@@ -23199,7 +23199,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="34">
-        <v>157665</v>
+        <v>155937</v>
       </c>
       <c r="G31" s="35" t="s">
         <v>69</v>
@@ -23337,7 +23337,7 @@
         <v>120</v>
       </c>
       <c r="F37" s="34">
-        <v>11410</v>
+        <v>11290</v>
       </c>
       <c r="G37" s="35" t="s">
         <v>69</v>
@@ -23429,7 +23429,7 @@
         <v>144</v>
       </c>
       <c r="F41" s="34">
-        <v>7742</v>
+        <v>7442</v>
       </c>
       <c r="G41" s="35" t="s">
         <v>69</v>
@@ -23682,7 +23682,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="34">
-        <v>6596</v>
+        <v>6496</v>
       </c>
       <c r="G52" s="35" t="s">
         <v>69</v>
@@ -23958,7 +23958,7 @@
         <v>120</v>
       </c>
       <c r="F64" s="34">
-        <v>7640</v>
+        <v>7340</v>
       </c>
       <c r="G64" s="35" t="s">
         <v>69</v>
@@ -24211,7 +24211,7 @@
         <v>240</v>
       </c>
       <c r="F75" s="34">
-        <v>9747</v>
+        <v>9447</v>
       </c>
       <c r="G75" s="35" t="s">
         <v>69</v>
@@ -24395,7 +24395,7 @@
         <v>144</v>
       </c>
       <c r="F83" s="34">
-        <v>8199</v>
+        <v>7739</v>
       </c>
       <c r="G83" s="35" t="s">
         <v>69</v>
@@ -24464,7 +24464,7 @@
         <v>144</v>
       </c>
       <c r="F86" s="34">
-        <v>26114</v>
+        <v>25754</v>
       </c>
       <c r="G86" s="35" t="s">
         <v>69</v>
@@ -24510,7 +24510,7 @@
         <v>144</v>
       </c>
       <c r="F88" s="34">
-        <v>8455</v>
+        <v>8155</v>
       </c>
       <c r="G88" s="35" t="s">
         <v>69</v>
@@ -24533,7 +24533,7 @@
         <v>144</v>
       </c>
       <c r="F89" s="34">
-        <v>7086</v>
+        <v>6626</v>
       </c>
       <c r="G89" s="35" t="s">
         <v>69</v>
@@ -24579,7 +24579,7 @@
         <v>144</v>
       </c>
       <c r="F91" s="34">
-        <v>12312</v>
+        <v>11952</v>
       </c>
       <c r="G91" s="35" t="s">
         <v>69</v>
@@ -24829,7 +24829,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="34">
-        <v>14958</v>
+        <v>11958</v>
       </c>
       <c r="G5" s="35" t="s">
         <v>69</v>
@@ -24875,7 +24875,7 @@
         <v>50</v>
       </c>
       <c r="F7" s="34">
-        <v>7989</v>
+        <v>7589</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>69</v>
@@ -24944,7 +24944,7 @@
         <v>50</v>
       </c>
       <c r="F10" s="34">
-        <v>14254</v>
+        <v>13954</v>
       </c>
       <c r="G10" s="35" t="s">
         <v>69</v>
@@ -25036,7 +25036,7 @@
         <v>50</v>
       </c>
       <c r="F14" s="34">
-        <v>471</v>
+        <v>321</v>
       </c>
       <c r="G14" s="35" t="s">
         <v>69</v>
@@ -25082,7 +25082,7 @@
         <v>50</v>
       </c>
       <c r="F16" s="34">
-        <v>5267</v>
+        <v>5117</v>
       </c>
       <c r="G16" s="35" t="s">
         <v>69</v>
@@ -25105,7 +25105,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="34">
-        <v>8332</v>
+        <v>8232</v>
       </c>
       <c r="G17" s="35" t="s">
         <v>69</v>
@@ -25128,7 +25128,7 @@
         <v>50</v>
       </c>
       <c r="F18" s="34">
-        <v>15919</v>
+        <v>15769</v>
       </c>
       <c r="G18" s="35" t="s">
         <v>69</v>
@@ -25197,7 +25197,7 @@
         <v>50</v>
       </c>
       <c r="F21" s="34">
-        <v>950</v>
+        <v>800</v>
       </c>
       <c r="G21" s="35" t="s">
         <v>69</v>
@@ -25266,7 +25266,7 @@
         <v>50</v>
       </c>
       <c r="F24" s="34">
-        <v>49692</v>
+        <v>47692</v>
       </c>
       <c r="G24" s="35" t="s">
         <v>69</v>
@@ -25496,7 +25496,7 @@
         <v>50</v>
       </c>
       <c r="F34" s="34">
-        <v>8524</v>
+        <v>8424</v>
       </c>
       <c r="G34" s="35" t="s">
         <v>69</v>
@@ -25588,7 +25588,7 @@
         <v>50</v>
       </c>
       <c r="F38" s="34">
-        <v>4621</v>
+        <v>4321</v>
       </c>
       <c r="G38" s="35" t="s">
         <v>69</v>
@@ -25611,7 +25611,7 @@
         <v>50</v>
       </c>
       <c r="F39" s="34">
-        <v>3223</v>
+        <v>2723</v>
       </c>
       <c r="G39" s="35" t="s">
         <v>69</v>
@@ -25657,7 +25657,7 @@
         <v>50</v>
       </c>
       <c r="F41" s="34">
-        <v>8844</v>
+        <v>8344</v>
       </c>
       <c r="G41" s="35" t="s">
         <v>69</v>
@@ -25726,7 +25726,7 @@
         <v>100</v>
       </c>
       <c r="F44" s="34">
-        <v>3439</v>
+        <v>3139</v>
       </c>
       <c r="G44" s="35" t="s">
         <v>69</v>
@@ -25795,7 +25795,7 @@
         <v>100</v>
       </c>
       <c r="F47" s="34">
-        <v>3213</v>
+        <v>2713</v>
       </c>
       <c r="G47" s="35" t="s">
         <v>69</v>
@@ -25841,7 +25841,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="34">
-        <v>1689</v>
+        <v>1189</v>
       </c>
       <c r="G49" s="35" t="s">
         <v>69</v>
@@ -25887,7 +25887,7 @@
         <v>100</v>
       </c>
       <c r="F51" s="34">
-        <v>1492</v>
+        <v>1192</v>
       </c>
       <c r="G51" s="35" t="s">
         <v>69</v>
@@ -25910,7 +25910,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="34">
-        <v>1217</v>
+        <v>817</v>
       </c>
       <c r="G52" s="35" t="s">
         <v>69</v>
@@ -25955,11 +25955,11 @@
       <c r="E54">
         <v>100</v>
       </c>
-      <c r="F54" s="34">
-        <v>751</v>
-      </c>
-      <c r="G54" s="35" t="s">
-        <v>69</v>
+      <c r="F54" s="36">
+        <v>451</v>
+      </c>
+      <c r="G54" s="37" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -26002,7 +26002,7 @@
         <v>100</v>
       </c>
       <c r="F56" s="34">
-        <v>6582</v>
+        <v>6082</v>
       </c>
       <c r="G56" s="35" t="s">
         <v>69</v>
@@ -26232,7 +26232,7 @@
         <v>50</v>
       </c>
       <c r="F66" s="34">
-        <v>784</v>
+        <v>584</v>
       </c>
       <c r="G66" s="35" t="s">
         <v>69</v>
@@ -26439,7 +26439,7 @@
         <v>100</v>
       </c>
       <c r="F75" s="34">
-        <v>23876</v>
+        <v>23176</v>
       </c>
       <c r="G75" s="35" t="s">
         <v>69</v>
@@ -26738,7 +26738,7 @@
         <v>100</v>
       </c>
       <c r="F88" s="34">
-        <v>6508</v>
+        <v>6308</v>
       </c>
       <c r="G88" s="35" t="s">
         <v>69</v>
@@ -26761,7 +26761,7 @@
         <v>100</v>
       </c>
       <c r="F89" s="34">
-        <v>12750</v>
+        <v>12650</v>
       </c>
       <c r="G89" s="35" t="s">
         <v>69</v>
@@ -26830,7 +26830,7 @@
         <v>100</v>
       </c>
       <c r="F92" s="34">
-        <v>935</v>
+        <v>835</v>
       </c>
       <c r="G92" s="35" t="s">
         <v>69</v>
@@ -26899,7 +26899,7 @@
         <v>100</v>
       </c>
       <c r="F95" s="34">
-        <v>6803</v>
+        <v>6503</v>
       </c>
       <c r="G95" s="35" t="s">
         <v>69</v>
@@ -26967,11 +26967,11 @@
       <c r="E98">
         <v>120</v>
       </c>
-      <c r="F98" s="36">
-        <v>25</v>
-      </c>
-      <c r="G98" s="37" t="s">
-        <v>109</v>
+      <c r="F98" s="32">
+        <v>0</v>
+      </c>
+      <c r="G98" s="33" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.25">
@@ -27014,7 +27014,7 @@
         <v>120</v>
       </c>
       <c r="F100" s="34">
-        <v>1440</v>
+        <v>1340</v>
       </c>
       <c r="G100" s="35" t="s">
         <v>69</v>
@@ -27543,7 +27543,7 @@
         <v>24</v>
       </c>
       <c r="F123" s="34">
-        <v>1462</v>
+        <v>1412</v>
       </c>
       <c r="G123" s="35" t="s">
         <v>69</v>
@@ -28118,7 +28118,7 @@
         <v>12</v>
       </c>
       <c r="F148" s="34">
-        <v>172</v>
+        <v>64</v>
       </c>
       <c r="G148" s="35" t="s">
         <v>69</v>
@@ -29199,7 +29199,7 @@
         <v>48</v>
       </c>
       <c r="F195" s="34">
-        <v>2132</v>
+        <v>1432</v>
       </c>
       <c r="G195" s="35" t="s">
         <v>69</v>
@@ -30602,7 +30602,7 @@
         <v>100</v>
       </c>
       <c r="F256" s="34">
-        <v>90955</v>
+        <v>90455</v>
       </c>
       <c r="G256" s="35" t="s">
         <v>69</v>
@@ -31036,7 +31036,7 @@
         <v>400</v>
       </c>
       <c r="F8" s="34">
-        <v>20598</v>
+        <v>17523</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>69</v>
@@ -31128,7 +31128,7 @@
         <v>500</v>
       </c>
       <c r="F12" s="34">
-        <v>15281</v>
+        <v>15181</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>69</v>
@@ -31220,7 +31220,7 @@
         <v>200</v>
       </c>
       <c r="F16" s="34">
-        <v>2947</v>
+        <v>2747</v>
       </c>
       <c r="G16" s="35" t="s">
         <v>69</v>
@@ -32387,7 +32387,7 @@
         <v>96</v>
       </c>
       <c r="F16" s="34">
-        <v>9675</v>
+        <v>9579</v>
       </c>
       <c r="G16" s="35" t="s">
         <v>69</v>
@@ -32433,7 +32433,7 @@
         <v>192</v>
       </c>
       <c r="F18" s="34">
-        <v>17198</v>
+        <v>17006</v>
       </c>
       <c r="G18" s="35" t="s">
         <v>69</v>
@@ -33261,7 +33261,7 @@
         <v>96</v>
       </c>
       <c r="F54" s="34">
-        <v>7579</v>
+        <v>7483</v>
       </c>
       <c r="G54" s="35" t="s">
         <v>69</v>
@@ -33284,7 +33284,7 @@
         <v>96</v>
       </c>
       <c r="F55" s="34">
-        <v>16418</v>
+        <v>16322</v>
       </c>
       <c r="G55" s="35" t="s">
         <v>69</v>
@@ -33905,7 +33905,7 @@
         <v>1152</v>
       </c>
       <c r="F82" s="34">
-        <v>64226</v>
+        <v>61922</v>
       </c>
       <c r="G82" s="35" t="s">
         <v>69</v>
@@ -33997,7 +33997,7 @@
         <v>576</v>
       </c>
       <c r="F86" s="34">
-        <v>20494</v>
+        <v>19918</v>
       </c>
       <c r="G86" s="35" t="s">
         <v>69</v>
@@ -34135,7 +34135,7 @@
         <v>576</v>
       </c>
       <c r="F92" s="34">
-        <v>5395</v>
+        <v>4243</v>
       </c>
       <c r="G92" s="35" t="s">
         <v>69</v>
@@ -34250,7 +34250,7 @@
         <v>288</v>
       </c>
       <c r="F97" s="34">
-        <v>25960</v>
+        <v>25660</v>
       </c>
       <c r="G97" s="35" t="s">
         <v>69</v>
@@ -34526,7 +34526,7 @@
         <v>192</v>
       </c>
       <c r="F109" s="34">
-        <v>20645</v>
+        <v>20445</v>
       </c>
       <c r="G109" s="35" t="s">
         <v>69</v>
@@ -34572,7 +34572,7 @@
         <v>192</v>
       </c>
       <c r="F111" s="34">
-        <v>25522</v>
+        <v>25422</v>
       </c>
       <c r="G111" s="35" t="s">
         <v>69</v>
@@ -35397,7 +35397,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="34">
-        <v>75321</v>
+        <v>74821</v>
       </c>
       <c r="G2" s="35" t="s">
         <v>69</v>
@@ -35420,7 +35420,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="34">
-        <v>217243</v>
+        <v>212993</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>69</v>
@@ -35489,7 +35489,7 @@
         <v>25</v>
       </c>
       <c r="F6" s="34">
-        <v>3627</v>
+        <v>1627</v>
       </c>
       <c r="G6" s="35" t="s">
         <v>69</v>
@@ -35535,7 +35535,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="34">
-        <v>70240</v>
+        <v>69808</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>69</v>
@@ -35558,7 +35558,7 @@
         <v>48</v>
       </c>
       <c r="F9" s="34">
-        <v>83953</v>
+        <v>83857</v>
       </c>
       <c r="G9" s="35" t="s">
         <v>69</v>
@@ -35581,7 +35581,7 @@
         <v>18</v>
       </c>
       <c r="F10" s="34">
-        <v>23800</v>
+        <v>22800</v>
       </c>
       <c r="G10" s="35" t="s">
         <v>69</v>
@@ -35604,7 +35604,7 @@
         <v>36</v>
       </c>
       <c r="F11" s="34">
-        <v>29904</v>
+        <v>29604</v>
       </c>
       <c r="G11" s="35" t="s">
         <v>69</v>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -29,7 +29,7 @@
     <t>STOCKPULSE - RESUMEN</t>
   </si>
   <si>
-    <t>Actualización: 09/03/2026, 10:58:36</t>
+    <t>Actualización: 09/03/2026, 12:03:34</t>
   </si>
   <si>
     <t>TOTAL GENERAL</t>
@@ -41,7 +41,7 @@
     <t>Unidades:</t>
   </si>
   <si>
-    <t>8,578,043</t>
+    <t>8,566,118</t>
   </si>
   <si>
     <t>Agotados:</t>
@@ -68,7 +68,7 @@
     <t>ACCESORIOS</t>
   </si>
   <si>
-    <t>978,767</t>
+    <t>975,707</t>
   </si>
   <si>
     <t>11.4%</t>
@@ -77,7 +77,7 @@
     <t>ARCHIVO</t>
   </si>
   <si>
-    <t>1,756,455</t>
+    <t>1,755,340</t>
   </si>
   <si>
     <t>20.5%</t>
@@ -104,7 +104,7 @@
     <t>ESCRITURA</t>
   </si>
   <si>
-    <t>1,456,272</t>
+    <t>1,453,700</t>
   </si>
   <si>
     <t>17.0%</t>
@@ -113,7 +113,7 @@
     <t>FORROS</t>
   </si>
   <si>
-    <t>858,809</t>
+    <t>854,459</t>
   </si>
   <si>
     <t>10.0%</t>
@@ -140,7 +140,7 @@
     <t>METALICA</t>
   </si>
   <si>
-    <t>260,848</t>
+    <t>260,752</t>
   </si>
   <si>
     <t>3.0%</t>
@@ -149,7 +149,7 @@
     <t>PEGAMENTOS</t>
   </si>
   <si>
-    <t>632,170</t>
+    <t>631,594</t>
   </si>
   <si>
     <t>7.4%</t>
@@ -167,7 +167,7 @@
     <t>PINTURA</t>
   </si>
   <si>
-    <t>1,245,181</t>
+    <t>1,245,145</t>
   </si>
   <si>
     <t>14.5%</t>
@@ -176,7 +176,7 @@
     <t>REPRESENTADAS</t>
   </si>
   <si>
-    <t>319,747</t>
+    <t>319,627</t>
   </si>
   <si>
     <t>3.7%</t>
@@ -10518,7 +10518,7 @@
         <v>96</v>
       </c>
       <c r="F2" s="34">
-        <v>10869</v>
+        <v>10845</v>
       </c>
       <c r="G2" s="35" t="s">
         <v>69</v>
@@ -10541,7 +10541,7 @@
         <v>96</v>
       </c>
       <c r="F3" s="34">
-        <v>12288</v>
+        <v>12264</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>69</v>
@@ -10564,7 +10564,7 @@
         <v>96</v>
       </c>
       <c r="F4" s="34">
-        <v>11433</v>
+        <v>11409</v>
       </c>
       <c r="G4" s="35" t="s">
         <v>69</v>
@@ -10656,7 +10656,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="34">
-        <v>10076</v>
+        <v>10052</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>69</v>
@@ -11481,7 +11481,7 @@
         <v>192</v>
       </c>
       <c r="F12" s="34">
-        <v>38556</v>
+        <v>37980</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>69</v>
@@ -17271,7 +17271,7 @@
         <v>36</v>
       </c>
       <c r="F49" s="34">
-        <v>38450</v>
+        <v>38414</v>
       </c>
       <c r="G49" s="35" t="s">
         <v>69</v>
@@ -19821,7 +19821,7 @@
         <v>40</v>
       </c>
       <c r="F82" s="34">
-        <v>2716</v>
+        <v>2596</v>
       </c>
       <c r="G82" s="35" t="s">
         <v>69</v>
@@ -23015,7 +23015,7 @@
         <v>60</v>
       </c>
       <c r="F23" s="34">
-        <v>666</v>
+        <v>606</v>
       </c>
       <c r="G23" s="35" t="s">
         <v>69</v>
@@ -23084,7 +23084,7 @@
         <v>36</v>
       </c>
       <c r="F26" s="34">
-        <v>5421</v>
+        <v>5385</v>
       </c>
       <c r="G26" s="35" t="s">
         <v>69</v>
@@ -23153,7 +23153,7 @@
         <v>36</v>
       </c>
       <c r="F29" s="34">
-        <v>5346</v>
+        <v>5310</v>
       </c>
       <c r="G29" s="35" t="s">
         <v>69</v>
@@ -23199,7 +23199,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="34">
-        <v>155937</v>
+        <v>153777</v>
       </c>
       <c r="G31" s="35" t="s">
         <v>69</v>
@@ -23245,7 +23245,7 @@
         <v>120</v>
       </c>
       <c r="F33" s="34">
-        <v>40352</v>
+        <v>39992</v>
       </c>
       <c r="G33" s="35" t="s">
         <v>69</v>
@@ -23337,7 +23337,7 @@
         <v>120</v>
       </c>
       <c r="F37" s="34">
-        <v>11290</v>
+        <v>10930</v>
       </c>
       <c r="G37" s="35" t="s">
         <v>69</v>
@@ -23935,7 +23935,7 @@
         <v>120</v>
       </c>
       <c r="F63" s="34">
-        <v>9089</v>
+        <v>9041</v>
       </c>
       <c r="G63" s="35" t="s">
         <v>69</v>
@@ -24829,7 +24829,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="34">
-        <v>11958</v>
+        <v>11708</v>
       </c>
       <c r="G5" s="35" t="s">
         <v>69</v>
@@ -24875,7 +24875,7 @@
         <v>50</v>
       </c>
       <c r="F7" s="34">
-        <v>7589</v>
+        <v>7539</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>69</v>
@@ -24921,7 +24921,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="34">
-        <v>3793</v>
+        <v>3743</v>
       </c>
       <c r="G9" s="35" t="s">
         <v>69</v>
@@ -24944,7 +24944,7 @@
         <v>50</v>
       </c>
       <c r="F10" s="34">
-        <v>13954</v>
+        <v>13854</v>
       </c>
       <c r="G10" s="35" t="s">
         <v>69</v>
@@ -24990,7 +24990,7 @@
         <v>50</v>
       </c>
       <c r="F12" s="34">
-        <v>3159</v>
+        <v>3109</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>69</v>
@@ -25036,7 +25036,7 @@
         <v>50</v>
       </c>
       <c r="F14" s="34">
-        <v>321</v>
+        <v>271</v>
       </c>
       <c r="G14" s="35" t="s">
         <v>69</v>
@@ -25059,7 +25059,7 @@
         <v>50</v>
       </c>
       <c r="F15" s="34">
-        <v>445</v>
+        <v>395</v>
       </c>
       <c r="G15" s="35" t="s">
         <v>69</v>
@@ -25128,7 +25128,7 @@
         <v>50</v>
       </c>
       <c r="F18" s="34">
-        <v>15769</v>
+        <v>15719</v>
       </c>
       <c r="G18" s="35" t="s">
         <v>69</v>
@@ -25197,7 +25197,7 @@
         <v>50</v>
       </c>
       <c r="F21" s="34">
-        <v>800</v>
+        <v>750</v>
       </c>
       <c r="G21" s="35" t="s">
         <v>69</v>
@@ -25220,7 +25220,7 @@
         <v>50</v>
       </c>
       <c r="F22" s="34">
-        <v>793</v>
+        <v>743</v>
       </c>
       <c r="G22" s="35" t="s">
         <v>69</v>
@@ -25289,7 +25289,7 @@
         <v>50</v>
       </c>
       <c r="F25" s="34">
-        <v>23061</v>
+        <v>23011</v>
       </c>
       <c r="G25" s="35" t="s">
         <v>69</v>
@@ -25496,7 +25496,7 @@
         <v>50</v>
       </c>
       <c r="F34" s="34">
-        <v>8424</v>
+        <v>8399</v>
       </c>
       <c r="G34" s="35" t="s">
         <v>69</v>
@@ -25519,7 +25519,7 @@
         <v>50</v>
       </c>
       <c r="F35" s="34">
-        <v>18686</v>
+        <v>18661</v>
       </c>
       <c r="G35" s="35" t="s">
         <v>69</v>
@@ -25542,7 +25542,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="34">
-        <v>24483</v>
+        <v>24458</v>
       </c>
       <c r="G36" s="35" t="s">
         <v>69</v>
@@ -27451,7 +27451,7 @@
         <v>24</v>
       </c>
       <c r="F119" s="34">
-        <v>25356</v>
+        <v>25116</v>
       </c>
       <c r="G119" s="35" t="s">
         <v>69</v>
@@ -33514,7 +33514,7 @@
         <v>200</v>
       </c>
       <c r="F65" s="34">
-        <v>5330</v>
+        <v>4930</v>
       </c>
       <c r="G65" s="35" t="s">
         <v>69</v>
@@ -33537,7 +33537,7 @@
         <v>200</v>
       </c>
       <c r="F66" s="34">
-        <v>7647</v>
+        <v>7447</v>
       </c>
       <c r="G66" s="35" t="s">
         <v>69</v>
@@ -33560,7 +33560,7 @@
         <v>200</v>
       </c>
       <c r="F67" s="34">
-        <v>33838</v>
+        <v>33638</v>
       </c>
       <c r="G67" s="35" t="s">
         <v>69</v>
@@ -33606,7 +33606,7 @@
         <v>200</v>
       </c>
       <c r="F69" s="34">
-        <v>25179</v>
+        <v>24979</v>
       </c>
       <c r="G69" s="35" t="s">
         <v>69</v>
@@ -33629,7 +33629,7 @@
         <v>200</v>
       </c>
       <c r="F70" s="34">
-        <v>11081</v>
+        <v>9581</v>
       </c>
       <c r="G70" s="35" t="s">
         <v>69</v>
@@ -33928,7 +33928,7 @@
         <v>1152</v>
       </c>
       <c r="F83" s="36">
-        <v>227</v>
+        <v>191</v>
       </c>
       <c r="G83" s="37" t="s">
         <v>109</v>
@@ -33974,7 +33974,7 @@
         <v>1152</v>
       </c>
       <c r="F85" s="36">
-        <v>3385</v>
+        <v>3349</v>
       </c>
       <c r="G85" s="37" t="s">
         <v>109</v>
@@ -35397,7 +35397,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="34">
-        <v>74821</v>
+        <v>73971</v>
       </c>
       <c r="G2" s="35" t="s">
         <v>69</v>
@@ -35420,7 +35420,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="34">
-        <v>212993</v>
+        <v>210993</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>69</v>
@@ -35650,7 +35650,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="34">
-        <v>130113</v>
+        <v>128613</v>
       </c>
       <c r="G13" s="35" t="s">
         <v>69</v>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -29,7 +29,7 @@
     <t>STOCKPULSE - RESUMEN</t>
   </si>
   <si>
-    <t>Actualización: 09/03/2026, 12:03:34</t>
+    <t>Actualización: 09/03/2026, 13:53:44</t>
   </si>
   <si>
     <t>TOTAL GENERAL</t>
@@ -41,7 +41,7 @@
     <t>Unidades:</t>
   </si>
   <si>
-    <t>8,566,118</t>
+    <t>8,583,451</t>
   </si>
   <si>
     <t>Agotados:</t>
@@ -68,7 +68,7 @@
     <t>ACCESORIOS</t>
   </si>
   <si>
-    <t>975,707</t>
+    <t>976,033</t>
   </si>
   <si>
     <t>11.4%</t>
@@ -77,16 +77,16 @@
     <t>ARCHIVO</t>
   </si>
   <si>
-    <t>1,755,340</t>
-  </si>
-  <si>
-    <t>20.5%</t>
+    <t>1,752,614</t>
+  </si>
+  <si>
+    <t>20.4%</t>
   </si>
   <si>
     <t>DIBUJO</t>
   </si>
   <si>
-    <t>118,449</t>
+    <t>117,649</t>
   </si>
   <si>
     <t>1.4%</t>
@@ -104,25 +104,25 @@
     <t>ESCRITURA</t>
   </si>
   <si>
-    <t>1,453,700</t>
-  </si>
-  <si>
-    <t>17.0%</t>
+    <t>1,453,492</t>
+  </si>
+  <si>
+    <t>16.9%</t>
   </si>
   <si>
     <t>FORROS</t>
   </si>
   <si>
-    <t>854,459</t>
-  </si>
-  <si>
-    <t>10.0%</t>
+    <t>879,610</t>
+  </si>
+  <si>
+    <t>10.2%</t>
   </si>
   <si>
     <t>MANUALIDADES</t>
   </si>
   <si>
-    <t>436,973</t>
+    <t>435,893</t>
   </si>
   <si>
     <t>5.1%</t>
@@ -140,7 +140,7 @@
     <t>METALICA</t>
   </si>
   <si>
-    <t>260,752</t>
+    <t>259,755</t>
   </si>
   <si>
     <t>3.0%</t>
@@ -149,16 +149,16 @@
     <t>PEGAMENTOS</t>
   </si>
   <si>
-    <t>631,594</t>
-  </si>
-  <si>
-    <t>7.4%</t>
+    <t>628,873</t>
+  </si>
+  <si>
+    <t>7.3%</t>
   </si>
   <si>
     <t>PELOTAS</t>
   </si>
   <si>
-    <t>477,986</t>
+    <t>480,148</t>
   </si>
   <si>
     <t>5.6%</t>
@@ -167,7 +167,7 @@
     <t>PINTURA</t>
   </si>
   <si>
-    <t>1,245,145</t>
+    <t>1,243,751</t>
   </si>
   <si>
     <t>14.5%</t>
@@ -176,7 +176,7 @@
     <t>REPRESENTADAS</t>
   </si>
   <si>
-    <t>319,627</t>
+    <t>319,247</t>
   </si>
   <si>
     <t>3.7%</t>
@@ -10217,13 +10217,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="6">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="7">
-        <v>242</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10" ht="25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -10771,7 +10771,7 @@
         <v>96</v>
       </c>
       <c r="F13" s="34">
-        <v>1735</v>
+        <v>1639</v>
       </c>
       <c r="G13" s="35" t="s">
         <v>69</v>
@@ -10794,7 +10794,7 @@
         <v>400</v>
       </c>
       <c r="F14" s="34">
-        <v>16202</v>
+        <v>15802</v>
       </c>
       <c r="G14" s="35" t="s">
         <v>69</v>
@@ -10817,7 +10817,7 @@
         <v>100</v>
       </c>
       <c r="F15" s="34">
-        <v>40069</v>
+        <v>39569</v>
       </c>
       <c r="G15" s="35" t="s">
         <v>69</v>
@@ -10932,7 +10932,7 @@
         <v>72</v>
       </c>
       <c r="F20" s="34">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="G20" s="35" t="s">
         <v>69</v>
@@ -11251,7 +11251,7 @@
         <v>288</v>
       </c>
       <c r="F2" s="34">
-        <v>39219</v>
+        <v>36339</v>
       </c>
       <c r="G2" s="35" t="s">
         <v>69</v>
@@ -11481,7 +11481,7 @@
         <v>192</v>
       </c>
       <c r="F12" s="34">
-        <v>37980</v>
+        <v>37974</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>69</v>
@@ -11527,7 +11527,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="34">
-        <v>91774</v>
+        <v>91771</v>
       </c>
       <c r="G14" s="35" t="s">
         <v>69</v>
@@ -11550,7 +11550,7 @@
         <v>24</v>
       </c>
       <c r="F15" s="34">
-        <v>10937</v>
+        <v>11105</v>
       </c>
       <c r="G15" s="35" t="s">
         <v>69</v>
@@ -11915,7 +11915,7 @@
         <v>24</v>
       </c>
       <c r="F8" s="34">
-        <v>4741</v>
+        <v>5341</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>69</v>
@@ -12351,11 +12351,11 @@
       <c r="E27">
         <v>36</v>
       </c>
-      <c r="F27" s="32">
-        <v>0</v>
-      </c>
-      <c r="G27" s="33" t="s">
-        <v>65</v>
+      <c r="F27" s="36">
+        <v>1</v>
+      </c>
+      <c r="G27" s="37" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -12674,7 +12674,7 @@
         <v>48</v>
       </c>
       <c r="F41" s="36">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G41" s="37" t="s">
         <v>109</v>
@@ -12927,7 +12927,7 @@
         <v>48</v>
       </c>
       <c r="F52" s="36">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G52" s="37" t="s">
         <v>109</v>
@@ -12949,11 +12949,11 @@
       <c r="E53">
         <v>48</v>
       </c>
-      <c r="F53" s="32">
-        <v>0</v>
-      </c>
-      <c r="G53" s="33" t="s">
-        <v>65</v>
+      <c r="F53" s="36">
+        <v>5</v>
+      </c>
+      <c r="G53" s="37" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -13640,7 +13640,7 @@
         <v>60</v>
       </c>
       <c r="F83" s="34">
-        <v>1037</v>
+        <v>1013</v>
       </c>
       <c r="G83" s="35" t="s">
         <v>69</v>
@@ -14169,7 +14169,7 @@
         <v>60</v>
       </c>
       <c r="F106" s="34">
-        <v>853</v>
+        <v>1458</v>
       </c>
       <c r="G106" s="35" t="s">
         <v>69</v>
@@ -14215,7 +14215,7 @@
         <v>60</v>
       </c>
       <c r="F108" s="34">
-        <v>1999</v>
+        <v>2999</v>
       </c>
       <c r="G108" s="35" t="s">
         <v>69</v>
@@ -14353,7 +14353,7 @@
         <v>60</v>
       </c>
       <c r="F114" s="34">
-        <v>11130</v>
+        <v>11106</v>
       </c>
       <c r="G114" s="35" t="s">
         <v>69</v>
@@ -15089,7 +15089,7 @@
         <v>60</v>
       </c>
       <c r="F146" s="34">
-        <v>750</v>
+        <v>743</v>
       </c>
       <c r="G146" s="35" t="s">
         <v>69</v>
@@ -16328,7 +16328,7 @@
         <v>72</v>
       </c>
       <c r="F8" s="34">
-        <v>15506</v>
+        <v>15505</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>69</v>
@@ -16420,7 +16420,7 @@
         <v>144</v>
       </c>
       <c r="F12" s="34">
-        <v>16099</v>
+        <v>15523</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>69</v>
@@ -16535,7 +16535,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="34">
-        <v>98197</v>
+        <v>98101</v>
       </c>
       <c r="G17" s="35" t="s">
         <v>69</v>
@@ -17271,7 +17271,7 @@
         <v>36</v>
       </c>
       <c r="F49" s="34">
-        <v>38414</v>
+        <v>37693</v>
       </c>
       <c r="G49" s="35" t="s">
         <v>69</v>
@@ -17981,7 +17981,7 @@
         <v>30</v>
       </c>
       <c r="F2" s="34">
-        <v>6590</v>
+        <v>6410</v>
       </c>
       <c r="G2" s="35" t="s">
         <v>69</v>
@@ -18050,7 +18050,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="34">
-        <v>20689</v>
+        <v>20489</v>
       </c>
       <c r="G5" s="35" t="s">
         <v>69</v>
@@ -22555,7 +22555,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="34">
-        <v>2704</v>
+        <v>2703</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>69</v>
@@ -23038,7 +23038,7 @@
         <v>60</v>
       </c>
       <c r="F24" s="34">
-        <v>3514</v>
+        <v>3513</v>
       </c>
       <c r="G24" s="35" t="s">
         <v>69</v>
@@ -23199,7 +23199,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="34">
-        <v>153777</v>
+        <v>153771</v>
       </c>
       <c r="G31" s="35" t="s">
         <v>69</v>
@@ -23360,7 +23360,7 @@
         <v>120</v>
       </c>
       <c r="F38" s="34">
-        <v>101258</v>
+        <v>101256</v>
       </c>
       <c r="G38" s="35" t="s">
         <v>69</v>
@@ -23636,7 +23636,7 @@
         <v>144</v>
       </c>
       <c r="F50" s="34">
-        <v>5674</v>
+        <v>5656</v>
       </c>
       <c r="G50" s="35" t="s">
         <v>69</v>
@@ -23682,7 +23682,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="34">
-        <v>6496</v>
+        <v>6526</v>
       </c>
       <c r="G52" s="35" t="s">
         <v>69</v>
@@ -23727,11 +23727,11 @@
       <c r="E54">
         <v>144</v>
       </c>
-      <c r="F54" s="32">
-        <v>0</v>
-      </c>
-      <c r="G54" s="33" t="s">
-        <v>65</v>
+      <c r="F54" s="36">
+        <v>432</v>
+      </c>
+      <c r="G54" s="37" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -23843,7 +23843,7 @@
         <v>144</v>
       </c>
       <c r="F59" s="34">
-        <v>4562</v>
+        <v>4550</v>
       </c>
       <c r="G59" s="35" t="s">
         <v>69</v>
@@ -23889,7 +23889,7 @@
         <v>96</v>
       </c>
       <c r="F61" s="34">
-        <v>3341</v>
+        <v>3245</v>
       </c>
       <c r="G61" s="35" t="s">
         <v>69</v>
@@ -24829,7 +24829,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="34">
-        <v>11708</v>
+        <v>11704</v>
       </c>
       <c r="G5" s="35" t="s">
         <v>69</v>
@@ -26324,7 +26324,7 @@
         <v>100</v>
       </c>
       <c r="F70" s="34">
-        <v>5567</v>
+        <v>5067</v>
       </c>
       <c r="G70" s="35" t="s">
         <v>69</v>
@@ -26370,7 +26370,7 @@
         <v>100</v>
       </c>
       <c r="F72" s="34">
-        <v>30095</v>
+        <v>30071</v>
       </c>
       <c r="G72" s="35" t="s">
         <v>69</v>
@@ -26485,7 +26485,7 @@
         <v>100</v>
       </c>
       <c r="F77" s="34">
-        <v>43524</v>
+        <v>43324</v>
       </c>
       <c r="G77" s="35" t="s">
         <v>69</v>
@@ -27658,7 +27658,7 @@
         <v>24</v>
       </c>
       <c r="F128" s="34">
-        <v>5434</v>
+        <v>5534</v>
       </c>
       <c r="G128" s="35" t="s">
         <v>69</v>
@@ -28164,7 +28164,7 @@
         <v>12</v>
       </c>
       <c r="F150" s="34">
-        <v>557</v>
+        <v>543</v>
       </c>
       <c r="G150" s="35" t="s">
         <v>69</v>
@@ -28325,7 +28325,7 @@
         <v>6</v>
       </c>
       <c r="F157" s="34">
-        <v>263</v>
+        <v>179</v>
       </c>
       <c r="G157" s="35" t="s">
         <v>69</v>
@@ -30556,7 +30556,7 @@
         <v>40</v>
       </c>
       <c r="F254" s="34">
-        <v>143054</v>
+        <v>141054</v>
       </c>
       <c r="G254" s="35" t="s">
         <v>69</v>
@@ -31036,7 +31036,7 @@
         <v>400</v>
       </c>
       <c r="F8" s="34">
-        <v>17523</v>
+        <v>16723</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>69</v>
@@ -32111,7 +32111,7 @@
         <v>144</v>
       </c>
       <c r="F4" s="34">
-        <v>27804</v>
+        <v>27803</v>
       </c>
       <c r="G4" s="35" t="s">
         <v>69</v>
@@ -32502,7 +32502,7 @@
         <v>192</v>
       </c>
       <c r="F21" s="34">
-        <v>9267</v>
+        <v>9266</v>
       </c>
       <c r="G21" s="35" t="s">
         <v>69</v>
@@ -32571,7 +32571,7 @@
         <v>96</v>
       </c>
       <c r="F24" s="34">
-        <v>3511</v>
+        <v>3510</v>
       </c>
       <c r="G24" s="35" t="s">
         <v>69</v>
@@ -33767,7 +33767,7 @@
         <v>200</v>
       </c>
       <c r="F76" s="34">
-        <v>61188</v>
+        <v>60988</v>
       </c>
       <c r="G76" s="35" t="s">
         <v>69</v>
@@ -33974,7 +33974,7 @@
         <v>1152</v>
       </c>
       <c r="F85" s="36">
-        <v>3349</v>
+        <v>3348</v>
       </c>
       <c r="G85" s="37" t="s">
         <v>109</v>
@@ -34227,7 +34227,7 @@
         <v>144</v>
       </c>
       <c r="F96" s="34">
-        <v>189585</v>
+        <v>189582</v>
       </c>
       <c r="G96" s="35" t="s">
         <v>69</v>
@@ -34848,7 +34848,7 @@
         <v>192</v>
       </c>
       <c r="F123" s="34">
-        <v>23601</v>
+        <v>23600</v>
       </c>
       <c r="G123" s="35" t="s">
         <v>69</v>
@@ -35397,7 +35397,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="34">
-        <v>73971</v>
+        <v>75638</v>
       </c>
       <c r="G2" s="35" t="s">
         <v>69</v>
@@ -35420,7 +35420,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="34">
-        <v>210993</v>
+        <v>235977</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>69</v>
@@ -35443,7 +35443,7 @@
         <v>100</v>
       </c>
       <c r="F4" s="34">
-        <v>83362</v>
+        <v>82862</v>
       </c>
       <c r="G4" s="35" t="s">
         <v>69</v>
@@ -35535,7 +35535,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="34">
-        <v>69808</v>
+        <v>69708</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>69</v>
@@ -35650,7 +35650,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="34">
-        <v>128613</v>
+        <v>128213</v>
       </c>
       <c r="G13" s="35" t="s">
         <v>69</v>
@@ -35673,7 +35673,7 @@
         <v>100</v>
       </c>
       <c r="F14" s="34">
-        <v>114396</v>
+        <v>113896</v>
       </c>
       <c r="G14" s="35" t="s">
         <v>69</v>
@@ -35739,7 +35739,7 @@
         <v>72</v>
       </c>
       <c r="F2" s="34">
-        <v>120536</v>
+        <v>120176</v>
       </c>
       <c r="G2" s="35" t="s">
         <v>69</v>
@@ -35762,7 +35762,7 @@
         <v>72</v>
       </c>
       <c r="F3" s="34">
-        <v>216410</v>
+        <v>215690</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>69</v>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -29,7 +29,7 @@
     <t>STOCKPULSE - RESUMEN</t>
   </si>
   <si>
-    <t>Actualización: 09/03/2026, 18:28:29</t>
+    <t>Actualización: 09/03/2026, 20:59:53</t>
   </si>
   <si>
     <t>TOTAL GENERAL</t>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -29,7 +29,7 @@
     <t>STOCKPULSE - RESUMEN</t>
   </si>
   <si>
-    <t>Actualización: 10/03/2026, 08:00:35</t>
+    <t>Actualización: 10/03/2026, 08:22:27</t>
   </si>
   <si>
     <t>TOTAL GENERAL</t>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -29,7 +29,7 @@
     <t>STOCKPULSE - RESUMEN</t>
   </si>
   <si>
-    <t>Actualización: 10/03/2026, 15:34:38</t>
+    <t>Actualización: 10/03/2026, 16:48:18</t>
   </si>
   <si>
     <t>TOTAL GENERAL</t>
@@ -41,7 +41,7 @@
     <t>Unidades:</t>
   </si>
   <si>
-    <t>8,330,991</t>
+    <t>8,325,829</t>
   </si>
   <si>
     <t>Agotados:</t>
@@ -68,7 +68,7 @@
     <t>ACCESORIOS</t>
   </si>
   <si>
-    <t>934,276</t>
+    <t>934,154</t>
   </si>
   <si>
     <t>11.2%</t>
@@ -77,7 +77,7 @@
     <t>ARCHIVO</t>
   </si>
   <si>
-    <t>1,732,787</t>
+    <t>1,732,783</t>
   </si>
   <si>
     <t>20.8%</t>
@@ -104,7 +104,7 @@
     <t>ESCRITURA</t>
   </si>
   <si>
-    <t>1,423,045</t>
+    <t>1,421,844</t>
   </si>
   <si>
     <t>17.1%</t>
@@ -113,7 +113,7 @@
     <t>FORROS</t>
   </si>
   <si>
-    <t>833,110</t>
+    <t>832,410</t>
   </si>
   <si>
     <t>10.0%</t>
@@ -122,7 +122,7 @@
     <t>MANUALIDADES</t>
   </si>
   <si>
-    <t>425,994</t>
+    <t>425,993</t>
   </si>
   <si>
     <t>5.1%</t>
@@ -140,7 +140,7 @@
     <t>METALICA</t>
   </si>
   <si>
-    <t>244,952</t>
+    <t>244,752</t>
   </si>
   <si>
     <t>2.9%</t>
@@ -149,7 +149,7 @@
     <t>PEGAMENTOS</t>
   </si>
   <si>
-    <t>582,928</t>
+    <t>582,042</t>
   </si>
   <si>
     <t>7.0%</t>
@@ -158,7 +158,7 @@
     <t>PELOTAS</t>
   </si>
   <si>
-    <t>476,718</t>
+    <t>476,362</t>
   </si>
   <si>
     <t>5.7%</t>
@@ -167,7 +167,7 @@
     <t>PINTURA</t>
   </si>
   <si>
-    <t>1,224,131</t>
+    <t>1,223,313</t>
   </si>
   <si>
     <t>14.7%</t>
@@ -176,7 +176,7 @@
     <t>REPRESENTADAS</t>
   </si>
   <si>
-    <t>313,942</t>
+    <t>313,068</t>
   </si>
   <si>
     <t>3.8%</t>
@@ -10217,13 +10217,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="6">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="7">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10" ht="25" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -10817,7 +10817,7 @@
         <v>100</v>
       </c>
       <c r="F15" s="34">
-        <v>38969</v>
+        <v>38769</v>
       </c>
       <c r="G15" s="35" t="s">
         <v>69</v>
@@ -11251,7 +11251,7 @@
         <v>288</v>
       </c>
       <c r="F2" s="34">
-        <v>36339</v>
+        <v>36051</v>
       </c>
       <c r="G2" s="35" t="s">
         <v>69</v>
@@ -11527,7 +11527,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="34">
-        <v>78778</v>
+        <v>78180</v>
       </c>
       <c r="G14" s="35" t="s">
         <v>69</v>
@@ -11800,7 +11800,7 @@
         <v>24</v>
       </c>
       <c r="F3" s="34">
-        <v>2038</v>
+        <v>2032</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>69</v>
@@ -11915,7 +11915,7 @@
         <v>24</v>
       </c>
       <c r="F8" s="34">
-        <v>5329</v>
+        <v>5323</v>
       </c>
       <c r="G8" s="35" t="s">
         <v>69</v>
@@ -12282,11 +12282,11 @@
       <c r="E24">
         <v>48</v>
       </c>
-      <c r="F24" s="36">
-        <v>1</v>
-      </c>
-      <c r="G24" s="37" t="s">
-        <v>109</v>
+      <c r="F24" s="32">
+        <v>0</v>
+      </c>
+      <c r="G24" s="33" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -12305,11 +12305,11 @@
       <c r="E25">
         <v>48</v>
       </c>
-      <c r="F25" s="36">
-        <v>1</v>
-      </c>
-      <c r="G25" s="37" t="s">
-        <v>109</v>
+      <c r="F25" s="32">
+        <v>0</v>
+      </c>
+      <c r="G25" s="33" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -12490,7 +12490,7 @@
         <v>50</v>
       </c>
       <c r="F33" s="34">
-        <v>2910</v>
+        <v>2904</v>
       </c>
       <c r="G33" s="35" t="s">
         <v>69</v>
@@ -12605,7 +12605,7 @@
         <v>48</v>
       </c>
       <c r="F38" s="34">
-        <v>1375</v>
+        <v>1363</v>
       </c>
       <c r="G38" s="35" t="s">
         <v>69</v>
@@ -12812,7 +12812,7 @@
         <v>48</v>
       </c>
       <c r="F47" s="34">
-        <v>11761</v>
+        <v>11737</v>
       </c>
       <c r="G47" s="35" t="s">
         <v>69</v>
@@ -12927,7 +12927,7 @@
         <v>48</v>
       </c>
       <c r="F52" s="36">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="G52" s="37" t="s">
         <v>109</v>
@@ -13410,7 +13410,7 @@
         <v>60</v>
       </c>
       <c r="F73" s="34">
-        <v>3182</v>
+        <v>3170</v>
       </c>
       <c r="G73" s="35" t="s">
         <v>69</v>
@@ -13433,7 +13433,7 @@
         <v>60</v>
       </c>
       <c r="F74" s="34">
-        <v>1245</v>
+        <v>1221</v>
       </c>
       <c r="G74" s="35" t="s">
         <v>69</v>
@@ -13479,7 +13479,7 @@
         <v>60</v>
       </c>
       <c r="F76" s="34">
-        <v>8533</v>
+        <v>8509</v>
       </c>
       <c r="G76" s="35" t="s">
         <v>69</v>
@@ -13571,7 +13571,7 @@
         <v>60</v>
       </c>
       <c r="F80" s="36">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="G80" s="37" t="s">
         <v>109</v>
@@ -14008,7 +14008,7 @@
         <v>60</v>
       </c>
       <c r="F99" s="34">
-        <v>3842</v>
+        <v>3818</v>
       </c>
       <c r="G99" s="35" t="s">
         <v>69</v>
@@ -14192,7 +14192,7 @@
         <v>60</v>
       </c>
       <c r="F107" s="34">
-        <v>5505</v>
+        <v>5481</v>
       </c>
       <c r="G107" s="35" t="s">
         <v>69</v>
@@ -14353,7 +14353,7 @@
         <v>60</v>
       </c>
       <c r="F114" s="34">
-        <v>11004</v>
+        <v>10980</v>
       </c>
       <c r="G114" s="35" t="s">
         <v>69</v>
@@ -14675,7 +14675,7 @@
         <v>120</v>
       </c>
       <c r="F128" s="36">
-        <v>477</v>
+        <v>441</v>
       </c>
       <c r="G128" s="37" t="s">
         <v>109</v>
@@ -14974,7 +14974,7 @@
         <v>120</v>
       </c>
       <c r="F141" s="34">
-        <v>4127</v>
+        <v>4091</v>
       </c>
       <c r="G141" s="35" t="s">
         <v>69</v>
@@ -15457,7 +15457,7 @@
         <v>120</v>
       </c>
       <c r="F162" s="34">
-        <v>4648</v>
+        <v>4636</v>
       </c>
       <c r="G162" s="35" t="s">
         <v>69</v>
@@ -15664,7 +15664,7 @@
         <v>120</v>
       </c>
       <c r="F171" s="34">
-        <v>7678</v>
+        <v>7666</v>
       </c>
       <c r="G171" s="35" t="s">
         <v>69</v>
@@ -15687,7 +15687,7 @@
         <v>120</v>
       </c>
       <c r="F172" s="34">
-        <v>2053</v>
+        <v>2029</v>
       </c>
       <c r="G172" s="35" t="s">
         <v>69</v>
@@ -16420,7 +16420,7 @@
         <v>144</v>
       </c>
       <c r="F12" s="34">
-        <v>14243</v>
+        <v>13881</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>69</v>
@@ -16535,7 +16535,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="34">
-        <v>94853</v>
+        <v>94832</v>
       </c>
       <c r="G17" s="35" t="s">
         <v>69</v>
@@ -16696,7 +16696,7 @@
         <v>48</v>
       </c>
       <c r="F24" s="34">
-        <v>9802</v>
+        <v>9801</v>
       </c>
       <c r="G24" s="35" t="s">
         <v>69</v>
@@ -17248,7 +17248,7 @@
         <v>144</v>
       </c>
       <c r="F48" s="34">
-        <v>46934</v>
+        <v>46933</v>
       </c>
       <c r="G48" s="35" t="s">
         <v>69</v>
@@ -17271,7 +17271,7 @@
         <v>36</v>
       </c>
       <c r="F49" s="34">
-        <v>37807</v>
+        <v>37374</v>
       </c>
       <c r="G49" s="35" t="s">
         <v>69</v>
@@ -18832,7 +18832,7 @@
         <v>240</v>
       </c>
       <c r="F39" s="36">
-        <v>278</v>
+        <v>254</v>
       </c>
       <c r="G39" s="37" t="s">
         <v>109</v>
@@ -19038,11 +19038,11 @@
       <c r="E48">
         <v>120</v>
       </c>
-      <c r="F48" s="36">
-        <v>140</v>
-      </c>
-      <c r="G48" s="37" t="s">
-        <v>109</v>
+      <c r="F48" s="32">
+        <v>0</v>
+      </c>
+      <c r="G48" s="33" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -19177,7 +19177,7 @@
         <v>720</v>
       </c>
       <c r="F54" s="36">
-        <v>2462</v>
+        <v>2342</v>
       </c>
       <c r="G54" s="37" t="s">
         <v>109</v>
@@ -19246,7 +19246,7 @@
         <v>720</v>
       </c>
       <c r="F57" s="34">
-        <v>4873</v>
+        <v>4633</v>
       </c>
       <c r="G57" s="35" t="s">
         <v>69</v>
@@ -19384,7 +19384,7 @@
         <v>240</v>
       </c>
       <c r="F63" s="34">
-        <v>7884</v>
+        <v>7644</v>
       </c>
       <c r="G63" s="35" t="s">
         <v>69</v>
@@ -19706,7 +19706,7 @@
         <v>600</v>
       </c>
       <c r="F77" s="36">
-        <v>539</v>
+        <v>529</v>
       </c>
       <c r="G77" s="37" t="s">
         <v>109</v>
@@ -20074,7 +20074,7 @@
         <v>2</v>
       </c>
       <c r="F93" s="34">
-        <v>203</v>
+        <v>153</v>
       </c>
       <c r="G93" s="35" t="s">
         <v>69</v>
@@ -20097,7 +20097,7 @@
         <v>6</v>
       </c>
       <c r="F94" s="34">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="G94" s="35" t="s">
         <v>69</v>
@@ -23245,7 +23245,7 @@
         <v>120</v>
       </c>
       <c r="F33" s="34">
-        <v>38191</v>
+        <v>38071</v>
       </c>
       <c r="G33" s="35" t="s">
         <v>69</v>
@@ -24050,7 +24050,7 @@
         <v>12</v>
       </c>
       <c r="F68" s="36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G68" s="37" t="s">
         <v>109</v>
@@ -24648,7 +24648,7 @@
         <v>144</v>
       </c>
       <c r="F94" s="36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G94" s="37" t="s">
         <v>109</v>
@@ -26922,7 +26922,7 @@
         <v>100</v>
       </c>
       <c r="F96" s="34">
-        <v>15313</v>
+        <v>15309</v>
       </c>
       <c r="G96" s="35" t="s">
         <v>69</v>
@@ -32088,7 +32088,7 @@
         <v>144</v>
       </c>
       <c r="F3" s="34">
-        <v>36593</v>
+        <v>36592</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>69</v>
@@ -33629,7 +33629,7 @@
         <v>200</v>
       </c>
       <c r="F70" s="34">
-        <v>7171</v>
+        <v>5971</v>
       </c>
       <c r="G70" s="35" t="s">
         <v>69</v>
@@ -35420,7 +35420,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="34">
-        <v>226077</v>
+        <v>225777</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>69</v>
@@ -35489,7 +35489,7 @@
         <v>25</v>
       </c>
       <c r="F6" s="34">
-        <v>502</v>
+        <v>377</v>
       </c>
       <c r="G6" s="35" t="s">
         <v>69</v>
@@ -35512,7 +35512,7 @@
         <v>25</v>
       </c>
       <c r="F7" s="34">
-        <v>5675</v>
+        <v>5800</v>
       </c>
       <c r="G7" s="35" t="s">
         <v>69</v>
@@ -35627,7 +35627,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="34">
-        <v>15778</v>
+        <v>15378</v>
       </c>
       <c r="G12" s="35" t="s">
         <v>69</v>
@@ -35762,7 +35762,7 @@
         <v>72</v>
       </c>
       <c r="F3" s="34">
-        <v>206682</v>
+        <v>206681</v>
       </c>
       <c r="G3" s="35" t="s">
         <v>69</v>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -29,7 +29,7 @@
     <t>STOCKPULSE - RESUMEN</t>
   </si>
   <si>
-    <t>Actualización: 10/03/2026, 17:28:56</t>
+    <t>Actualización: 10/03/2026, 18:12:03</t>
   </si>
   <si>
     <t>TOTAL GENERAL</t>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -29,7 +29,7 @@
     <t>STOCKPULSE - RESUMEN</t>
   </si>
   <si>
-    <t>Actualización: 10/03/2026, 18:12:03</t>
+    <t>Actualización: 10/03/2026, 18:28:28</t>
   </si>
   <si>
     <t>TOTAL GENERAL</t>

--- a/frontend/public/reports/StockPulse_TODOS.xlsx
+++ b/frontend/public/reports/StockPulse_TODOS.xlsx
@@ -29,7 +29,7 @@
     <t>STOCKPULSE - RESUMEN</t>
   </si>
   <si>
-    <t>Actualización: 10/03/2026, 18:28:28</t>
+    <t>Actualización: 10/03/2026, 20:59:39</t>
   </si>
   <si>
     <t>TOTAL GENERAL</t>
